--- a/out/production/MScanner/file/MScanner.xlsx
+++ b/out/production/MScanner/file/MScanner.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="НалБанки" sheetId="22" r:id="rId1"/>
-    <sheet name="Лизинг" sheetId="24" r:id="rId2"/>
+    <sheet name="Лизинг" sheetId="24" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="Выборподотл" localSheetId="1">Лизинг!$Y$14:$Y$15</definedName>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="58">
   <si>
     <t>Установка, у.е</t>
   </si>
@@ -217,26 +217,13 @@
 ЭКСПРЕСС-КРЕДИТ </t>
   </si>
   <si>
-    <t>+</t>
-  </si>
-  <si>
     <t>Просто</t>
-  </si>
-  <si>
-    <t>3 мес</t>
-  </si>
-  <si>
-    <t>10 мес</t>
   </si>
   <si>
     <t>15 мес</t>
   </si>
   <si>
     <t>НАЛ</t>
-  </si>
-  <si>
-    <t>АЛЬФА БАНК
-ЭКСПРЕСС-КРЕДИТ ПЛЮС</t>
   </si>
   <si>
     <t>60 мес</t>
@@ -251,16 +238,10 @@
     <t>СКРЕПКА-ДАБРАБЫТ</t>
   </si>
   <si>
-    <t>СКРЕПКА-ПАРИТЕТ</t>
-  </si>
-  <si>
     <t>РАССРОЧКА</t>
   </si>
   <si>
     <t>СКРП-Д</t>
-  </si>
-  <si>
-    <t>СКРП-П</t>
   </si>
   <si>
     <t>АЛЬФА-РАССРОЧКА</t>
@@ -273,9 +254,6 @@
   </si>
   <si>
     <t>% возн Д</t>
-  </si>
-  <si>
-    <t>% возн П</t>
   </si>
   <si>
     <t>Плюс</t>
@@ -295,6 +273,15 @@
   <si>
     <t>СБЕРБАНК - ГРЕЙС 6 МЕС</t>
   </si>
+  <si>
+    <t>ФШ</t>
+  </si>
+  <si>
+    <t>% возн ФШ</t>
+  </si>
+  <si>
+    <t>ФИНШОП</t>
+  </si>
 </sst>
 </file>
 
@@ -307,7 +294,7 @@
     <numFmt numFmtId="167" formatCode="#,##0_ ;[Red]\-#,##0\ "/>
     <numFmt numFmtId="168" formatCode="0.0000%"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -503,22 +490,6 @@
       <charset val="204"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="204"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
@@ -661,12 +632,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="2"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -689,8 +654,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="69">
+  <borders count="70">
     <border>
       <left/>
       <right/>
@@ -1559,10 +1530,23 @@
     </border>
     <border>
       <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -1570,7 +1554,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="356">
+  <cellXfs count="327">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
@@ -1789,7 +1773,270 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="18" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="7" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="33" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="19" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="17" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="25" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
@@ -1797,384 +2044,48 @@
       <alignment horizontal="right"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="167" fontId="19" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="19" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="167" fontId="19" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="26" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="26" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="19" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="1" fontId="19" fillId="7" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="19" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="33" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="19" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="17" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="26" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="1" fillId="27" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="1" fillId="27" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="1" fontId="19" fillId="3" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2185,11 +2096,15 @@
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="19" fillId="3" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
@@ -2213,6 +2128,18 @@
       <alignment horizontal="left" vertical="top"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
@@ -2221,16 +2148,208 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="8" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="8" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="8" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="9" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="9" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="9" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="18" fillId="6" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="18" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="3" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="3" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="3" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="3" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="3" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="3" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2265,130 +2384,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="18" fillId="6" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="18" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="3" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="3" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="3" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="3" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="3" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="3" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="3" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
@@ -2401,10 +2396,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
@@ -2413,7 +2404,7 @@
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
@@ -2421,162 +2412,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="1" fontId="19" fillId="3" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="3" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="8" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="8" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="8" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="9" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="9" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="9" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="1" fillId="23" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="1" fillId="23" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection hidden="1"/>
@@ -2589,19 +2424,19 @@
       <alignment horizontal="left" vertical="top"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
@@ -2927,6 +2762,48 @@
     </xf>
     <xf numFmtId="166" fontId="2" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="27" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -3351,8 +3228,8 @@
     <col min="13" max="13" width="9.77734375" style="9" customWidth="1" collapsed="1"/>
     <col min="14" max="15" width="9.77734375" style="9" hidden="1" customWidth="1"/>
     <col min="16" max="16" width="3.77734375" style="9" customWidth="1" collapsed="1"/>
-    <col min="17" max="17" width="9.77734375" style="143" customWidth="1" collapsed="1"/>
-    <col min="18" max="22" width="9.77734375" style="143" customWidth="1"/>
+    <col min="17" max="17" width="9.77734375" style="110" customWidth="1" collapsed="1"/>
+    <col min="18" max="22" width="9.77734375" style="110" customWidth="1"/>
     <col min="23" max="23" width="10.77734375" style="9" customWidth="1"/>
     <col min="24" max="24" width="10.77734375" style="9" customWidth="1" collapsed="1"/>
     <col min="25" max="25" width="9.77734375" style="9" customWidth="1" collapsed="1"/>
@@ -3378,12 +3255,12 @@
       <c r="N1" s="10"/>
       <c r="O1" s="10"/>
       <c r="P1" s="10"/>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="106"/>
-      <c r="S1" s="106"/>
-      <c r="T1" s="106"/>
-      <c r="U1" s="106"/>
-      <c r="V1" s="106"/>
+      <c r="Q1" s="82"/>
+      <c r="R1" s="82"/>
+      <c r="S1" s="82"/>
+      <c r="T1" s="82"/>
+      <c r="U1" s="82"/>
+      <c r="V1" s="82"/>
       <c r="W1" s="10"/>
       <c r="X1" s="12"/>
     </row>
@@ -3391,7 +3268,7 @@
       <c r="A2" s="12"/>
       <c r="B2" s="12"/>
       <c r="C2" s="3" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>18</v>
@@ -3414,3439 +3291,3177 @@
       <c r="J2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="237" t="s">
-        <v>45</v>
-      </c>
-      <c r="L2" s="238"/>
-      <c r="M2" s="107" t="s">
+      <c r="K2" s="168" t="s">
+        <v>41</v>
+      </c>
+      <c r="L2" s="169"/>
+      <c r="M2" s="83" t="s">
         <v>31</v>
       </c>
-      <c r="N2" s="108"/>
-      <c r="O2" s="150" t="s">
+      <c r="N2" s="84"/>
+      <c r="O2" s="117" t="s">
         <v>4</v>
       </c>
-      <c r="Q2" s="231" t="s">
+      <c r="Q2" s="162" t="s">
         <v>23</v>
       </c>
-      <c r="R2" s="232"/>
-      <c r="S2" s="232"/>
-      <c r="T2" s="232"/>
-      <c r="U2" s="232"/>
-      <c r="V2" s="233"/>
-      <c r="W2" s="177" t="s">
+      <c r="R2" s="163"/>
+      <c r="S2" s="163"/>
+      <c r="T2" s="163"/>
+      <c r="U2" s="163"/>
+      <c r="V2" s="164"/>
+      <c r="W2" s="160" t="s">
         <v>24</v>
       </c>
-      <c r="X2" s="172" t="s">
+      <c r="X2" s="152" t="s">
         <v>25</v>
       </c>
-      <c r="Y2" s="105"/>
-      <c r="Z2" s="105"/>
-      <c r="AA2" s="105"/>
+      <c r="Y2" s="81"/>
+      <c r="Z2" s="81"/>
+      <c r="AA2" s="81"/>
     </row>
     <row r="3" spans="1:27" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
-      <c r="C3" s="104">
+      <c r="C3" s="80">
         <v>0</v>
       </c>
-      <c r="D3" s="104">
+      <c r="D3" s="80">
         <v>0</v>
       </c>
-      <c r="E3" s="104">
+      <c r="E3" s="80">
         <v>0</v>
       </c>
-      <c r="F3" s="104">
+      <c r="F3" s="80">
         <v>0</v>
       </c>
-      <c r="G3" s="104">
+      <c r="G3" s="80">
         <v>0</v>
       </c>
-      <c r="H3" s="104">
+      <c r="H3" s="80">
         <v>0</v>
       </c>
-      <c r="I3" s="104">
+      <c r="I3" s="80">
         <v>40</v>
       </c>
-      <c r="J3" s="160">
+      <c r="J3" s="124">
         <v>3.2</v>
       </c>
-      <c r="K3" s="239"/>
-      <c r="L3" s="240"/>
-      <c r="M3" s="109">
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="85">
         <v>45490</v>
       </c>
-      <c r="N3" s="110"/>
-      <c r="O3" s="151">
+      <c r="N3" s="86"/>
+      <c r="O3" s="118">
         <v>0.3</v>
       </c>
-      <c r="Q3" s="234"/>
-      <c r="R3" s="235"/>
-      <c r="S3" s="235"/>
-      <c r="T3" s="235"/>
-      <c r="U3" s="235"/>
-      <c r="V3" s="236"/>
-      <c r="W3" s="178"/>
-      <c r="X3" s="173"/>
-      <c r="Y3" s="105"/>
-      <c r="Z3" s="111"/>
-      <c r="AA3" s="105"/>
+      <c r="Q3" s="165"/>
+      <c r="R3" s="166"/>
+      <c r="S3" s="166"/>
+      <c r="T3" s="166"/>
+      <c r="U3" s="166"/>
+      <c r="V3" s="167"/>
+      <c r="W3" s="161"/>
+      <c r="X3" s="153"/>
+      <c r="Y3" s="81"/>
+      <c r="Z3" s="87"/>
+      <c r="AA3" s="81"/>
     </row>
     <row r="4" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="12"/>
       <c r="B4" s="12"/>
-      <c r="C4" s="250">
+      <c r="C4" s="204">
         <f ca="1">TODAY()</f>
-        <v>45490</v>
-      </c>
-      <c r="D4" s="251"/>
-      <c r="E4" s="251"/>
-      <c r="F4" s="251"/>
-      <c r="G4" s="251"/>
-      <c r="H4" s="252"/>
-      <c r="I4" s="241">
+        <v>45761</v>
+      </c>
+      <c r="D4" s="205"/>
+      <c r="E4" s="205"/>
+      <c r="F4" s="205"/>
+      <c r="G4" s="205"/>
+      <c r="H4" s="206"/>
+      <c r="I4" s="172">
         <f>ROUNDUP((SUM(C3:I3)*O3 +SUM(C3:I3) )*J3,-1)</f>
         <v>170</v>
       </c>
-      <c r="J4" s="244">
+      <c r="J4" s="175">
         <f>ROUNDUP((((SUM(D3:F3)+SUM(H3:I3)+(SUM(G3)*0.75))*O3)+(SUM(D3:F3)+SUM(H3:I3)+(SUM(G3)*0.75)))*J3,-1)</f>
         <v>170</v>
       </c>
-      <c r="K4" s="112"/>
-      <c r="L4" s="112"/>
-      <c r="M4" s="113"/>
-      <c r="N4" s="113"/>
-      <c r="O4" s="113"/>
-      <c r="Q4" s="247"/>
-      <c r="R4" s="248"/>
-      <c r="S4" s="248"/>
-      <c r="T4" s="248"/>
-      <c r="U4" s="248"/>
-      <c r="V4" s="249"/>
-      <c r="W4" s="114"/>
-      <c r="X4" s="115"/>
+      <c r="K4" s="88"/>
+      <c r="L4" s="88"/>
+      <c r="M4" s="89"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
+      <c r="Q4" s="178"/>
+      <c r="R4" s="179"/>
+      <c r="S4" s="179"/>
+      <c r="T4" s="179"/>
+      <c r="U4" s="179"/>
+      <c r="V4" s="180"/>
+      <c r="W4" s="90"/>
+      <c r="X4" s="91"/>
       <c r="Y4" s="1"/>
-      <c r="AA4" s="105"/>
+      <c r="AA4" s="81"/>
     </row>
     <row r="5" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="12"/>
       <c r="B5" s="12"/>
-      <c r="C5" s="253" t="s">
+      <c r="C5" s="207" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="254"/>
-      <c r="E5" s="254"/>
-      <c r="F5" s="254"/>
-      <c r="G5" s="254"/>
-      <c r="H5" s="255"/>
-      <c r="I5" s="242"/>
-      <c r="J5" s="245"/>
-      <c r="K5" s="112"/>
-      <c r="L5" s="112"/>
-      <c r="N5" s="116" t="s">
-        <v>49</v>
-      </c>
-      <c r="O5" s="117" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q5" s="174"/>
-      <c r="R5" s="175"/>
-      <c r="S5" s="175"/>
-      <c r="T5" s="175"/>
-      <c r="U5" s="175"/>
-      <c r="V5" s="176"/>
-      <c r="W5" s="118"/>
-      <c r="X5" s="119"/>
-      <c r="Y5" s="120"/>
-      <c r="AA5" s="105"/>
+      <c r="D5" s="208"/>
+      <c r="E5" s="208"/>
+      <c r="F5" s="208"/>
+      <c r="G5" s="208"/>
+      <c r="H5" s="209"/>
+      <c r="I5" s="173"/>
+      <c r="J5" s="176"/>
+      <c r="K5" s="88"/>
+      <c r="L5" s="88"/>
+      <c r="O5" s="92" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q5" s="154"/>
+      <c r="R5" s="155"/>
+      <c r="S5" s="155"/>
+      <c r="T5" s="155"/>
+      <c r="U5" s="155"/>
+      <c r="V5" s="156"/>
+      <c r="W5" s="93"/>
+      <c r="X5" s="94"/>
+      <c r="Y5" s="95"/>
+      <c r="AA5" s="81"/>
     </row>
     <row r="6" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12"/>
       <c r="B6" s="12"/>
-      <c r="C6" s="256"/>
-      <c r="D6" s="257"/>
-      <c r="E6" s="257"/>
-      <c r="F6" s="257"/>
-      <c r="G6" s="257"/>
-      <c r="H6" s="258"/>
-      <c r="I6" s="243"/>
-      <c r="J6" s="246"/>
-      <c r="K6" s="112"/>
-      <c r="L6" s="112"/>
-      <c r="N6" s="279">
+      <c r="C6" s="210"/>
+      <c r="D6" s="211"/>
+      <c r="E6" s="211"/>
+      <c r="F6" s="211"/>
+      <c r="G6" s="211"/>
+      <c r="H6" s="212"/>
+      <c r="I6" s="174"/>
+      <c r="J6" s="177"/>
+      <c r="K6" s="88"/>
+      <c r="L6" s="88"/>
+      <c r="O6" s="239">
         <v>0.19989999999999999</v>
       </c>
-      <c r="O6" s="259">
-        <v>0.19989999999999999</v>
-      </c>
-      <c r="Q6" s="174"/>
-      <c r="R6" s="175"/>
-      <c r="S6" s="175"/>
-      <c r="T6" s="175"/>
-      <c r="U6" s="175"/>
-      <c r="V6" s="176"/>
-      <c r="W6" s="118"/>
-      <c r="X6" s="119"/>
-      <c r="Y6" s="120"/>
-      <c r="AA6" s="105"/>
+      <c r="Q6" s="154"/>
+      <c r="R6" s="155"/>
+      <c r="S6" s="155"/>
+      <c r="T6" s="155"/>
+      <c r="U6" s="155"/>
+      <c r="V6" s="156"/>
+      <c r="W6" s="93"/>
+      <c r="X6" s="94"/>
+      <c r="Y6" s="95"/>
+      <c r="AA6" s="81"/>
     </row>
     <row r="7" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="12"/>
       <c r="B7" s="12"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
-      <c r="E7" s="101"/>
-      <c r="F7" s="101"/>
-      <c r="G7" s="101"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="77"/>
+      <c r="G7" s="77"/>
       <c r="H7" s="10"/>
-      <c r="I7" s="102"/>
-      <c r="J7" s="103"/>
+      <c r="I7" s="78"/>
+      <c r="J7" s="79"/>
       <c r="K7" s="12"/>
       <c r="L7" s="12"/>
-      <c r="N7" s="280"/>
-      <c r="O7" s="260"/>
-      <c r="Q7" s="174"/>
-      <c r="R7" s="175"/>
-      <c r="S7" s="175"/>
-      <c r="T7" s="175"/>
-      <c r="U7" s="175"/>
-      <c r="V7" s="176"/>
-      <c r="W7" s="118"/>
-      <c r="X7" s="119"/>
-      <c r="Y7" s="105"/>
-      <c r="Z7" s="111"/>
-      <c r="AA7" s="105"/>
+      <c r="O7" s="240"/>
+      <c r="Q7" s="154"/>
+      <c r="R7" s="155"/>
+      <c r="S7" s="155"/>
+      <c r="T7" s="155"/>
+      <c r="U7" s="155"/>
+      <c r="V7" s="156"/>
+      <c r="W7" s="93"/>
+      <c r="X7" s="94"/>
+      <c r="Y7" s="81"/>
+      <c r="Z7" s="87"/>
+      <c r="AA7" s="81"/>
     </row>
     <row r="8" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="12"/>
       <c r="B8" s="12"/>
-      <c r="C8" s="194" t="s">
+      <c r="C8" s="221" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="195"/>
-      <c r="E8" s="196"/>
-      <c r="F8" s="212" t="s">
+      <c r="D8" s="222"/>
+      <c r="E8" s="223"/>
+      <c r="F8" s="226" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="212" t="s">
+      <c r="G8" s="226" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="200" t="s">
+      <c r="H8" s="185" t="s">
         <v>35</v>
       </c>
-      <c r="I8" s="201"/>
-      <c r="J8" s="201"/>
-      <c r="K8" s="201"/>
-      <c r="L8" s="202"/>
-      <c r="M8" s="121"/>
-      <c r="N8" s="122" t="s">
+      <c r="I8" s="185"/>
+      <c r="J8" s="185"/>
+      <c r="K8" s="185"/>
+      <c r="L8" s="186"/>
+      <c r="M8" s="96"/>
+      <c r="O8" s="129" t="s">
         <v>36</v>
       </c>
-      <c r="O8" s="123" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q8" s="174"/>
-      <c r="R8" s="175"/>
-      <c r="S8" s="175"/>
-      <c r="T8" s="175"/>
-      <c r="U8" s="175"/>
-      <c r="V8" s="176"/>
-      <c r="W8" s="118"/>
-      <c r="X8" s="119"/>
-      <c r="Y8" s="105"/>
-      <c r="Z8" s="105"/>
-      <c r="AA8" s="105"/>
+      <c r="Q8" s="154"/>
+      <c r="R8" s="155"/>
+      <c r="S8" s="155"/>
+      <c r="T8" s="155"/>
+      <c r="U8" s="155"/>
+      <c r="V8" s="156"/>
+      <c r="W8" s="93"/>
+      <c r="X8" s="94"/>
+      <c r="Y8" s="81"/>
+      <c r="Z8" s="81"/>
+      <c r="AA8" s="81"/>
     </row>
     <row r="9" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="12"/>
       <c r="B9" s="12"/>
-      <c r="C9" s="197"/>
-      <c r="D9" s="198"/>
-      <c r="E9" s="199"/>
-      <c r="F9" s="213"/>
-      <c r="G9" s="213"/>
-      <c r="H9" s="203"/>
-      <c r="I9" s="204"/>
-      <c r="J9" s="204"/>
-      <c r="K9" s="204"/>
-      <c r="L9" s="205"/>
-      <c r="M9" s="121"/>
-      <c r="N9" s="192">
-        <v>0.17</v>
-      </c>
-      <c r="O9" s="192">
-        <v>0.19900000000000001</v>
-      </c>
-      <c r="Q9" s="261"/>
-      <c r="R9" s="262"/>
-      <c r="S9" s="262"/>
-      <c r="T9" s="262"/>
-      <c r="U9" s="262"/>
-      <c r="V9" s="263"/>
-      <c r="W9" s="118"/>
-      <c r="X9" s="119"/>
-      <c r="Y9" s="105"/>
-      <c r="Z9" s="105"/>
-      <c r="AA9" s="105"/>
+      <c r="C9" s="67" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="72" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="72" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="227"/>
+      <c r="G9" s="227"/>
+      <c r="H9" s="187"/>
+      <c r="I9" s="187"/>
+      <c r="J9" s="187"/>
+      <c r="K9" s="187"/>
+      <c r="L9" s="188"/>
+      <c r="M9" s="96"/>
+      <c r="O9" s="183">
+        <v>0.17199999999999999</v>
+      </c>
+      <c r="Q9" s="197"/>
+      <c r="R9" s="198"/>
+      <c r="S9" s="198"/>
+      <c r="T9" s="198"/>
+      <c r="U9" s="198"/>
+      <c r="V9" s="199"/>
+      <c r="W9" s="93"/>
+      <c r="X9" s="94"/>
+      <c r="Y9" s="81"/>
+      <c r="Z9" s="81"/>
+      <c r="AA9" s="81"/>
     </row>
     <row r="10" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="12"/>
       <c r="B10" s="12"/>
       <c r="C10" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="71">
+        <f>ROUNDUP($N$20/100*(100+O12),-1)</f>
+        <v>170</v>
+      </c>
+      <c r="E10" s="71">
+        <f>ROUNDUP($O$20/100*(100+O12),-1)</f>
+        <v>170</v>
+      </c>
+      <c r="F10" s="65" t="str">
+        <f>"~"&amp;ROUNDUP(PMT($O$6/12,6,-D10),0)</f>
+        <v>~31</v>
+      </c>
+      <c r="G10" s="65" t="str">
+        <f>"~"&amp;ROUNDUP(PMT($O$6/12,6,-E10),0)</f>
+        <v>~31</v>
+      </c>
+      <c r="H10" s="125" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="87" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="88" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" s="213"/>
-      <c r="G10" s="213"/>
-      <c r="H10" s="80" t="s">
-        <v>7</v>
-      </c>
-      <c r="I10" s="206" t="s">
+      <c r="I10" s="189" t="s">
         <v>17</v>
       </c>
-      <c r="J10" s="207"/>
-      <c r="K10" s="264" t="s">
+      <c r="J10" s="190"/>
+      <c r="K10" s="200" t="s">
         <v>16</v>
       </c>
-      <c r="L10" s="265"/>
-      <c r="M10" s="121"/>
-      <c r="N10" s="193"/>
-      <c r="O10" s="193"/>
-      <c r="Q10" s="174"/>
-      <c r="R10" s="175"/>
-      <c r="S10" s="175"/>
-      <c r="T10" s="175"/>
-      <c r="U10" s="175"/>
-      <c r="V10" s="176"/>
-      <c r="W10" s="118"/>
-      <c r="X10" s="119"/>
-      <c r="Y10" s="105"/>
-      <c r="Z10" s="105"/>
-      <c r="AA10" s="105"/>
+      <c r="L10" s="201"/>
+      <c r="M10" s="96"/>
+      <c r="O10" s="184"/>
+      <c r="Q10" s="154"/>
+      <c r="R10" s="155"/>
+      <c r="S10" s="155"/>
+      <c r="T10" s="155"/>
+      <c r="U10" s="155"/>
+      <c r="V10" s="156"/>
+      <c r="W10" s="93"/>
+      <c r="X10" s="94"/>
+      <c r="Y10" s="81"/>
+      <c r="Z10" s="81"/>
+      <c r="AA10" s="81"/>
     </row>
     <row r="11" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="12"/>
       <c r="B11" s="12"/>
-      <c r="C11" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="124">
-        <f>ROUNDUP($N$20*1.016,-1)</f>
-        <v>180</v>
-      </c>
-      <c r="E11" s="125">
-        <f>ROUNDUP($O$20*1.016,-1)</f>
-        <v>180</v>
-      </c>
-      <c r="F11" s="65">
-        <f>ROUNDUP(PMT($N$9/12,3,-D11),0)</f>
-        <v>62</v>
-      </c>
-      <c r="G11" s="77">
-        <f>ROUNDUP(PMT($N$9/12,3,-E11),0)</f>
-        <v>62</v>
-      </c>
-      <c r="H11" s="81" t="s">
+      <c r="C11" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="64">
+        <f>ROUNDUP($N$20/100*(100+O13),-1)</f>
+        <v>170</v>
+      </c>
+      <c r="E11" s="64">
+        <f>ROUNDUP($O$20/100*(100+O13),-1)</f>
+        <v>170</v>
+      </c>
+      <c r="F11" s="66" t="str">
+        <f>"~"&amp;ROUNDUP(PMT($O$6/12,12,-D11),0)</f>
+        <v>~16</v>
+      </c>
+      <c r="G11" s="66" t="str">
+        <f>"~"&amp;ROUNDUP(PMT($O$6/12,12,-E11),0)</f>
+        <v>~16</v>
+      </c>
+      <c r="H11" s="126" t="s">
         <v>9</v>
       </c>
-      <c r="I11" s="214">
+      <c r="I11" s="193">
         <f>ROUNDUP(PMT($O$9/12,6,-$N$20),0)</f>
-        <v>31</v>
-      </c>
-      <c r="J11" s="215"/>
-      <c r="K11" s="208">
+        <v>30</v>
+      </c>
+      <c r="J11" s="194"/>
+      <c r="K11" s="191">
         <f>ROUNDUP(PMT($O$9/12,6,-$O$20),0)</f>
-        <v>31</v>
-      </c>
-      <c r="L11" s="209"/>
-      <c r="M11" s="121"/>
-      <c r="N11" s="126" t="s">
-        <v>54</v>
-      </c>
-      <c r="O11" s="127" t="s">
-        <v>55</v>
-      </c>
-      <c r="P11" s="128"/>
-      <c r="Q11" s="174"/>
-      <c r="R11" s="175"/>
-      <c r="S11" s="175"/>
-      <c r="T11" s="175"/>
-      <c r="U11" s="175"/>
-      <c r="V11" s="176"/>
-      <c r="W11" s="118"/>
-      <c r="X11" s="119"/>
-      <c r="Y11" s="105"/>
-      <c r="Z11" s="105"/>
-      <c r="AA11" s="105"/>
+        <v>30</v>
+      </c>
+      <c r="L11" s="192"/>
+      <c r="M11" s="96"/>
+      <c r="O11" s="98" t="s">
+        <v>48</v>
+      </c>
+      <c r="P11" s="99"/>
+      <c r="Q11" s="154"/>
+      <c r="R11" s="155"/>
+      <c r="S11" s="155"/>
+      <c r="T11" s="155"/>
+      <c r="U11" s="155"/>
+      <c r="V11" s="156"/>
+      <c r="W11" s="93"/>
+      <c r="X11" s="94"/>
+      <c r="Y11" s="81"/>
     </row>
     <row r="12" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="12"/>
       <c r="B12" s="12"/>
-      <c r="C12" s="66" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="124">
-        <f>ROUNDUP($N$20*1.021,-1)</f>
-        <v>180</v>
-      </c>
-      <c r="E12" s="125">
-        <f>ROUNDUP($O$20*1.021,-1)</f>
-        <v>180</v>
-      </c>
-      <c r="F12" s="67">
-        <f>ROUNDUP(PMT($N$9/12,6,-D12),0)</f>
-        <v>32</v>
-      </c>
-      <c r="G12" s="78">
-        <f>ROUNDUP(PMT($N$9/12,6,-E12),0)</f>
-        <v>32</v>
-      </c>
-      <c r="H12" s="81" t="s">
+      <c r="C12" s="63" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="64">
+        <f>ROUNDUP($N$20/100*(100+O14),-1)</f>
+        <v>170</v>
+      </c>
+      <c r="E12" s="64">
+        <f>ROUNDUP($O$20/100*(100+O14),-1)</f>
+        <v>170</v>
+      </c>
+      <c r="F12" s="66" t="str">
+        <f>"~"&amp;ROUNDUP(PMT($O$6/12,18,-D12),0)</f>
+        <v>~12</v>
+      </c>
+      <c r="G12" s="66" t="str">
+        <f>"~"&amp;ROUNDUP(PMT($O$6/12,18,-E12),0)</f>
+        <v>~12</v>
+      </c>
+      <c r="H12" s="126" t="s">
         <v>10</v>
       </c>
-      <c r="I12" s="216">
+      <c r="I12" s="195">
         <f>ROUNDUP(PMT($O$9/12,12,-$N$20),0)</f>
         <v>16</v>
       </c>
-      <c r="J12" s="217"/>
-      <c r="K12" s="208">
+      <c r="J12" s="196"/>
+      <c r="K12" s="191">
         <f>ROUNDUP(PMT($O$9/12,12,-$O$20),0)</f>
         <v>16</v>
       </c>
-      <c r="L12" s="209"/>
-      <c r="M12" s="121"/>
-      <c r="N12" s="125">
+      <c r="L12" s="192"/>
+      <c r="M12" s="96"/>
+      <c r="O12" s="119">
         <v>0</v>
       </c>
-      <c r="O12" s="124">
-        <v>0</v>
-      </c>
-      <c r="P12" s="128"/>
-      <c r="Q12" s="174"/>
-      <c r="R12" s="175"/>
-      <c r="S12" s="175"/>
-      <c r="T12" s="175"/>
-      <c r="U12" s="175"/>
-      <c r="V12" s="176"/>
-      <c r="W12" s="118"/>
-      <c r="X12" s="119"/>
-      <c r="Y12" s="105"/>
-      <c r="Z12" s="105"/>
-      <c r="AA12" s="105"/>
+      <c r="P12" s="99"/>
+      <c r="Q12" s="154"/>
+      <c r="R12" s="155"/>
+      <c r="S12" s="155"/>
+      <c r="T12" s="155"/>
+      <c r="U12" s="155"/>
+      <c r="V12" s="156"/>
+      <c r="W12" s="93"/>
+      <c r="X12" s="94"/>
+      <c r="Y12" s="81"/>
     </row>
     <row r="13" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="12"/>
       <c r="B13" s="12"/>
-      <c r="C13" s="66" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="124">
-        <f>ROUNDUP($N$20*1.031,-1)</f>
-        <v>180</v>
-      </c>
-      <c r="E13" s="125">
-        <f>ROUNDUP($O$20*1.031,-1)</f>
-        <v>180</v>
-      </c>
-      <c r="F13" s="67">
-        <f>ROUNDUP(PMT($N$9/12,10,-D13),0)</f>
-        <v>20</v>
-      </c>
-      <c r="G13" s="78">
-        <f>ROUNDUP(PMT($N$9/12,10,-E13),0)</f>
-        <v>20</v>
-      </c>
-      <c r="H13" s="81" t="s">
-        <v>11</v>
-      </c>
-      <c r="I13" s="216">
-        <f>ROUNDUP(PMT($O$9/12,18,-$N$20),0)</f>
+      <c r="C13" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="J13" s="217"/>
-      <c r="K13" s="208">
-        <f>ROUNDUP(PMT($O$9/12,18,-$O$20),0)</f>
+      <c r="D13" s="64">
+        <f>ROUNDUP($N$20/100*(100+O15),-1)</f>
+        <v>170</v>
+      </c>
+      <c r="E13" s="64">
+        <f>ROUNDUP($O$20/100*(100+O15),-1)</f>
+        <v>170</v>
+      </c>
+      <c r="F13" s="66" t="str">
+        <f>"~"&amp;ROUNDUP(PMT($O$6/12,24,-D13),0)</f>
+        <v>~9</v>
+      </c>
+      <c r="G13" s="66" t="str">
+        <f>"~"&amp;ROUNDUP(PMT($O$6/12,24,-E13),0)</f>
+        <v>~9</v>
+      </c>
+      <c r="H13" s="126" t="s">
         <v>12</v>
       </c>
-      <c r="L13" s="209"/>
-      <c r="M13" s="121"/>
-      <c r="N13" s="125">
+      <c r="I13" s="195">
+        <f>ROUNDUP(PMT($O$9/12,24,-$N$20),0)</f>
+        <v>9</v>
+      </c>
+      <c r="J13" s="196"/>
+      <c r="K13" s="191">
+        <f>ROUNDUP(PMT($O$9/12,24,-$O$20),0)</f>
+        <v>9</v>
+      </c>
+      <c r="L13" s="192"/>
+      <c r="M13" s="96"/>
+      <c r="O13" s="119">
         <v>0</v>
       </c>
-      <c r="O13" s="129">
-        <v>0</v>
-      </c>
-      <c r="P13" s="130"/>
-      <c r="Q13" s="174"/>
-      <c r="R13" s="175"/>
-      <c r="S13" s="175"/>
-      <c r="T13" s="175"/>
-      <c r="U13" s="175"/>
-      <c r="V13" s="176"/>
-      <c r="W13" s="118"/>
-      <c r="X13" s="119"/>
-      <c r="Y13" s="105"/>
-      <c r="Z13" s="105"/>
-      <c r="AA13" s="105"/>
+      <c r="P13" s="100"/>
+      <c r="Q13" s="154"/>
+      <c r="R13" s="155"/>
+      <c r="S13" s="155"/>
+      <c r="T13" s="155"/>
+      <c r="U13" s="155"/>
+      <c r="V13" s="156"/>
+      <c r="W13" s="93"/>
+      <c r="X13" s="94"/>
+      <c r="Y13" s="81"/>
     </row>
     <row r="14" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="12"/>
       <c r="B14" s="12"/>
-      <c r="C14" s="66" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" s="124">
-        <f>ROUNDUP($N$20*1.037,-1)</f>
-        <v>180</v>
-      </c>
-      <c r="E14" s="125">
-        <f>ROUNDUP($O$20*1.037,-1)</f>
-        <v>180</v>
-      </c>
-      <c r="F14" s="67">
-        <f>ROUNDUP(PMT($N$9/12,12,-D14),0)</f>
-        <v>17</v>
-      </c>
-      <c r="G14" s="78">
-        <f>ROUNDUP(PMT($N$9/12,12,-E14),0)</f>
-        <v>17</v>
-      </c>
-      <c r="H14" s="81" t="s">
-        <v>12</v>
-      </c>
-      <c r="I14" s="216">
-        <f>ROUNDUP(PMT($O$9/12,24,-$N$20),0)</f>
-        <v>9</v>
-      </c>
-      <c r="J14" s="217"/>
-      <c r="K14" s="208">
-        <f>ROUNDUP(PMT($O$9/12,24,-$O$20),0)</f>
-        <v>9</v>
-      </c>
-      <c r="L14" s="209"/>
-      <c r="M14" s="121"/>
-      <c r="N14" s="125">
+      <c r="C14" s="63" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="64">
+        <f>ROUNDUP($N$20/100*(100+O16),-1)</f>
+        <v>170</v>
+      </c>
+      <c r="E14" s="64">
+        <f>ROUNDUP($O$20/100*(100+O16),-1)</f>
+        <v>170</v>
+      </c>
+      <c r="F14" s="66" t="str">
+        <f>"~"&amp;ROUNDUP(PMT($O$6/12,36,-D14),0)</f>
+        <v>~7</v>
+      </c>
+      <c r="G14" s="66" t="str">
+        <f>"~"&amp;ROUNDUP(PMT($O$6/12,36,-E14),0)</f>
+        <v>~7</v>
+      </c>
+      <c r="H14" s="126" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="195">
+        <f>ROUNDUP(PMT($O$9/12,36,-$N$20),0)</f>
+        <v>7</v>
+      </c>
+      <c r="J14" s="196"/>
+      <c r="K14" s="191">
+        <f>ROUNDUP(PMT($O$9/12,36,-$O$20),0)</f>
+        <v>7</v>
+      </c>
+      <c r="L14" s="192"/>
+      <c r="M14" s="96"/>
+      <c r="O14" s="119">
         <v>0</v>
       </c>
-      <c r="O14" s="129">
-        <v>0</v>
-      </c>
-      <c r="P14" s="131"/>
-      <c r="Q14" s="174"/>
-      <c r="R14" s="175"/>
-      <c r="S14" s="175"/>
-      <c r="T14" s="175"/>
-      <c r="U14" s="175"/>
-      <c r="V14" s="176"/>
-      <c r="W14" s="118"/>
-      <c r="X14" s="119"/>
-      <c r="Y14" s="105"/>
-      <c r="Z14" s="105"/>
-      <c r="AA14" s="105"/>
+      <c r="P14" s="101"/>
+      <c r="Q14" s="154"/>
+      <c r="R14" s="155"/>
+      <c r="S14" s="155"/>
+      <c r="T14" s="155"/>
+      <c r="U14" s="155"/>
+      <c r="V14" s="156"/>
+      <c r="W14" s="93"/>
+      <c r="X14" s="94"/>
+      <c r="Y14" s="81"/>
     </row>
     <row r="15" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="12"/>
       <c r="B15" s="12"/>
-      <c r="C15" s="66" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" s="124">
-        <f>ROUNDUP($N$20*1.042,-1)</f>
-        <v>180</v>
-      </c>
-      <c r="E15" s="125">
-        <f>ROUNDUP($O$20*1.042,-1)</f>
-        <v>180</v>
-      </c>
-      <c r="F15" s="67">
-        <f>ROUNDUP(PMT($N$9/12,15,-D15),0)</f>
-        <v>14</v>
-      </c>
-      <c r="G15" s="78">
-        <f>ROUNDUP(PMT($N$9/12,15,-E15),0)</f>
-        <v>14</v>
-      </c>
-      <c r="H15" s="81" t="s">
-        <v>13</v>
-      </c>
-      <c r="I15" s="216">
-        <f>ROUNDUP(PMT($O$9/12,36,-$N$20),0)</f>
-        <v>7</v>
-      </c>
-      <c r="J15" s="217"/>
-      <c r="K15" s="208">
-        <f>ROUNDUP(PMT($O$9/12,36,-$O$20),0)</f>
-        <v>7</v>
-      </c>
-      <c r="L15" s="209"/>
-      <c r="M15" s="121"/>
-      <c r="N15" s="125">
+      <c r="C15" s="137" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" s="138"/>
+      <c r="E15" s="138"/>
+      <c r="F15" s="138"/>
+      <c r="G15" s="139"/>
+      <c r="H15" s="127" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="195">
+        <f>ROUNDUP(PMT($O$9/12,48,-$N$20),0)</f>
+        <v>5</v>
+      </c>
+      <c r="J15" s="196"/>
+      <c r="K15" s="191">
+        <f>ROUNDUP(PMT($O$9/12,48,-$O$20),0)</f>
+        <v>5</v>
+      </c>
+      <c r="L15" s="192"/>
+      <c r="M15" s="96"/>
+      <c r="O15" s="119">
         <v>0</v>
       </c>
-      <c r="O15" s="129">
-        <v>0</v>
-      </c>
       <c r="P15" s="10"/>
-      <c r="Q15" s="174"/>
-      <c r="R15" s="175"/>
-      <c r="S15" s="175"/>
-      <c r="T15" s="175"/>
-      <c r="U15" s="175"/>
-      <c r="V15" s="176"/>
-      <c r="W15" s="118"/>
-      <c r="X15" s="119"/>
-      <c r="Y15" s="105"/>
-      <c r="Z15" s="105"/>
-      <c r="AA15" s="105"/>
+      <c r="Q15" s="154"/>
+      <c r="R15" s="155"/>
+      <c r="S15" s="155"/>
+      <c r="T15" s="155"/>
+      <c r="U15" s="155"/>
+      <c r="V15" s="156"/>
+      <c r="W15" s="93"/>
+      <c r="X15" s="94"/>
+      <c r="Y15" s="81"/>
     </row>
     <row r="16" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="12"/>
       <c r="B16" s="12"/>
-      <c r="C16" s="66" t="s">
+      <c r="C16" s="115" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="150" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="151"/>
+      <c r="F16" s="150" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="151"/>
+      <c r="H16" s="224" t="s">
+        <v>45</v>
+      </c>
+      <c r="I16" s="224"/>
+      <c r="J16" s="225"/>
+      <c r="K16" s="202" t="s">
+        <v>17</v>
+      </c>
+      <c r="L16" s="202" t="s">
+        <v>16</v>
+      </c>
+      <c r="M16" s="96"/>
+      <c r="O16" s="130">
+        <v>0</v>
+      </c>
+      <c r="P16" s="101"/>
+      <c r="Q16" s="154"/>
+      <c r="R16" s="155"/>
+      <c r="S16" s="155"/>
+      <c r="T16" s="155"/>
+      <c r="U16" s="155"/>
+      <c r="V16" s="156"/>
+      <c r="W16" s="93"/>
+      <c r="X16" s="94"/>
+      <c r="Y16" s="81"/>
+    </row>
+    <row r="17" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="12"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="113" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="147">
+        <f>ROUNDUP(PMT($N$22/12,13,-$N$20),0)</f>
+        <v>15</v>
+      </c>
+      <c r="E17" s="148"/>
+      <c r="F17" s="147">
+        <f>ROUNDUP(PMT($N$22/12,13,-$O$20),0)</f>
+        <v>15</v>
+      </c>
+      <c r="G17" s="148"/>
+      <c r="H17" s="128" t="s">
+        <v>7</v>
+      </c>
+      <c r="I17" s="70" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="K17" s="203"/>
+      <c r="L17" s="203"/>
+      <c r="M17" s="96"/>
+      <c r="N17" s="73"/>
+      <c r="O17" s="73"/>
+      <c r="P17" s="10"/>
+      <c r="Q17" s="154"/>
+      <c r="R17" s="155"/>
+      <c r="S17" s="155"/>
+      <c r="T17" s="155"/>
+      <c r="U17" s="155"/>
+      <c r="V17" s="156"/>
+      <c r="W17" s="93"/>
+      <c r="X17" s="94"/>
+      <c r="Y17" s="81"/>
+    </row>
+    <row r="18" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="12"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="113" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="147">
+        <f>ROUNDUP(PMT($N$22/12,15,-$N$20),0)</f>
+        <v>13</v>
+      </c>
+      <c r="E18" s="148"/>
+      <c r="F18" s="147">
+        <f>ROUNDUP(PMT($N$22/12,15,-$O$20),0)</f>
+        <v>13</v>
+      </c>
+      <c r="G18" s="148"/>
+      <c r="H18" s="120" t="s">
+        <v>19</v>
+      </c>
+      <c r="I18" s="71">
+        <f>ROUNDUP($N$20/100*(100+O22),-1)</f>
+        <v>180</v>
+      </c>
+      <c r="J18" s="71">
+        <f>ROUNDUP($O$20/100*(100+O22),-1)</f>
+        <v>180</v>
+      </c>
+      <c r="K18" s="97">
+        <f>ROUNDUP(I18/4,0)</f>
+        <v>45</v>
+      </c>
+      <c r="L18" s="105">
+        <f>ROUNDUP(J18/4,0)</f>
+        <v>45</v>
+      </c>
+      <c r="M18" s="96"/>
+      <c r="N18" s="181" t="s">
+        <v>38</v>
+      </c>
+      <c r="O18" s="182"/>
+      <c r="P18" s="10"/>
+      <c r="Q18" s="154"/>
+      <c r="R18" s="155"/>
+      <c r="S18" s="155"/>
+      <c r="T18" s="155"/>
+      <c r="U18" s="155"/>
+      <c r="V18" s="156"/>
+      <c r="W18" s="93"/>
+      <c r="X18" s="94"/>
+    </row>
+    <row r="19" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="12"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="113" t="s">
         <v>11</v>
       </c>
-      <c r="D16" s="124">
+      <c r="D19" s="147">
+        <f>ROUNDUP(PMT($N$22/12,18,-$N$20),0)</f>
+        <v>11</v>
+      </c>
+      <c r="E19" s="148"/>
+      <c r="F19" s="147">
+        <f>ROUNDUP(PMT($N$22/12,18,-$O$20),0)</f>
+        <v>11</v>
+      </c>
+      <c r="G19" s="148"/>
+      <c r="H19" s="131" t="s">
+        <v>46</v>
+      </c>
+      <c r="I19" s="132">
+        <f>ROUNDUP($N$20/100*(100+O23),-1)</f>
+        <v>180</v>
+      </c>
+      <c r="J19" s="132">
+        <f>ROUNDUP($O$20/100*(100+O23),-1)</f>
+        <v>180</v>
+      </c>
+      <c r="K19" s="133">
+        <f>ROUNDUP(I19/5,0)</f>
+        <v>36</v>
+      </c>
+      <c r="L19" s="111">
+        <f>ROUNDUP(J19/5,0)</f>
+        <v>36</v>
+      </c>
+      <c r="M19" s="96"/>
+      <c r="N19" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="O19" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="P19" s="10"/>
+      <c r="Q19" s="154"/>
+      <c r="R19" s="155"/>
+      <c r="S19" s="155"/>
+      <c r="T19" s="155"/>
+      <c r="U19" s="155"/>
+      <c r="V19" s="156"/>
+      <c r="W19" s="93"/>
+      <c r="X19" s="94"/>
+    </row>
+    <row r="20" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="12"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="113" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" s="147">
+        <f>ROUNDUP(PMT($N$22/12,24,-$N$20),0)</f>
+        <v>9</v>
+      </c>
+      <c r="E20" s="148"/>
+      <c r="F20" s="147">
+        <f>ROUNDUP(PMT($N$22/12,24,-$O$20),0)</f>
+        <v>9</v>
+      </c>
+      <c r="G20" s="149"/>
+      <c r="H20" s="137" t="s">
+        <v>54</v>
+      </c>
+      <c r="I20" s="138"/>
+      <c r="J20" s="139"/>
+      <c r="K20" s="140" t="s">
+        <v>17</v>
+      </c>
+      <c r="L20" s="140" t="s">
+        <v>16</v>
+      </c>
+      <c r="M20" s="96"/>
+      <c r="N20" s="69">
+        <f>I4-K28</f>
+        <v>170</v>
+      </c>
+      <c r="O20" s="69">
+        <f>J4-K28</f>
+        <v>170</v>
+      </c>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="154"/>
+      <c r="R20" s="155"/>
+      <c r="S20" s="155"/>
+      <c r="T20" s="155"/>
+      <c r="U20" s="155"/>
+      <c r="V20" s="156"/>
+      <c r="W20" s="93"/>
+      <c r="X20" s="94"/>
+    </row>
+    <row r="21" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="12"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="113" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="147">
+        <f>ROUNDUP(PMT($N$22/12,36,-$N$20),0)</f>
+        <v>7</v>
+      </c>
+      <c r="E21" s="148"/>
+      <c r="F21" s="147">
+        <f>ROUNDUP(PMT($N$22/12,36,-$O$20),0)</f>
+        <v>7</v>
+      </c>
+      <c r="G21" s="149"/>
+      <c r="H21" s="134" t="s">
+        <v>7</v>
+      </c>
+      <c r="I21" s="122" t="s">
+        <v>15</v>
+      </c>
+      <c r="J21" s="123" t="s">
+        <v>14</v>
+      </c>
+      <c r="K21" s="141"/>
+      <c r="L21" s="141"/>
+      <c r="M21" s="96"/>
+      <c r="N21" s="116" t="s">
+        <v>53</v>
+      </c>
+      <c r="O21" s="112" t="s">
+        <v>47</v>
+      </c>
+      <c r="P21" s="103"/>
+      <c r="Q21" s="154"/>
+      <c r="R21" s="155"/>
+      <c r="S21" s="155"/>
+      <c r="T21" s="155"/>
+      <c r="U21" s="155"/>
+      <c r="V21" s="156"/>
+      <c r="W21" s="93"/>
+      <c r="X21" s="94"/>
+    </row>
+    <row r="22" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="12"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="114" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="147">
+        <f>ROUNDUP(PMT($N$22/12,48,-$N$20),0)</f>
+        <v>5</v>
+      </c>
+      <c r="E22" s="148"/>
+      <c r="F22" s="147">
+        <f>ROUNDUP(PMT($N$22/12,48,-$O$20),0)</f>
+        <v>5</v>
+      </c>
+      <c r="G22" s="149"/>
+      <c r="H22" s="135" t="s">
+        <v>12</v>
+      </c>
+      <c r="I22" s="119">
         <f>ROUNDUP($N$20*1.042,-1)</f>
         <v>180</v>
       </c>
-      <c r="E16" s="125">
+      <c r="J22" s="119">
         <f>ROUNDUP($O$20*1.042,-1)</f>
         <v>180</v>
       </c>
-      <c r="F16" s="67">
-        <f>ROUNDUP(PMT($N$9/12,18,-D16),0)</f>
-        <v>12</v>
-      </c>
-      <c r="G16" s="78">
-        <f>ROUNDUP(PMT($N$9/12,18,-E16),0)</f>
-        <v>12</v>
-      </c>
-      <c r="H16" s="82" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="229">
-        <f>ROUNDUP(PMT($O$9/12,48,-$N$20),0)</f>
-        <v>6</v>
-      </c>
-      <c r="J16" s="230"/>
-      <c r="K16" s="210">
-        <f>ROUNDUP(PMT($O$9/12,48,-$O$20),0)</f>
-        <v>6</v>
-      </c>
-      <c r="L16" s="211"/>
-      <c r="M16" s="121"/>
-      <c r="N16" s="125">
-        <v>0</v>
-      </c>
-      <c r="O16" s="129">
-        <v>0</v>
-      </c>
-      <c r="P16" s="131"/>
-      <c r="Q16" s="174"/>
-      <c r="R16" s="175"/>
-      <c r="S16" s="175"/>
-      <c r="T16" s="175"/>
-      <c r="U16" s="175"/>
-      <c r="V16" s="176"/>
-      <c r="W16" s="118"/>
-      <c r="X16" s="119"/>
-      <c r="Y16" s="105"/>
-      <c r="Z16" s="105"/>
-      <c r="AA16" s="105"/>
-    </row>
-    <row r="17" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="12"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="66" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" s="124">
+      <c r="K22" s="121" t="str">
+        <f>"&lt; "&amp;ROUNDUP(PMT($N$22/12,24,-I22),0)</f>
+        <v>&lt; 9</v>
+      </c>
+      <c r="L22" s="121" t="str">
+        <f>"&lt; "&amp;ROUNDUP(PMT($N$22/12,24,-J22),0)</f>
+        <v>&lt; 9</v>
+      </c>
+      <c r="M22" s="96"/>
+      <c r="N22" s="142">
+        <v>0.17710000000000001</v>
+      </c>
+      <c r="O22" s="119">
+        <v>4.2</v>
+      </c>
+      <c r="P22" s="104"/>
+      <c r="Q22" s="154"/>
+      <c r="R22" s="155"/>
+      <c r="S22" s="155"/>
+      <c r="T22" s="155"/>
+      <c r="U22" s="155"/>
+      <c r="V22" s="156"/>
+      <c r="W22" s="93"/>
+      <c r="X22" s="94"/>
+    </row>
+    <row r="23" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="12"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="114" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" s="144">
+        <f>ROUNDUP(PMT($N$22/12,60,-$N$20),0)</f>
+        <v>5</v>
+      </c>
+      <c r="E23" s="145"/>
+      <c r="F23" s="144">
+        <f>ROUNDUP(PMT($N$22/12,60,-$O$20),0)</f>
+        <v>5</v>
+      </c>
+      <c r="G23" s="146"/>
+      <c r="H23" s="113" t="s">
+        <v>13</v>
+      </c>
+      <c r="I23" s="119">
         <f>ROUNDUP($N$20*1.042,-1)</f>
         <v>180</v>
       </c>
-      <c r="E17" s="125">
+      <c r="J23" s="119">
         <f>ROUNDUP($O$20*1.042,-1)</f>
         <v>180</v>
       </c>
-      <c r="F17" s="67">
-        <f>ROUNDUP(PMT($N$9/12,24,-D17),0)</f>
-        <v>9</v>
-      </c>
-      <c r="G17" s="78">
-        <f>ROUNDUP(PMT($N$9/12,24,-E17),0)</f>
-        <v>9</v>
-      </c>
-      <c r="H17" s="224" t="s">
-        <v>51</v>
-      </c>
-      <c r="I17" s="225"/>
-      <c r="J17" s="226"/>
-      <c r="K17" s="212" t="s">
+      <c r="K23" s="121" t="str">
+        <f>"&lt; "&amp;ROUNDUP(PMT($N$22/12,36,-I23),0)</f>
+        <v>&lt; 7</v>
+      </c>
+      <c r="L23" s="121" t="str">
+        <f>"&lt; "&amp;ROUNDUP(PMT($N$22/12,36,-J23),0)</f>
+        <v>&lt; 7</v>
+      </c>
+      <c r="M23" s="96"/>
+      <c r="N23" s="143"/>
+      <c r="O23" s="102">
+        <v>5.3</v>
+      </c>
+      <c r="P23" s="104"/>
+      <c r="Q23" s="154"/>
+      <c r="R23" s="155"/>
+      <c r="S23" s="155"/>
+      <c r="T23" s="155"/>
+      <c r="U23" s="155"/>
+      <c r="V23" s="156"/>
+      <c r="W23" s="93"/>
+      <c r="X23" s="94"/>
+    </row>
+    <row r="24" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="12"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="319" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" s="320"/>
+      <c r="E24" s="321"/>
+      <c r="F24" s="322" t="s">
         <v>17</v>
       </c>
-      <c r="L17" s="212" t="s">
+      <c r="G24" s="322" t="s">
         <v>16</v>
       </c>
-      <c r="M17" s="121"/>
-      <c r="N17" s="93"/>
-      <c r="O17" s="144">
-        <v>0</v>
-      </c>
-      <c r="P17" s="10"/>
-      <c r="Q17" s="174"/>
-      <c r="R17" s="175"/>
-      <c r="S17" s="175"/>
-      <c r="T17" s="175"/>
-      <c r="U17" s="175"/>
-      <c r="V17" s="176"/>
-      <c r="W17" s="118"/>
-      <c r="X17" s="119"/>
-      <c r="Y17" s="105"/>
-      <c r="Z17" s="105"/>
-      <c r="AA17" s="105"/>
-    </row>
-    <row r="18" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="12"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="66" t="s">
-        <v>13</v>
-      </c>
-      <c r="D18" s="124">
+      <c r="H24" s="113" t="s">
+        <v>32</v>
+      </c>
+      <c r="I24" s="119">
         <f>ROUNDUP($N$20*1.042,-1)</f>
         <v>180</v>
       </c>
-      <c r="E18" s="125">
+      <c r="J24" s="119">
         <f>ROUNDUP($O$20*1.042,-1)</f>
         <v>180</v>
       </c>
-      <c r="F18" s="67">
-        <f>ROUNDUP(PMT($N$9/12,36,-D18),0)</f>
+      <c r="K24" s="121" t="str">
+        <f>"&lt; "&amp;ROUNDUP(PMT($N$22/12,48,-I24),0)</f>
+        <v>&lt; 6</v>
+      </c>
+      <c r="L24" s="121" t="str">
+        <f>"&lt; "&amp;ROUNDUP(PMT($N$22/12,48,-J24),0)</f>
+        <v>&lt; 6</v>
+      </c>
+      <c r="M24" s="96"/>
+      <c r="N24" s="316" t="s">
+        <v>55</v>
+      </c>
+      <c r="O24" s="96"/>
+      <c r="P24" s="104"/>
+      <c r="Q24" s="197"/>
+      <c r="R24" s="198"/>
+      <c r="S24" s="198"/>
+      <c r="T24" s="198"/>
+      <c r="U24" s="198"/>
+      <c r="V24" s="199"/>
+      <c r="W24" s="93"/>
+      <c r="X24" s="94"/>
+    </row>
+    <row r="25" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="12"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="323" t="s">
         <v>7</v>
       </c>
-      <c r="G18" s="78">
-        <f>ROUNDUP(PMT($N$9/12,36,-E18),0)</f>
-        <v>7</v>
-      </c>
-      <c r="H18" s="90" t="s">
-        <v>7</v>
-      </c>
-      <c r="I18" s="89" t="s">
+      <c r="D25" s="324" t="s">
         <v>21</v>
       </c>
-      <c r="J18" s="89" t="s">
+      <c r="E25" s="324" t="s">
         <v>22</v>
       </c>
-      <c r="K18" s="213"/>
-      <c r="L18" s="213"/>
-      <c r="M18" s="121"/>
-      <c r="N18" s="190" t="s">
-        <v>41</v>
-      </c>
-      <c r="O18" s="191"/>
-      <c r="P18" s="10"/>
-      <c r="Q18" s="174"/>
-      <c r="R18" s="175"/>
-      <c r="S18" s="175"/>
-      <c r="T18" s="175"/>
-      <c r="U18" s="175"/>
-      <c r="V18" s="176"/>
-      <c r="W18" s="118"/>
-      <c r="X18" s="119"/>
-      <c r="Z18" s="105"/>
-    </row>
-    <row r="19" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="68" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" s="134">
+      <c r="F25" s="325"/>
+      <c r="G25" s="325"/>
+      <c r="H25" s="114" t="s">
+        <v>39</v>
+      </c>
+      <c r="I25" s="130">
         <f>ROUNDUP($N$20*1.042,-1)</f>
         <v>180</v>
       </c>
-      <c r="E19" s="132">
+      <c r="J25" s="130">
         <f>ROUNDUP($O$20*1.042,-1)</f>
         <v>180</v>
       </c>
-      <c r="F19" s="83">
-        <f>ROUNDUP(PMT($N$9/12,48,-D19),0)</f>
-        <v>6</v>
-      </c>
-      <c r="G19" s="84">
-        <f>ROUNDUP(PMT($N$9/12,48,-E19),0)</f>
-        <v>6</v>
-      </c>
-      <c r="H19" s="64" t="s">
-        <v>19</v>
-      </c>
-      <c r="I19" s="91">
-        <f>ROUNDUP($N$20/100*(100+O22),-1)</f>
-        <v>180</v>
-      </c>
-      <c r="J19" s="91">
-        <f>ROUNDUP($O$20/100*(100+O22),-1)</f>
-        <v>180</v>
-      </c>
-      <c r="K19" s="125">
-        <f>ROUNDUP(I19/4,0)</f>
-        <v>45</v>
-      </c>
-      <c r="L19" s="137">
-        <f>ROUNDUP(J19/4,0)</f>
-        <v>45</v>
-      </c>
-      <c r="M19" s="121"/>
-      <c r="N19" s="85" t="s">
-        <v>21</v>
-      </c>
-      <c r="O19" s="85" t="s">
-        <v>22</v>
-      </c>
-      <c r="P19" s="10"/>
-      <c r="Q19" s="174"/>
-      <c r="R19" s="175"/>
-      <c r="S19" s="175"/>
-      <c r="T19" s="175"/>
-      <c r="U19" s="175"/>
-      <c r="V19" s="176"/>
-      <c r="W19" s="118"/>
-      <c r="X19" s="119"/>
-      <c r="Z19" s="105"/>
-    </row>
-    <row r="20" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="221" t="s">
-        <v>46</v>
-      </c>
-      <c r="D20" s="222"/>
-      <c r="E20" s="223"/>
-      <c r="F20" s="227" t="s">
-        <v>17</v>
-      </c>
-      <c r="G20" s="227" t="s">
-        <v>16</v>
-      </c>
-      <c r="H20" s="68" t="s">
-        <v>52</v>
-      </c>
-      <c r="I20" s="71">
-        <f>ROUNDUP($N$20/100*(100+O23),-1)</f>
-        <v>180</v>
-      </c>
-      <c r="J20" s="71">
-        <f>ROUNDUP($O$20/100*(100+O23),-1)</f>
-        <v>180</v>
-      </c>
-      <c r="K20" s="138">
-        <f>ROUNDUP(I20/5,0)</f>
-        <v>36</v>
-      </c>
-      <c r="L20" s="133">
-        <f>ROUNDUP(J20/5,0)</f>
-        <v>36</v>
-      </c>
-      <c r="M20" s="121"/>
-      <c r="N20" s="86">
-        <f>I4-E37</f>
-        <v>170</v>
-      </c>
-      <c r="O20" s="86">
-        <f>J4-E37</f>
-        <v>170</v>
-      </c>
-      <c r="P20" s="10"/>
-      <c r="Q20" s="174"/>
-      <c r="R20" s="175"/>
-      <c r="S20" s="175"/>
-      <c r="T20" s="175"/>
-      <c r="U20" s="175"/>
-      <c r="V20" s="176"/>
-      <c r="W20" s="118"/>
-      <c r="X20" s="119"/>
-      <c r="Z20" s="105"/>
-    </row>
-    <row r="21" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="76" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" s="92" t="s">
-        <v>21</v>
-      </c>
-      <c r="E21" s="92" t="s">
-        <v>22</v>
-      </c>
-      <c r="F21" s="228"/>
-      <c r="G21" s="228"/>
-      <c r="H21" s="218" t="s">
-        <v>47</v>
-      </c>
-      <c r="I21" s="219"/>
-      <c r="J21" s="220"/>
-      <c r="K21" s="266" t="s">
-        <v>17</v>
-      </c>
-      <c r="L21" s="266" t="s">
-        <v>16</v>
-      </c>
-      <c r="M21" s="121"/>
-      <c r="N21" s="149" t="s">
-        <v>60</v>
-      </c>
-      <c r="O21" s="145" t="s">
-        <v>53</v>
-      </c>
-      <c r="P21" s="135"/>
-      <c r="Q21" s="174"/>
-      <c r="R21" s="175"/>
-      <c r="S21" s="175"/>
-      <c r="T21" s="175"/>
-      <c r="U21" s="175"/>
-      <c r="V21" s="176"/>
-      <c r="W21" s="118"/>
-      <c r="X21" s="119"/>
-      <c r="Z21" s="105"/>
-    </row>
-    <row r="22" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="12"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="91">
-        <f>ROUNDUP($N$20/100*(100+N12),-1)</f>
-        <v>170</v>
-      </c>
-      <c r="E22" s="91">
-        <f>ROUNDUP($O$20/100*(100+N12),-1)</f>
-        <v>170</v>
-      </c>
-      <c r="F22" s="72" t="str">
-        <f>"~"&amp;ROUNDUP(PMT($N$6/12,6,-D22),0)</f>
-        <v>~31</v>
-      </c>
-      <c r="G22" s="72" t="str">
-        <f>"~"&amp;ROUNDUP(PMT($N$6/12,6,-E22),0)</f>
-        <v>~31</v>
-      </c>
-      <c r="H22" s="99" t="s">
-        <v>7</v>
-      </c>
-      <c r="I22" s="100" t="s">
-        <v>21</v>
-      </c>
-      <c r="J22" s="100" t="s">
-        <v>22</v>
-      </c>
-      <c r="K22" s="267"/>
-      <c r="L22" s="267"/>
-      <c r="M22" s="121"/>
-      <c r="N22" s="166">
-        <v>0.14599999999999999</v>
-      </c>
-      <c r="O22" s="124">
-        <v>4.2</v>
-      </c>
-      <c r="P22" s="136"/>
-      <c r="Q22" s="174"/>
-      <c r="R22" s="175"/>
-      <c r="S22" s="175"/>
-      <c r="T22" s="175"/>
-      <c r="U22" s="175"/>
-      <c r="V22" s="176"/>
-      <c r="W22" s="118"/>
-      <c r="X22" s="119"/>
-      <c r="Z22" s="105"/>
-    </row>
-    <row r="23" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="12"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="69" t="s">
-        <v>10</v>
-      </c>
-      <c r="D23" s="70">
-        <f>ROUNDUP($N$20/100*(100+N13),-1)</f>
-        <v>170</v>
-      </c>
-      <c r="E23" s="70">
-        <f>ROUNDUP($O$20/100*(100+N13),-1)</f>
-        <v>170</v>
-      </c>
-      <c r="F23" s="73" t="str">
-        <f>"~"&amp;ROUNDUP(PMT($N$6/12,12,-D23),0)</f>
-        <v>~16</v>
-      </c>
-      <c r="G23" s="73" t="str">
-        <f>"~"&amp;ROUNDUP(PMT($N$6/12,12,-E23),0)</f>
-        <v>~16</v>
-      </c>
-      <c r="H23" s="98" t="s">
-        <v>9</v>
-      </c>
-      <c r="I23" s="91">
-        <f t="shared" ref="I23:I28" si="0">ROUNDUP($N$20/100*(100+O12),-1)</f>
-        <v>170</v>
-      </c>
-      <c r="J23" s="91">
-        <f t="shared" ref="J23:J28" si="1">ROUNDUP($O$20/100*(100+O12),-1)</f>
-        <v>170</v>
-      </c>
-      <c r="K23" s="72" t="str">
-        <f>"~"&amp;ROUNDUP(PMT($O$6/12,6,-I23),0)</f>
-        <v>~31</v>
-      </c>
-      <c r="L23" s="72" t="str">
-        <f>"~"&amp;ROUNDUP(PMT($O$6/12,6,-J23),0)</f>
-        <v>~31</v>
-      </c>
-      <c r="M23" s="121"/>
-      <c r="N23" s="167"/>
-      <c r="O23" s="133">
-        <v>5.3</v>
-      </c>
-      <c r="P23" s="136"/>
-      <c r="Q23" s="174"/>
-      <c r="R23" s="175"/>
-      <c r="S23" s="175"/>
-      <c r="T23" s="175"/>
-      <c r="U23" s="175"/>
-      <c r="V23" s="176"/>
-      <c r="W23" s="118"/>
-      <c r="X23" s="119"/>
-      <c r="Z23" s="105"/>
-    </row>
-    <row r="24" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="12"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="69" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" s="70">
-        <f>ROUNDUP($N$20/100*(100+N14),-1)</f>
-        <v>170</v>
-      </c>
-      <c r="E24" s="70">
-        <f>ROUNDUP($O$20/100*(100+N14),-1)</f>
-        <v>170</v>
-      </c>
-      <c r="F24" s="73" t="str">
-        <f>"~"&amp;ROUNDUP(PMT($N$6/12,18,-D24),0)</f>
-        <v>~12</v>
-      </c>
-      <c r="G24" s="79" t="str">
-        <f>"~"&amp;ROUNDUP(PMT($N$6/12,18,-E24),0)</f>
-        <v>~12</v>
-      </c>
-      <c r="H24" s="69" t="s">
-        <v>10</v>
-      </c>
-      <c r="I24" s="70">
-        <f t="shared" si="0"/>
-        <v>170</v>
-      </c>
-      <c r="J24" s="70">
-        <f t="shared" si="1"/>
-        <v>170</v>
-      </c>
-      <c r="K24" s="73" t="str">
-        <f>"~"&amp;ROUNDUP(PMT($O$6/12,12,-I24),0)</f>
-        <v>~16</v>
-      </c>
-      <c r="L24" s="73" t="str">
-        <f>"~"&amp;ROUNDUP(PMT($O$6/12,12,-J24),0)</f>
-        <v>~16</v>
-      </c>
-      <c r="M24" s="121"/>
-      <c r="N24" s="94"/>
-      <c r="O24" s="121"/>
-      <c r="P24" s="136"/>
-      <c r="Q24" s="261"/>
-      <c r="R24" s="262"/>
-      <c r="S24" s="262"/>
-      <c r="T24" s="262"/>
-      <c r="U24" s="262"/>
-      <c r="V24" s="263"/>
-      <c r="W24" s="118"/>
-      <c r="X24" s="119"/>
-      <c r="Z24" s="105"/>
-    </row>
-    <row r="25" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="12"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="69" t="s">
-        <v>12</v>
-      </c>
-      <c r="D25" s="70">
-        <f>ROUNDUP($N$20/100*(100+N15),-1)</f>
-        <v>170</v>
-      </c>
-      <c r="E25" s="70">
-        <f>ROUNDUP($O$20/100*(100+N15),-1)</f>
-        <v>170</v>
-      </c>
-      <c r="F25" s="73" t="str">
-        <f>"~"&amp;ROUNDUP(PMT($N$6/12,24,-D25),0)</f>
-        <v>~9</v>
-      </c>
-      <c r="G25" s="79" t="str">
-        <f>"~"&amp;ROUNDUP(PMT($N$6/12,24,-E25),0)</f>
-        <v>~9</v>
-      </c>
-      <c r="H25" s="69" t="s">
-        <v>11</v>
-      </c>
-      <c r="I25" s="70">
-        <f t="shared" si="0"/>
-        <v>170</v>
-      </c>
-      <c r="J25" s="70">
-        <f t="shared" si="1"/>
-        <v>170</v>
-      </c>
-      <c r="K25" s="73" t="str">
-        <f>"~"&amp;ROUNDUP(PMT($O$6/12,18,-I25),0)</f>
-        <v>~12</v>
-      </c>
-      <c r="L25" s="73" t="str">
-        <f>"~"&amp;ROUNDUP(PMT($O$6/12,18,-J25),0)</f>
-        <v>~12</v>
-      </c>
-      <c r="M25" s="121"/>
-      <c r="N25" s="94"/>
-      <c r="O25" s="121"/>
-      <c r="Q25" s="174"/>
-      <c r="R25" s="175"/>
-      <c r="S25" s="175"/>
-      <c r="T25" s="175"/>
-      <c r="U25" s="175"/>
-      <c r="V25" s="176"/>
-      <c r="W25" s="118"/>
-      <c r="X25" s="119"/>
-      <c r="Z25" s="105"/>
-    </row>
-    <row r="26" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K25" s="136" t="str">
+        <f>"&lt; "&amp;ROUNDUP(PMT($N$22/12,60,-I25),0)</f>
+        <v>&lt; 5</v>
+      </c>
+      <c r="L25" s="136" t="str">
+        <f>"&lt; "&amp;ROUNDUP(PMT($N$22/12,60,-J25),0)</f>
+        <v>&lt; 5</v>
+      </c>
+      <c r="M25" s="96"/>
+      <c r="N25" s="326">
+        <v>0.19989999999999999</v>
+      </c>
+      <c r="O25" s="96"/>
+      <c r="Q25" s="154"/>
+      <c r="R25" s="155"/>
+      <c r="S25" s="155"/>
+      <c r="T25" s="155"/>
+      <c r="U25" s="155"/>
+      <c r="V25" s="156"/>
+      <c r="W25" s="93"/>
+      <c r="X25" s="94"/>
+    </row>
+    <row r="26" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="12"/>
       <c r="B26" s="12"/>
-      <c r="C26" s="69" t="s">
-        <v>13</v>
-      </c>
-      <c r="D26" s="70">
-        <f>ROUNDUP($N$20/100*(100+N16),-1)</f>
-        <v>170</v>
-      </c>
-      <c r="E26" s="70">
-        <f>ROUNDUP($O$20/100*(100+N16),-1)</f>
-        <v>170</v>
-      </c>
-      <c r="F26" s="73" t="str">
-        <f>"~"&amp;ROUNDUP(PMT($N$6/12,36,-D26),0)</f>
-        <v>~7</v>
-      </c>
-      <c r="G26" s="79" t="str">
-        <f>"~"&amp;ROUNDUP(PMT($N$6/12,36,-E26),0)</f>
-        <v>~7</v>
-      </c>
-      <c r="H26" s="69" t="s">
-        <v>12</v>
-      </c>
-      <c r="I26" s="70">
-        <f t="shared" si="0"/>
-        <v>170</v>
-      </c>
-      <c r="J26" s="70">
-        <f t="shared" si="1"/>
-        <v>170</v>
-      </c>
-      <c r="K26" s="73" t="str">
-        <f>"~"&amp;ROUNDUP(PMT($O$6/12,24,-I26),0)</f>
-        <v>~9</v>
-      </c>
-      <c r="L26" s="73" t="str">
-        <f>"~"&amp;ROUNDUP(PMT($O$6/12,24,-J26),0)</f>
-        <v>~9</v>
-      </c>
-      <c r="M26" s="121"/>
-      <c r="N26" s="94"/>
-      <c r="O26" s="121"/>
-      <c r="Q26" s="174"/>
-      <c r="R26" s="175"/>
-      <c r="S26" s="175"/>
-      <c r="T26" s="175"/>
-      <c r="U26" s="175"/>
-      <c r="V26" s="176"/>
-      <c r="W26" s="118"/>
-      <c r="X26" s="119"/>
-      <c r="Z26" s="105"/>
-    </row>
-    <row r="27" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C26" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="71">
+        <f>ROUNDUP($N$20/100*(100+$N$27),-1)</f>
+        <v>180</v>
+      </c>
+      <c r="E26" s="71">
+        <f>ROUNDUP($O$20/100*(100+$N$27),-1)</f>
+        <v>180</v>
+      </c>
+      <c r="F26" s="65" t="str">
+        <f>"~"&amp;ROUNDUP(PMT($N$25/12,6,-D26),0)</f>
+        <v>~32</v>
+      </c>
+      <c r="G26" s="65" t="str">
+        <f>"~"&amp;ROUNDUP(PMT($N$25/12,6,-E26),0)</f>
+        <v>~32</v>
+      </c>
+      <c r="H26" s="74"/>
+      <c r="I26" s="75"/>
+      <c r="J26" s="75"/>
+      <c r="K26" s="76"/>
+      <c r="L26" s="76"/>
+      <c r="M26" s="96"/>
+      <c r="N26" s="317" t="s">
+        <v>56</v>
+      </c>
+      <c r="O26" s="96"/>
+      <c r="Q26" s="154"/>
+      <c r="R26" s="155"/>
+      <c r="S26" s="155"/>
+      <c r="T26" s="155"/>
+      <c r="U26" s="155"/>
+      <c r="V26" s="156"/>
+      <c r="W26" s="93"/>
+      <c r="X26" s="94"/>
+    </row>
+    <row r="27" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="12"/>
       <c r="B27" s="12"/>
-      <c r="C27" s="161" t="s">
-        <v>58</v>
-      </c>
-      <c r="D27" s="162"/>
-      <c r="E27" s="162"/>
-      <c r="F27" s="162"/>
-      <c r="G27" s="163"/>
-      <c r="H27" s="69" t="s">
-        <v>13</v>
-      </c>
-      <c r="I27" s="70">
-        <f t="shared" si="0"/>
-        <v>170</v>
-      </c>
-      <c r="J27" s="70">
-        <f t="shared" si="1"/>
-        <v>170</v>
-      </c>
-      <c r="K27" s="73" t="str">
-        <f>"~"&amp;ROUNDUP(PMT($O$6/12,36,-I27),0)</f>
-        <v>~7</v>
-      </c>
-      <c r="L27" s="73" t="str">
-        <f>"~"&amp;ROUNDUP(PMT($O$6/12,36,-J27),0)</f>
-        <v>~7</v>
-      </c>
-      <c r="M27" s="121"/>
-      <c r="N27" s="121"/>
-      <c r="O27" s="121"/>
-      <c r="Q27" s="174"/>
-      <c r="R27" s="175"/>
-      <c r="S27" s="175"/>
-      <c r="T27" s="175"/>
-      <c r="U27" s="175"/>
-      <c r="V27" s="176"/>
-      <c r="W27" s="118"/>
-      <c r="X27" s="119"/>
-      <c r="Z27" s="105"/>
-    </row>
-    <row r="28" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C27" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="71">
+        <f t="shared" ref="D27:E32" si="0">ROUNDUP($N$20/100*(100+$N$27),-1)</f>
+        <v>180</v>
+      </c>
+      <c r="E27" s="71">
+        <f t="shared" ref="E27:E32" si="1">ROUNDUP($O$20/100*(100+$N$27),-1)</f>
+        <v>180</v>
+      </c>
+      <c r="F27" s="65" t="str">
+        <f>"~"&amp;ROUNDUP(PMT($N$25/12,12,-D27),0)</f>
+        <v>~17</v>
+      </c>
+      <c r="G27" s="65" t="str">
+        <f>"~"&amp;ROUNDUP(PMT($N$25/12,12,-E27),0)</f>
+        <v>~17</v>
+      </c>
+      <c r="H27" s="74"/>
+      <c r="I27" s="75"/>
+      <c r="J27" s="75"/>
+      <c r="K27" s="76"/>
+      <c r="L27" s="76"/>
+      <c r="M27" s="96"/>
+      <c r="N27" s="318">
+        <v>3</v>
+      </c>
+      <c r="O27" s="96"/>
+      <c r="Q27" s="154"/>
+      <c r="R27" s="155"/>
+      <c r="S27" s="155"/>
+      <c r="T27" s="155"/>
+      <c r="U27" s="155"/>
+      <c r="V27" s="156"/>
+      <c r="W27" s="93"/>
+      <c r="X27" s="94"/>
+      <c r="Z27" s="81"/>
+    </row>
+    <row r="28" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="12"/>
       <c r="B28" s="12"/>
-      <c r="C28" s="148" t="s">
-        <v>7</v>
-      </c>
-      <c r="D28" s="170" t="s">
-        <v>17</v>
-      </c>
-      <c r="E28" s="171"/>
-      <c r="F28" s="170" t="s">
-        <v>16</v>
-      </c>
-      <c r="G28" s="171"/>
-      <c r="H28" s="75" t="s">
-        <v>43</v>
-      </c>
-      <c r="I28" s="71">
+      <c r="C28" s="63" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="71">
         <f t="shared" si="0"/>
-        <v>170</v>
-      </c>
-      <c r="J28" s="71">
+        <v>180</v>
+      </c>
+      <c r="E28" s="71">
         <f t="shared" si="1"/>
-        <v>170</v>
-      </c>
-      <c r="K28" s="74" t="str">
-        <f>"~"&amp;ROUNDUP(PMT($O$6/12,60,-I28),0)</f>
-        <v>~5</v>
-      </c>
-      <c r="L28" s="74" t="str">
-        <f>"~"&amp;ROUNDUP(PMT($O$6/12,60,-J28),0)</f>
-        <v>~5</v>
-      </c>
-      <c r="M28" s="121"/>
-      <c r="N28" s="121"/>
-      <c r="O28" s="121"/>
-      <c r="Q28" s="174"/>
-      <c r="R28" s="175"/>
-      <c r="S28" s="175"/>
-      <c r="T28" s="175"/>
-      <c r="U28" s="175"/>
-      <c r="V28" s="176"/>
-      <c r="W28" s="118"/>
-      <c r="X28" s="119"/>
-      <c r="Z28" s="105"/>
-    </row>
-    <row r="29" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>180</v>
+      </c>
+      <c r="F28" s="65" t="str">
+        <f>"~"&amp;ROUNDUP(PMT($N$25/12,18,-D28),0)</f>
+        <v>~12</v>
+      </c>
+      <c r="G28" s="65" t="str">
+        <f>"~"&amp;ROUNDUP(PMT($N$25/12,18,-E28),0)</f>
+        <v>~12</v>
+      </c>
+      <c r="I28" s="213" t="s">
+        <v>33</v>
+      </c>
+      <c r="J28" s="214"/>
+      <c r="K28" s="217">
+        <v>0</v>
+      </c>
+      <c r="L28" s="218"/>
+      <c r="M28" s="96"/>
+      <c r="N28" s="73"/>
+      <c r="O28" s="96"/>
+      <c r="Q28" s="154"/>
+      <c r="R28" s="155"/>
+      <c r="S28" s="155"/>
+      <c r="T28" s="155"/>
+      <c r="U28" s="155"/>
+      <c r="V28" s="156"/>
+      <c r="W28" s="93"/>
+      <c r="X28" s="94"/>
+      <c r="Z28" s="81"/>
+    </row>
+    <row r="29" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="12"/>
       <c r="B29" s="12"/>
-      <c r="C29" s="146" t="s">
-        <v>59</v>
-      </c>
-      <c r="D29" s="168">
-        <f>ROUNDUP(PMT($N$22/12,13,-$N$20),0)</f>
-        <v>15</v>
-      </c>
-      <c r="E29" s="169"/>
-      <c r="F29" s="168">
-        <f>ROUNDUP(PMT($N$22/12,13,-$O$20),0)</f>
-        <v>15</v>
-      </c>
-      <c r="G29" s="169"/>
-      <c r="H29" s="161" t="s">
-        <v>61</v>
-      </c>
-      <c r="I29" s="162"/>
-      <c r="J29" s="163"/>
-      <c r="K29" s="164" t="s">
-        <v>17</v>
-      </c>
-      <c r="L29" s="164" t="s">
-        <v>16</v>
-      </c>
-      <c r="M29" s="139"/>
-      <c r="N29" s="139"/>
-      <c r="O29" s="139"/>
+      <c r="C29" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" s="71">
+        <f t="shared" si="0"/>
+        <v>180</v>
+      </c>
+      <c r="E29" s="71">
+        <f t="shared" si="1"/>
+        <v>180</v>
+      </c>
+      <c r="F29" s="65" t="str">
+        <f>"~"&amp;ROUNDUP(PMT($N$25/12,24,-D29),0)</f>
+        <v>~10</v>
+      </c>
+      <c r="G29" s="65" t="str">
+        <f>"~"&amp;ROUNDUP(PMT($N$25/12,24,-E29),0)</f>
+        <v>~10</v>
+      </c>
+      <c r="I29" s="215"/>
+      <c r="J29" s="216"/>
+      <c r="K29" s="219"/>
+      <c r="L29" s="220"/>
+      <c r="M29" s="106"/>
+      <c r="N29" s="106"/>
+      <c r="O29" s="106"/>
       <c r="P29" s="12"/>
-      <c r="Q29" s="174"/>
-      <c r="R29" s="175"/>
-      <c r="S29" s="175"/>
-      <c r="T29" s="175"/>
-      <c r="U29" s="175"/>
-      <c r="V29" s="176"/>
-      <c r="W29" s="118"/>
-      <c r="X29" s="119"/>
-      <c r="Z29" s="105"/>
-    </row>
-    <row r="30" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q29" s="154"/>
+      <c r="R29" s="155"/>
+      <c r="S29" s="155"/>
+      <c r="T29" s="155"/>
+      <c r="U29" s="155"/>
+      <c r="V29" s="156"/>
+      <c r="W29" s="93"/>
+      <c r="X29" s="94"/>
+      <c r="Z29" s="81"/>
+    </row>
+    <row r="30" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="12"/>
       <c r="B30" s="12"/>
-      <c r="C30" s="146" t="s">
-        <v>40</v>
-      </c>
-      <c r="D30" s="168">
-        <f>ROUNDUP(PMT($N$22/12,15,-$N$20),0)</f>
+      <c r="C30" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="E30" s="169"/>
-      <c r="F30" s="168">
-        <f>ROUNDUP(PMT($N$22/12,15,-$O$20),0)</f>
-        <v>13</v>
-      </c>
-      <c r="G30" s="169"/>
-      <c r="H30" s="157" t="s">
-        <v>7</v>
-      </c>
-      <c r="I30" s="158" t="s">
-        <v>15</v>
-      </c>
-      <c r="J30" s="159" t="s">
-        <v>14</v>
-      </c>
-      <c r="K30" s="165"/>
-      <c r="L30" s="165"/>
-      <c r="M30" s="139"/>
-      <c r="N30" s="139"/>
-      <c r="O30" s="139"/>
+      <c r="D30" s="71">
+        <f t="shared" si="0"/>
+        <v>180</v>
+      </c>
+      <c r="E30" s="71">
+        <f>ROUNDUP($O$20/100*(100+$N$27),-1)</f>
+        <v>180</v>
+      </c>
+      <c r="F30" s="65" t="str">
+        <f>"~"&amp;ROUNDUP(PMT($N$25/12,36,-D30),0)</f>
+        <v>~7</v>
+      </c>
+      <c r="G30" s="65" t="str">
+        <f>"~"&amp;ROUNDUP(PMT($N$25/12,36,-E30),0)</f>
+        <v>~7</v>
+      </c>
+      <c r="I30" s="74"/>
+      <c r="J30" s="75"/>
+      <c r="K30" s="75"/>
+      <c r="L30" s="76"/>
+      <c r="M30" s="106"/>
+      <c r="N30" s="106"/>
+      <c r="O30" s="106"/>
       <c r="P30" s="12"/>
-      <c r="Q30" s="174"/>
-      <c r="R30" s="175"/>
-      <c r="S30" s="175"/>
-      <c r="T30" s="175"/>
-      <c r="U30" s="175"/>
-      <c r="V30" s="176"/>
-      <c r="W30" s="118"/>
-      <c r="X30" s="119"/>
-      <c r="Z30" s="105"/>
-    </row>
-    <row r="31" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q30" s="154"/>
+      <c r="R30" s="155"/>
+      <c r="S30" s="155"/>
+      <c r="T30" s="155"/>
+      <c r="U30" s="155"/>
+      <c r="V30" s="156"/>
+      <c r="W30" s="93"/>
+      <c r="X30" s="94"/>
+      <c r="Z30" s="81"/>
+    </row>
+    <row r="31" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="12"/>
       <c r="B31" s="12"/>
-      <c r="C31" s="146" t="s">
-        <v>11</v>
-      </c>
-      <c r="D31" s="168">
-        <f>ROUNDUP(PMT($N$22/12,18,-$N$20),0)</f>
-        <v>11</v>
-      </c>
-      <c r="E31" s="169"/>
-      <c r="F31" s="168">
-        <f>ROUNDUP(PMT($N$22/12,18,-$O$20),0)</f>
-        <v>11</v>
-      </c>
-      <c r="G31" s="169"/>
-      <c r="H31" s="155" t="s">
-        <v>12</v>
-      </c>
-      <c r="I31" s="154">
-        <f>ROUNDUP($N$20*1.042,-1)</f>
+      <c r="C31" s="63" t="s">
+        <v>32</v>
+      </c>
+      <c r="D31" s="71">
+        <f t="shared" si="0"/>
         <v>180</v>
       </c>
-      <c r="J31" s="154">
-        <f>ROUNDUP($O$20*1.042,-1)</f>
+      <c r="E31" s="71">
+        <f t="shared" si="1"/>
         <v>180</v>
       </c>
-      <c r="K31" s="156" t="str">
-        <f>"&lt; "&amp;ROUNDUP(PMT($N$22/12,24,-I31),0)</f>
-        <v>&lt; 9</v>
-      </c>
-      <c r="L31" s="156" t="str">
-        <f>"&lt; "&amp;ROUNDUP(PMT($N$22/12,24,-J31),0)</f>
-        <v>&lt; 9</v>
-      </c>
-      <c r="M31" s="139"/>
-      <c r="N31" s="139"/>
-      <c r="O31" s="139"/>
+      <c r="F31" s="65" t="str">
+        <f>"~"&amp;ROUNDUP(PMT($N$25/12,48,-D31),0)</f>
+        <v>~6</v>
+      </c>
+      <c r="G31" s="65" t="str">
+        <f>"~"&amp;ROUNDUP(PMT($N$25/12,48,-E31),0)</f>
+        <v>~6</v>
+      </c>
+      <c r="I31" s="231" t="s">
+        <v>50</v>
+      </c>
+      <c r="J31" s="232"/>
+      <c r="K31" s="235">
+        <f>C3*J3</f>
+        <v>0</v>
+      </c>
+      <c r="L31" s="236"/>
+      <c r="M31" s="106"/>
+      <c r="N31" s="106"/>
+      <c r="O31" s="106"/>
       <c r="P31" s="12"/>
-      <c r="Q31" s="174"/>
-      <c r="R31" s="175"/>
-      <c r="S31" s="175"/>
-      <c r="T31" s="175"/>
-      <c r="U31" s="175"/>
-      <c r="V31" s="176"/>
-      <c r="W31" s="118"/>
-      <c r="X31" s="119"/>
-      <c r="Z31" s="105"/>
-    </row>
-    <row r="32" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q31" s="154"/>
+      <c r="R31" s="155"/>
+      <c r="S31" s="155"/>
+      <c r="T31" s="155"/>
+      <c r="U31" s="155"/>
+      <c r="V31" s="156"/>
+      <c r="W31" s="93"/>
+      <c r="X31" s="94"/>
+      <c r="Z31" s="81"/>
+    </row>
+    <row r="32" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="12"/>
       <c r="B32" s="12"/>
-      <c r="C32" s="146" t="s">
-        <v>12</v>
-      </c>
-      <c r="D32" s="168">
-        <f>ROUNDUP(PMT($N$22/12,24,-$N$20),0)</f>
-        <v>9</v>
-      </c>
-      <c r="E32" s="169"/>
-      <c r="F32" s="168">
-        <f>ROUNDUP(PMT($N$22/12,24,-$O$20),0)</f>
-        <v>9</v>
-      </c>
-      <c r="G32" s="169"/>
-      <c r="H32" s="152" t="s">
-        <v>13</v>
-      </c>
-      <c r="I32" s="154">
-        <f>ROUNDUP($N$20*1.042,-1)</f>
+      <c r="C32" s="63" t="s">
+        <v>39</v>
+      </c>
+      <c r="D32" s="71">
+        <f t="shared" si="0"/>
         <v>180</v>
       </c>
-      <c r="J32" s="154">
-        <f>ROUNDUP($O$20*1.042,-1)</f>
+      <c r="E32" s="71">
+        <f t="shared" si="1"/>
         <v>180</v>
       </c>
-      <c r="K32" s="156" t="str">
-        <f>"&lt; "&amp;ROUNDUP(PMT($N$22/12,36,-I32),0)</f>
-        <v>&lt; 7</v>
-      </c>
-      <c r="L32" s="156" t="str">
-        <f>"&lt; "&amp;ROUNDUP(PMT($N$22/12,36,-J32),0)</f>
-        <v>&lt; 7</v>
-      </c>
-      <c r="M32" s="139"/>
-      <c r="N32" s="139"/>
-      <c r="O32" s="139"/>
+      <c r="F32" s="65" t="str">
+        <f>"~"&amp;ROUNDUP(PMT($N$25/12,60,-D32),0)</f>
+        <v>~5</v>
+      </c>
+      <c r="G32" s="65" t="str">
+        <f>"~"&amp;ROUNDUP(PMT($N$25/12,60,-E32),0)</f>
+        <v>~5</v>
+      </c>
+      <c r="I32" s="233"/>
+      <c r="J32" s="234"/>
+      <c r="K32" s="237"/>
+      <c r="L32" s="238"/>
+      <c r="M32" s="106"/>
+      <c r="N32" s="106"/>
+      <c r="O32" s="106"/>
       <c r="P32" s="12"/>
-      <c r="Q32" s="174"/>
-      <c r="R32" s="175"/>
-      <c r="S32" s="175"/>
-      <c r="T32" s="175"/>
-      <c r="U32" s="175"/>
-      <c r="V32" s="176"/>
-      <c r="W32" s="118"/>
-      <c r="X32" s="119"/>
-      <c r="Z32" s="105"/>
-    </row>
-    <row r="33" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q32" s="154"/>
+      <c r="R32" s="155"/>
+      <c r="S32" s="155"/>
+      <c r="T32" s="155"/>
+      <c r="U32" s="155"/>
+      <c r="V32" s="156"/>
+      <c r="W32" s="93"/>
+      <c r="X32" s="94"/>
+      <c r="Z32" s="81"/>
+    </row>
+    <row r="33" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="12"/>
       <c r="B33" s="12"/>
-      <c r="C33" s="146" t="s">
-        <v>13</v>
-      </c>
-      <c r="D33" s="168">
-        <f>ROUNDUP(PMT($N$22/12,36,-$N$20),0)</f>
-        <v>6</v>
-      </c>
-      <c r="E33" s="169"/>
-      <c r="F33" s="168">
-        <f>ROUNDUP(PMT($N$22/12,36,-$O$20),0)</f>
-        <v>6</v>
-      </c>
-      <c r="G33" s="169"/>
-      <c r="H33" s="152" t="s">
-        <v>32</v>
-      </c>
-      <c r="I33" s="154">
-        <f>ROUNDUP($N$20*1.042,-1)</f>
-        <v>180</v>
-      </c>
-      <c r="J33" s="154">
-        <f>ROUNDUP($O$20*1.042,-1)</f>
-        <v>180</v>
-      </c>
-      <c r="K33" s="156" t="str">
-        <f>"&lt; "&amp;ROUNDUP(PMT($N$22/12,48,-I33),0)</f>
-        <v>&lt; 5</v>
-      </c>
-      <c r="L33" s="156" t="str">
-        <f>"&lt; "&amp;ROUNDUP(PMT($N$22/12,48,-J33),0)</f>
-        <v>&lt; 5</v>
-      </c>
       <c r="M33" s="12"/>
       <c r="N33" s="12"/>
       <c r="O33" s="12"/>
       <c r="P33" s="12"/>
-      <c r="Q33" s="174"/>
-      <c r="R33" s="175"/>
-      <c r="S33" s="175"/>
-      <c r="T33" s="175"/>
-      <c r="U33" s="175"/>
-      <c r="V33" s="176"/>
-      <c r="W33" s="118"/>
-      <c r="X33" s="119"/>
-      <c r="Z33" s="105"/>
-    </row>
-    <row r="34" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q33" s="154"/>
+      <c r="R33" s="155"/>
+      <c r="S33" s="155"/>
+      <c r="T33" s="155"/>
+      <c r="U33" s="155"/>
+      <c r="V33" s="156"/>
+      <c r="W33" s="93"/>
+      <c r="X33" s="94"/>
+      <c r="Z33" s="81"/>
+    </row>
+    <row r="34" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="12"/>
       <c r="B34" s="12"/>
-      <c r="C34" s="147" t="s">
-        <v>32</v>
-      </c>
-      <c r="D34" s="168">
-        <f>ROUNDUP(PMT($N$22/12,48,-$N$20),0)</f>
-        <v>5</v>
-      </c>
-      <c r="E34" s="169"/>
-      <c r="F34" s="168">
-        <f>ROUNDUP(PMT($N$22/12,48,-$O$20),0)</f>
-        <v>5</v>
-      </c>
-      <c r="G34" s="169"/>
-      <c r="H34" s="153" t="s">
-        <v>43</v>
-      </c>
-      <c r="I34" s="154">
-        <f>ROUNDUP($N$20*1.042,-1)</f>
-        <v>180</v>
-      </c>
-      <c r="J34" s="154">
-        <f>ROUNDUP($O$20*1.042,-1)</f>
-        <v>180</v>
-      </c>
-      <c r="K34" s="156" t="str">
-        <f>"&lt; "&amp;ROUNDUP(PMT($N$22/12,60,-I34),0)</f>
-        <v>&lt; 5</v>
-      </c>
-      <c r="L34" s="156" t="str">
-        <f>"&lt; "&amp;ROUNDUP(PMT($N$22/12,60,-J34),0)</f>
-        <v>&lt; 5</v>
-      </c>
       <c r="M34" s="12"/>
       <c r="N34" s="12"/>
       <c r="O34" s="12"/>
       <c r="P34" s="12"/>
-      <c r="Q34" s="174"/>
-      <c r="R34" s="175"/>
-      <c r="S34" s="175"/>
-      <c r="T34" s="175"/>
-      <c r="U34" s="175"/>
-      <c r="V34" s="176"/>
-      <c r="W34" s="118"/>
-      <c r="X34" s="119"/>
-      <c r="Z34" s="105"/>
-    </row>
-    <row r="35" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q34" s="154"/>
+      <c r="R34" s="155"/>
+      <c r="S34" s="155"/>
+      <c r="T34" s="155"/>
+      <c r="U34" s="155"/>
+      <c r="V34" s="156"/>
+      <c r="W34" s="93"/>
+      <c r="X34" s="94"/>
+      <c r="Z34" s="81"/>
+    </row>
+    <row r="35" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="12"/>
       <c r="B35" s="12"/>
-      <c r="C35" s="147" t="s">
-        <v>43</v>
-      </c>
-      <c r="D35" s="168">
-        <f>ROUNDUP(PMT($N$22/12,60,-$N$20),0)</f>
-        <v>5</v>
-      </c>
-      <c r="E35" s="169"/>
-      <c r="F35" s="168">
-        <f>ROUNDUP(PMT($N$22/12,60,-$O$20),0)</f>
-        <v>5</v>
-      </c>
-      <c r="G35" s="169"/>
-      <c r="M35" s="12"/>
       <c r="N35" s="12"/>
       <c r="O35" s="12"/>
       <c r="P35" s="12"/>
-      <c r="Q35" s="174"/>
-      <c r="R35" s="175"/>
-      <c r="S35" s="175"/>
-      <c r="T35" s="175"/>
-      <c r="U35" s="175"/>
-      <c r="V35" s="176"/>
-      <c r="W35" s="118"/>
-      <c r="X35" s="119"/>
-      <c r="Z35" s="105"/>
-    </row>
-    <row r="36" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q35" s="154"/>
+      <c r="R35" s="155"/>
+      <c r="S35" s="155"/>
+      <c r="T35" s="155"/>
+      <c r="U35" s="155"/>
+      <c r="V35" s="156"/>
+      <c r="W35" s="93"/>
+      <c r="X35" s="94"/>
+      <c r="Z35" s="81"/>
+    </row>
+    <row r="36" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="12"/>
       <c r="B36" s="12"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-      <c r="M36" s="12"/>
       <c r="N36" s="12"/>
       <c r="O36" s="12"/>
       <c r="P36" s="12"/>
-      <c r="Q36" s="174"/>
-      <c r="R36" s="175"/>
-      <c r="S36" s="175"/>
-      <c r="T36" s="175"/>
-      <c r="U36" s="175"/>
-      <c r="V36" s="176"/>
-      <c r="W36" s="118"/>
-      <c r="X36" s="119"/>
-      <c r="Z36" s="105"/>
+      <c r="Q36" s="154"/>
+      <c r="R36" s="155"/>
+      <c r="S36" s="155"/>
+      <c r="T36" s="155"/>
+      <c r="U36" s="155"/>
+      <c r="V36" s="156"/>
+      <c r="W36" s="93"/>
+      <c r="X36" s="94"/>
+      <c r="Z36" s="81"/>
     </row>
     <row r="37" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="12"/>
       <c r="B37" s="12"/>
-      <c r="C37" s="182" t="s">
-        <v>33</v>
-      </c>
-      <c r="D37" s="183"/>
-      <c r="E37" s="186">
-        <v>0</v>
-      </c>
-      <c r="F37" s="187"/>
-      <c r="M37" s="12"/>
       <c r="N37" s="12"/>
       <c r="O37" s="12"/>
       <c r="P37" s="12"/>
-      <c r="Q37" s="174"/>
-      <c r="R37" s="175"/>
-      <c r="S37" s="175"/>
-      <c r="T37" s="175"/>
-      <c r="U37" s="175"/>
-      <c r="V37" s="176"/>
-      <c r="W37" s="118"/>
-      <c r="X37" s="119"/>
-      <c r="Z37" s="105"/>
-    </row>
-    <row r="38" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q37" s="154"/>
+      <c r="R37" s="155"/>
+      <c r="S37" s="155"/>
+      <c r="T37" s="155"/>
+      <c r="U37" s="155"/>
+      <c r="V37" s="156"/>
+      <c r="W37" s="93"/>
+      <c r="X37" s="94"/>
+      <c r="Z37" s="81"/>
+    </row>
+    <row r="38" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="12"/>
       <c r="B38" s="12"/>
-      <c r="C38" s="184"/>
-      <c r="D38" s="185"/>
-      <c r="E38" s="188"/>
-      <c r="F38" s="189"/>
-      <c r="M38" s="12"/>
       <c r="N38" s="12"/>
       <c r="O38" s="12"/>
       <c r="P38" s="12"/>
-      <c r="Q38" s="174"/>
-      <c r="R38" s="175"/>
-      <c r="S38" s="175"/>
-      <c r="T38" s="175"/>
-      <c r="U38" s="175"/>
-      <c r="V38" s="176"/>
-      <c r="W38" s="118"/>
-      <c r="X38" s="119"/>
-      <c r="Z38" s="105"/>
-    </row>
-    <row r="39" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q38" s="154"/>
+      <c r="R38" s="155"/>
+      <c r="S38" s="155"/>
+      <c r="T38" s="155"/>
+      <c r="U38" s="155"/>
+      <c r="V38" s="156"/>
+      <c r="W38" s="93"/>
+      <c r="X38" s="94"/>
+      <c r="Z38" s="81"/>
+    </row>
+    <row r="39" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="12"/>
       <c r="B39" s="12"/>
-      <c r="C39" s="95"/>
-      <c r="D39" s="96"/>
-      <c r="E39" s="96"/>
-      <c r="F39" s="97"/>
       <c r="G39" s="12"/>
       <c r="H39" s="12"/>
-      <c r="I39" s="12"/>
-      <c r="J39" s="12"/>
-      <c r="K39" s="12"/>
-      <c r="L39" s="12"/>
-      <c r="M39" s="12"/>
       <c r="N39" s="12"/>
       <c r="O39" s="12"/>
       <c r="P39" s="12"/>
-      <c r="Q39" s="174"/>
-      <c r="R39" s="175"/>
-      <c r="S39" s="175"/>
-      <c r="T39" s="175"/>
-      <c r="U39" s="175"/>
-      <c r="V39" s="176"/>
-      <c r="W39" s="118"/>
-      <c r="X39" s="119"/>
-      <c r="Z39" s="105"/>
+      <c r="Q39" s="154"/>
+      <c r="R39" s="155"/>
+      <c r="S39" s="155"/>
+      <c r="T39" s="155"/>
+      <c r="U39" s="155"/>
+      <c r="V39" s="156"/>
+      <c r="W39" s="93"/>
+      <c r="X39" s="94"/>
+      <c r="Z39" s="81"/>
     </row>
     <row r="40" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="12"/>
       <c r="B40" s="12"/>
-      <c r="C40" s="271" t="s">
-        <v>57</v>
-      </c>
-      <c r="D40" s="272"/>
-      <c r="E40" s="275">
-        <f>C3*J3</f>
-        <v>0</v>
-      </c>
-      <c r="F40" s="276"/>
       <c r="H40" s="12"/>
-      <c r="I40" s="12"/>
-      <c r="J40" s="12"/>
-      <c r="K40" s="12"/>
-      <c r="L40" s="12"/>
-      <c r="M40" s="12"/>
       <c r="N40" s="12"/>
       <c r="O40" s="12"/>
       <c r="P40" s="12"/>
-      <c r="Q40" s="174"/>
-      <c r="R40" s="175"/>
-      <c r="S40" s="175"/>
-      <c r="T40" s="175"/>
-      <c r="U40" s="175"/>
-      <c r="V40" s="176"/>
-      <c r="W40" s="118"/>
-      <c r="X40" s="119"/>
-      <c r="Z40" s="105"/>
-    </row>
-    <row r="41" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q40" s="154"/>
+      <c r="R40" s="155"/>
+      <c r="S40" s="155"/>
+      <c r="T40" s="155"/>
+      <c r="U40" s="155"/>
+      <c r="V40" s="156"/>
+      <c r="W40" s="93"/>
+      <c r="X40" s="94"/>
+      <c r="Z40" s="81"/>
+    </row>
+    <row r="41" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="12"/>
       <c r="B41" s="12"/>
-      <c r="C41" s="273"/>
-      <c r="D41" s="274"/>
-      <c r="E41" s="277"/>
-      <c r="F41" s="278"/>
-      <c r="I41" s="12"/>
-      <c r="J41" s="12"/>
-      <c r="K41" s="12"/>
-      <c r="L41" s="12"/>
-      <c r="M41" s="12"/>
       <c r="N41" s="12"/>
       <c r="O41" s="12"/>
       <c r="P41" s="12"/>
-      <c r="Q41" s="174"/>
-      <c r="R41" s="175"/>
-      <c r="S41" s="175"/>
-      <c r="T41" s="175"/>
-      <c r="U41" s="175"/>
-      <c r="V41" s="176"/>
-      <c r="W41" s="118"/>
-      <c r="X41" s="119"/>
+      <c r="Q41" s="154"/>
+      <c r="R41" s="155"/>
+      <c r="S41" s="155"/>
+      <c r="T41" s="155"/>
+      <c r="U41" s="155"/>
+      <c r="V41" s="156"/>
+      <c r="W41" s="93"/>
+      <c r="X41" s="94"/>
     </row>
     <row r="42" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="12"/>
       <c r="B42" s="12"/>
-      <c r="I42" s="12"/>
-      <c r="J42" s="12"/>
-      <c r="K42" s="12"/>
-      <c r="L42" s="12"/>
-      <c r="M42" s="12"/>
       <c r="N42" s="12"/>
       <c r="O42" s="12"/>
       <c r="P42" s="12"/>
-      <c r="Q42" s="174"/>
-      <c r="R42" s="175"/>
-      <c r="S42" s="175"/>
-      <c r="T42" s="175"/>
-      <c r="U42" s="175"/>
-      <c r="V42" s="176"/>
-      <c r="W42" s="118"/>
-      <c r="X42" s="119"/>
+      <c r="Q42" s="154"/>
+      <c r="R42" s="155"/>
+      <c r="S42" s="155"/>
+      <c r="T42" s="155"/>
+      <c r="U42" s="155"/>
+      <c r="V42" s="156"/>
+      <c r="W42" s="93"/>
+      <c r="X42" s="94"/>
     </row>
     <row r="43" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="12"/>
       <c r="B43" s="12"/>
-      <c r="I43" s="12"/>
       <c r="N43" s="12"/>
       <c r="O43" s="12"/>
       <c r="P43" s="12"/>
-      <c r="Q43" s="174"/>
-      <c r="R43" s="175"/>
-      <c r="S43" s="175"/>
-      <c r="T43" s="175"/>
-      <c r="U43" s="175"/>
-      <c r="V43" s="176"/>
-      <c r="W43" s="118"/>
-      <c r="X43" s="119"/>
+      <c r="Q43" s="154"/>
+      <c r="R43" s="155"/>
+      <c r="S43" s="155"/>
+      <c r="T43" s="155"/>
+      <c r="U43" s="155"/>
+      <c r="V43" s="156"/>
+      <c r="W43" s="93"/>
+      <c r="X43" s="94"/>
     </row>
     <row r="44" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="Q44" s="174"/>
-      <c r="R44" s="175"/>
-      <c r="S44" s="175"/>
-      <c r="T44" s="175"/>
-      <c r="U44" s="175"/>
-      <c r="V44" s="176"/>
-      <c r="W44" s="118"/>
-      <c r="X44" s="119"/>
+      <c r="Q44" s="154"/>
+      <c r="R44" s="155"/>
+      <c r="S44" s="155"/>
+      <c r="T44" s="155"/>
+      <c r="U44" s="155"/>
+      <c r="V44" s="156"/>
+      <c r="W44" s="93"/>
+      <c r="X44" s="94"/>
     </row>
     <row r="45" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="Q45" s="174"/>
-      <c r="R45" s="175"/>
-      <c r="S45" s="175"/>
-      <c r="T45" s="175"/>
-      <c r="U45" s="175"/>
-      <c r="V45" s="176"/>
-      <c r="W45" s="118"/>
-      <c r="X45" s="119"/>
+      <c r="Q45" s="154"/>
+      <c r="R45" s="155"/>
+      <c r="S45" s="155"/>
+      <c r="T45" s="155"/>
+      <c r="U45" s="155"/>
+      <c r="V45" s="156"/>
+      <c r="W45" s="93"/>
+      <c r="X45" s="94"/>
     </row>
     <row r="46" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="Q46" s="174"/>
-      <c r="R46" s="175"/>
-      <c r="S46" s="175"/>
-      <c r="T46" s="175"/>
-      <c r="U46" s="175"/>
-      <c r="V46" s="176"/>
-      <c r="W46" s="118"/>
-      <c r="X46" s="119"/>
+      <c r="Q46" s="154"/>
+      <c r="R46" s="155"/>
+      <c r="S46" s="155"/>
+      <c r="T46" s="155"/>
+      <c r="U46" s="155"/>
+      <c r="V46" s="156"/>
+      <c r="W46" s="93"/>
+      <c r="X46" s="94"/>
     </row>
     <row r="47" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="Q47" s="174"/>
-      <c r="R47" s="175"/>
-      <c r="S47" s="175"/>
-      <c r="T47" s="175"/>
-      <c r="U47" s="175"/>
-      <c r="V47" s="176"/>
-      <c r="W47" s="118"/>
-      <c r="X47" s="119"/>
+      <c r="Q47" s="154"/>
+      <c r="R47" s="155"/>
+      <c r="S47" s="155"/>
+      <c r="T47" s="155"/>
+      <c r="U47" s="155"/>
+      <c r="V47" s="156"/>
+      <c r="W47" s="93"/>
+      <c r="X47" s="94"/>
     </row>
     <row r="48" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="Q48" s="174"/>
-      <c r="R48" s="175"/>
-      <c r="S48" s="175"/>
-      <c r="T48" s="175"/>
-      <c r="U48" s="175"/>
-      <c r="V48" s="176"/>
-      <c r="W48" s="118"/>
-      <c r="X48" s="119"/>
+      <c r="Q48" s="154"/>
+      <c r="R48" s="155"/>
+      <c r="S48" s="155"/>
+      <c r="T48" s="155"/>
+      <c r="U48" s="155"/>
+      <c r="V48" s="156"/>
+      <c r="W48" s="93"/>
+      <c r="X48" s="94"/>
     </row>
     <row r="49" spans="17:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="Q49" s="174"/>
-      <c r="R49" s="175"/>
-      <c r="S49" s="175"/>
-      <c r="T49" s="175"/>
-      <c r="U49" s="175"/>
-      <c r="V49" s="176"/>
-      <c r="W49" s="118"/>
-      <c r="X49" s="119"/>
+      <c r="Q49" s="154"/>
+      <c r="R49" s="155"/>
+      <c r="S49" s="155"/>
+      <c r="T49" s="155"/>
+      <c r="U49" s="155"/>
+      <c r="V49" s="156"/>
+      <c r="W49" s="93"/>
+      <c r="X49" s="94"/>
     </row>
     <row r="50" spans="17:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="Q50" s="174"/>
-      <c r="R50" s="175"/>
-      <c r="S50" s="175"/>
-      <c r="T50" s="175"/>
-      <c r="U50" s="175"/>
-      <c r="V50" s="176"/>
-      <c r="W50" s="118"/>
-      <c r="X50" s="119"/>
+      <c r="Q50" s="154"/>
+      <c r="R50" s="155"/>
+      <c r="S50" s="155"/>
+      <c r="T50" s="155"/>
+      <c r="U50" s="155"/>
+      <c r="V50" s="156"/>
+      <c r="W50" s="93"/>
+      <c r="X50" s="94"/>
     </row>
     <row r="51" spans="17:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="Q51" s="174"/>
-      <c r="R51" s="175"/>
-      <c r="S51" s="175"/>
-      <c r="T51" s="175"/>
-      <c r="U51" s="175"/>
-      <c r="V51" s="176"/>
-      <c r="W51" s="118"/>
-      <c r="X51" s="119"/>
+      <c r="Q51" s="154"/>
+      <c r="R51" s="155"/>
+      <c r="S51" s="155"/>
+      <c r="T51" s="155"/>
+      <c r="U51" s="155"/>
+      <c r="V51" s="156"/>
+      <c r="W51" s="93"/>
+      <c r="X51" s="94"/>
     </row>
     <row r="52" spans="17:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="Q52" s="174"/>
-      <c r="R52" s="175"/>
-      <c r="S52" s="175"/>
-      <c r="T52" s="175"/>
-      <c r="U52" s="175"/>
-      <c r="V52" s="176"/>
-      <c r="W52" s="118"/>
-      <c r="X52" s="119"/>
+      <c r="Q52" s="154"/>
+      <c r="R52" s="155"/>
+      <c r="S52" s="155"/>
+      <c r="T52" s="155"/>
+      <c r="U52" s="155"/>
+      <c r="V52" s="156"/>
+      <c r="W52" s="93"/>
+      <c r="X52" s="94"/>
     </row>
     <row r="53" spans="17:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="Q53" s="174"/>
-      <c r="R53" s="175"/>
-      <c r="S53" s="175"/>
-      <c r="T53" s="175"/>
-      <c r="U53" s="175"/>
-      <c r="V53" s="176"/>
-      <c r="W53" s="118"/>
-      <c r="X53" s="119"/>
+      <c r="Q53" s="154"/>
+      <c r="R53" s="155"/>
+      <c r="S53" s="155"/>
+      <c r="T53" s="155"/>
+      <c r="U53" s="155"/>
+      <c r="V53" s="156"/>
+      <c r="W53" s="93"/>
+      <c r="X53" s="94"/>
     </row>
     <row r="54" spans="17:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="Q54" s="174"/>
-      <c r="R54" s="175"/>
-      <c r="S54" s="175"/>
-      <c r="T54" s="175"/>
-      <c r="U54" s="175"/>
-      <c r="V54" s="176"/>
-      <c r="W54" s="118"/>
-      <c r="X54" s="119"/>
+      <c r="Q54" s="154"/>
+      <c r="R54" s="155"/>
+      <c r="S54" s="155"/>
+      <c r="T54" s="155"/>
+      <c r="U54" s="155"/>
+      <c r="V54" s="156"/>
+      <c r="W54" s="93"/>
+      <c r="X54" s="94"/>
     </row>
     <row r="55" spans="17:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="Q55" s="174"/>
-      <c r="R55" s="175"/>
-      <c r="S55" s="175"/>
-      <c r="T55" s="175"/>
-      <c r="U55" s="175"/>
-      <c r="V55" s="176"/>
-      <c r="W55" s="118"/>
-      <c r="X55" s="119"/>
+      <c r="Q55" s="154"/>
+      <c r="R55" s="155"/>
+      <c r="S55" s="155"/>
+      <c r="T55" s="155"/>
+      <c r="U55" s="155"/>
+      <c r="V55" s="156"/>
+      <c r="W55" s="93"/>
+      <c r="X55" s="94"/>
     </row>
     <row r="56" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q56" s="179"/>
-      <c r="R56" s="180"/>
-      <c r="S56" s="180"/>
-      <c r="T56" s="180"/>
-      <c r="U56" s="180"/>
-      <c r="V56" s="181"/>
-      <c r="W56" s="114"/>
-      <c r="X56" s="140"/>
+      <c r="Q56" s="157"/>
+      <c r="R56" s="158"/>
+      <c r="S56" s="158"/>
+      <c r="T56" s="158"/>
+      <c r="U56" s="158"/>
+      <c r="V56" s="159"/>
+      <c r="W56" s="90"/>
+      <c r="X56" s="107"/>
     </row>
     <row r="57" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q57" s="174"/>
-      <c r="R57" s="175"/>
-      <c r="S57" s="175"/>
-      <c r="T57" s="175"/>
-      <c r="U57" s="175"/>
-      <c r="V57" s="176"/>
-      <c r="W57" s="118"/>
-      <c r="X57" s="119"/>
+      <c r="Q57" s="154"/>
+      <c r="R57" s="155"/>
+      <c r="S57" s="155"/>
+      <c r="T57" s="155"/>
+      <c r="U57" s="155"/>
+      <c r="V57" s="156"/>
+      <c r="W57" s="93"/>
+      <c r="X57" s="94"/>
     </row>
     <row r="58" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q58" s="174"/>
-      <c r="R58" s="175"/>
-      <c r="S58" s="175"/>
-      <c r="T58" s="175"/>
-      <c r="U58" s="175"/>
-      <c r="V58" s="176"/>
-      <c r="W58" s="118"/>
-      <c r="X58" s="119"/>
+      <c r="Q58" s="154"/>
+      <c r="R58" s="155"/>
+      <c r="S58" s="155"/>
+      <c r="T58" s="155"/>
+      <c r="U58" s="155"/>
+      <c r="V58" s="156"/>
+      <c r="W58" s="93"/>
+      <c r="X58" s="94"/>
     </row>
     <row r="59" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q59" s="174"/>
-      <c r="R59" s="175"/>
-      <c r="S59" s="175"/>
-      <c r="T59" s="175"/>
-      <c r="U59" s="175"/>
-      <c r="V59" s="176"/>
-      <c r="W59" s="118"/>
-      <c r="X59" s="119"/>
+      <c r="Q59" s="154"/>
+      <c r="R59" s="155"/>
+      <c r="S59" s="155"/>
+      <c r="T59" s="155"/>
+      <c r="U59" s="155"/>
+      <c r="V59" s="156"/>
+      <c r="W59" s="93"/>
+      <c r="X59" s="94"/>
     </row>
     <row r="60" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q60" s="174"/>
-      <c r="R60" s="175"/>
-      <c r="S60" s="175"/>
-      <c r="T60" s="175"/>
-      <c r="U60" s="175"/>
-      <c r="V60" s="176"/>
-      <c r="W60" s="118"/>
-      <c r="X60" s="119"/>
+      <c r="Q60" s="154"/>
+      <c r="R60" s="155"/>
+      <c r="S60" s="155"/>
+      <c r="T60" s="155"/>
+      <c r="U60" s="155"/>
+      <c r="V60" s="156"/>
+      <c r="W60" s="93"/>
+      <c r="X60" s="94"/>
     </row>
     <row r="61" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q61" s="174"/>
-      <c r="R61" s="175"/>
-      <c r="S61" s="175"/>
-      <c r="T61" s="175"/>
-      <c r="U61" s="175"/>
-      <c r="V61" s="176"/>
-      <c r="W61" s="118"/>
-      <c r="X61" s="119"/>
+      <c r="Q61" s="154"/>
+      <c r="R61" s="155"/>
+      <c r="S61" s="155"/>
+      <c r="T61" s="155"/>
+      <c r="U61" s="155"/>
+      <c r="V61" s="156"/>
+      <c r="W61" s="93"/>
+      <c r="X61" s="94"/>
     </row>
     <row r="62" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q62" s="174"/>
-      <c r="R62" s="175"/>
-      <c r="S62" s="175"/>
-      <c r="T62" s="175"/>
-      <c r="U62" s="175"/>
-      <c r="V62" s="176"/>
-      <c r="W62" s="118"/>
-      <c r="X62" s="119"/>
+      <c r="Q62" s="154"/>
+      <c r="R62" s="155"/>
+      <c r="S62" s="155"/>
+      <c r="T62" s="155"/>
+      <c r="U62" s="155"/>
+      <c r="V62" s="156"/>
+      <c r="W62" s="93"/>
+      <c r="X62" s="94"/>
     </row>
     <row r="63" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q63" s="174"/>
-      <c r="R63" s="175"/>
-      <c r="S63" s="175"/>
-      <c r="T63" s="175"/>
-      <c r="U63" s="175"/>
-      <c r="V63" s="176"/>
-      <c r="W63" s="118"/>
-      <c r="X63" s="119"/>
+      <c r="Q63" s="154"/>
+      <c r="R63" s="155"/>
+      <c r="S63" s="155"/>
+      <c r="T63" s="155"/>
+      <c r="U63" s="155"/>
+      <c r="V63" s="156"/>
+      <c r="W63" s="93"/>
+      <c r="X63" s="94"/>
     </row>
     <row r="64" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q64" s="174"/>
-      <c r="R64" s="175"/>
-      <c r="S64" s="175"/>
-      <c r="T64" s="175"/>
-      <c r="U64" s="175"/>
-      <c r="V64" s="176"/>
-      <c r="W64" s="118"/>
-      <c r="X64" s="119"/>
+      <c r="Q64" s="154"/>
+      <c r="R64" s="155"/>
+      <c r="S64" s="155"/>
+      <c r="T64" s="155"/>
+      <c r="U64" s="155"/>
+      <c r="V64" s="156"/>
+      <c r="W64" s="93"/>
+      <c r="X64" s="94"/>
     </row>
     <row r="65" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q65" s="174"/>
-      <c r="R65" s="175"/>
-      <c r="S65" s="175"/>
-      <c r="T65" s="175"/>
-      <c r="U65" s="175"/>
-      <c r="V65" s="176"/>
-      <c r="W65" s="118"/>
-      <c r="X65" s="119"/>
+      <c r="Q65" s="154"/>
+      <c r="R65" s="155"/>
+      <c r="S65" s="155"/>
+      <c r="T65" s="155"/>
+      <c r="U65" s="155"/>
+      <c r="V65" s="156"/>
+      <c r="W65" s="93"/>
+      <c r="X65" s="94"/>
     </row>
     <row r="66" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q66" s="174"/>
-      <c r="R66" s="175"/>
-      <c r="S66" s="175"/>
-      <c r="T66" s="175"/>
-      <c r="U66" s="175"/>
-      <c r="V66" s="176"/>
-      <c r="W66" s="118"/>
-      <c r="X66" s="119"/>
+      <c r="Q66" s="154"/>
+      <c r="R66" s="155"/>
+      <c r="S66" s="155"/>
+      <c r="T66" s="155"/>
+      <c r="U66" s="155"/>
+      <c r="V66" s="156"/>
+      <c r="W66" s="93"/>
+      <c r="X66" s="94"/>
     </row>
     <row r="67" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q67" s="174"/>
-      <c r="R67" s="175"/>
-      <c r="S67" s="175"/>
-      <c r="T67" s="175"/>
-      <c r="U67" s="175"/>
-      <c r="V67" s="176"/>
-      <c r="W67" s="118"/>
-      <c r="X67" s="119"/>
+      <c r="Q67" s="154"/>
+      <c r="R67" s="155"/>
+      <c r="S67" s="155"/>
+      <c r="T67" s="155"/>
+      <c r="U67" s="155"/>
+      <c r="V67" s="156"/>
+      <c r="W67" s="93"/>
+      <c r="X67" s="94"/>
     </row>
     <row r="68" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q68" s="174"/>
-      <c r="R68" s="175"/>
-      <c r="S68" s="175"/>
-      <c r="T68" s="175"/>
-      <c r="U68" s="175"/>
-      <c r="V68" s="176"/>
-      <c r="W68" s="118"/>
-      <c r="X68" s="119"/>
+      <c r="Q68" s="154"/>
+      <c r="R68" s="155"/>
+      <c r="S68" s="155"/>
+      <c r="T68" s="155"/>
+      <c r="U68" s="155"/>
+      <c r="V68" s="156"/>
+      <c r="W68" s="93"/>
+      <c r="X68" s="94"/>
     </row>
     <row r="69" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q69" s="174"/>
-      <c r="R69" s="175"/>
-      <c r="S69" s="175"/>
-      <c r="T69" s="175"/>
-      <c r="U69" s="175"/>
-      <c r="V69" s="176"/>
-      <c r="W69" s="118"/>
-      <c r="X69" s="119"/>
+      <c r="Q69" s="154"/>
+      <c r="R69" s="155"/>
+      <c r="S69" s="155"/>
+      <c r="T69" s="155"/>
+      <c r="U69" s="155"/>
+      <c r="V69" s="156"/>
+      <c r="W69" s="93"/>
+      <c r="X69" s="94"/>
     </row>
     <row r="70" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q70" s="174"/>
-      <c r="R70" s="175"/>
-      <c r="S70" s="175"/>
-      <c r="T70" s="175"/>
-      <c r="U70" s="175"/>
-      <c r="V70" s="176"/>
-      <c r="W70" s="118"/>
-      <c r="X70" s="119"/>
+      <c r="Q70" s="154"/>
+      <c r="R70" s="155"/>
+      <c r="S70" s="155"/>
+      <c r="T70" s="155"/>
+      <c r="U70" s="155"/>
+      <c r="V70" s="156"/>
+      <c r="W70" s="93"/>
+      <c r="X70" s="94"/>
     </row>
     <row r="71" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q71" s="174"/>
-      <c r="R71" s="175"/>
-      <c r="S71" s="175"/>
-      <c r="T71" s="175"/>
-      <c r="U71" s="175"/>
-      <c r="V71" s="176"/>
-      <c r="W71" s="118"/>
-      <c r="X71" s="119"/>
+      <c r="Q71" s="154"/>
+      <c r="R71" s="155"/>
+      <c r="S71" s="155"/>
+      <c r="T71" s="155"/>
+      <c r="U71" s="155"/>
+      <c r="V71" s="156"/>
+      <c r="W71" s="93"/>
+      <c r="X71" s="94"/>
     </row>
     <row r="72" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q72" s="174"/>
-      <c r="R72" s="175"/>
-      <c r="S72" s="175"/>
-      <c r="T72" s="175"/>
-      <c r="U72" s="175"/>
-      <c r="V72" s="176"/>
-      <c r="W72" s="118"/>
-      <c r="X72" s="119"/>
+      <c r="Q72" s="154"/>
+      <c r="R72" s="155"/>
+      <c r="S72" s="155"/>
+      <c r="T72" s="155"/>
+      <c r="U72" s="155"/>
+      <c r="V72" s="156"/>
+      <c r="W72" s="93"/>
+      <c r="X72" s="94"/>
     </row>
     <row r="73" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q73" s="174"/>
-      <c r="R73" s="175"/>
-      <c r="S73" s="175"/>
-      <c r="T73" s="175"/>
-      <c r="U73" s="175"/>
-      <c r="V73" s="176"/>
-      <c r="W73" s="118"/>
-      <c r="X73" s="119"/>
+      <c r="Q73" s="154"/>
+      <c r="R73" s="155"/>
+      <c r="S73" s="155"/>
+      <c r="T73" s="155"/>
+      <c r="U73" s="155"/>
+      <c r="V73" s="156"/>
+      <c r="W73" s="93"/>
+      <c r="X73" s="94"/>
     </row>
     <row r="74" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q74" s="174"/>
-      <c r="R74" s="175"/>
-      <c r="S74" s="175"/>
-      <c r="T74" s="175"/>
-      <c r="U74" s="175"/>
-      <c r="V74" s="176"/>
-      <c r="W74" s="118"/>
-      <c r="X74" s="119"/>
+      <c r="Q74" s="154"/>
+      <c r="R74" s="155"/>
+      <c r="S74" s="155"/>
+      <c r="T74" s="155"/>
+      <c r="U74" s="155"/>
+      <c r="V74" s="156"/>
+      <c r="W74" s="93"/>
+      <c r="X74" s="94"/>
     </row>
     <row r="75" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q75" s="174"/>
-      <c r="R75" s="175"/>
-      <c r="S75" s="175"/>
-      <c r="T75" s="175"/>
-      <c r="U75" s="175"/>
-      <c r="V75" s="176"/>
-      <c r="W75" s="118"/>
-      <c r="X75" s="119"/>
+      <c r="Q75" s="154"/>
+      <c r="R75" s="155"/>
+      <c r="S75" s="155"/>
+      <c r="T75" s="155"/>
+      <c r="U75" s="155"/>
+      <c r="V75" s="156"/>
+      <c r="W75" s="93"/>
+      <c r="X75" s="94"/>
     </row>
     <row r="76" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q76" s="174"/>
-      <c r="R76" s="175"/>
-      <c r="S76" s="175"/>
-      <c r="T76" s="175"/>
-      <c r="U76" s="175"/>
-      <c r="V76" s="176"/>
-      <c r="W76" s="118"/>
-      <c r="X76" s="119"/>
+      <c r="Q76" s="154"/>
+      <c r="R76" s="155"/>
+      <c r="S76" s="155"/>
+      <c r="T76" s="155"/>
+      <c r="U76" s="155"/>
+      <c r="V76" s="156"/>
+      <c r="W76" s="93"/>
+      <c r="X76" s="94"/>
     </row>
     <row r="77" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q77" s="174"/>
-      <c r="R77" s="175"/>
-      <c r="S77" s="175"/>
-      <c r="T77" s="175"/>
-      <c r="U77" s="175"/>
-      <c r="V77" s="176"/>
-      <c r="W77" s="118"/>
-      <c r="X77" s="119"/>
+      <c r="Q77" s="154"/>
+      <c r="R77" s="155"/>
+      <c r="S77" s="155"/>
+      <c r="T77" s="155"/>
+      <c r="U77" s="155"/>
+      <c r="V77" s="156"/>
+      <c r="W77" s="93"/>
+      <c r="X77" s="94"/>
     </row>
     <row r="78" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q78" s="174"/>
-      <c r="R78" s="175"/>
-      <c r="S78" s="175"/>
-      <c r="T78" s="175"/>
-      <c r="U78" s="175"/>
-      <c r="V78" s="176"/>
-      <c r="W78" s="118"/>
-      <c r="X78" s="119"/>
+      <c r="Q78" s="154"/>
+      <c r="R78" s="155"/>
+      <c r="S78" s="155"/>
+      <c r="T78" s="155"/>
+      <c r="U78" s="155"/>
+      <c r="V78" s="156"/>
+      <c r="W78" s="93"/>
+      <c r="X78" s="94"/>
     </row>
     <row r="79" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q79" s="174"/>
-      <c r="R79" s="175"/>
-      <c r="S79" s="175"/>
-      <c r="T79" s="175"/>
-      <c r="U79" s="175"/>
-      <c r="V79" s="176"/>
-      <c r="W79" s="118"/>
-      <c r="X79" s="119"/>
+      <c r="Q79" s="154"/>
+      <c r="R79" s="155"/>
+      <c r="S79" s="155"/>
+      <c r="T79" s="155"/>
+      <c r="U79" s="155"/>
+      <c r="V79" s="156"/>
+      <c r="W79" s="93"/>
+      <c r="X79" s="94"/>
     </row>
     <row r="80" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q80" s="174"/>
-      <c r="R80" s="175"/>
-      <c r="S80" s="175"/>
-      <c r="T80" s="175"/>
-      <c r="U80" s="175"/>
-      <c r="V80" s="176"/>
-      <c r="W80" s="118"/>
-      <c r="X80" s="119"/>
+      <c r="Q80" s="154"/>
+      <c r="R80" s="155"/>
+      <c r="S80" s="155"/>
+      <c r="T80" s="155"/>
+      <c r="U80" s="155"/>
+      <c r="V80" s="156"/>
+      <c r="W80" s="93"/>
+      <c r="X80" s="94"/>
     </row>
     <row r="81" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q81" s="174"/>
-      <c r="R81" s="175"/>
-      <c r="S81" s="175"/>
-      <c r="T81" s="175"/>
-      <c r="U81" s="175"/>
-      <c r="V81" s="176"/>
-      <c r="W81" s="118"/>
-      <c r="X81" s="119"/>
+      <c r="Q81" s="154"/>
+      <c r="R81" s="155"/>
+      <c r="S81" s="155"/>
+      <c r="T81" s="155"/>
+      <c r="U81" s="155"/>
+      <c r="V81" s="156"/>
+      <c r="W81" s="93"/>
+      <c r="X81" s="94"/>
     </row>
     <row r="82" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q82" s="174"/>
-      <c r="R82" s="175"/>
-      <c r="S82" s="175"/>
-      <c r="T82" s="175"/>
-      <c r="U82" s="175"/>
-      <c r="V82" s="176"/>
-      <c r="W82" s="118"/>
-      <c r="X82" s="119"/>
+      <c r="Q82" s="154"/>
+      <c r="R82" s="155"/>
+      <c r="S82" s="155"/>
+      <c r="T82" s="155"/>
+      <c r="U82" s="155"/>
+      <c r="V82" s="156"/>
+      <c r="W82" s="93"/>
+      <c r="X82" s="94"/>
     </row>
     <row r="83" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q83" s="174"/>
-      <c r="R83" s="175"/>
-      <c r="S83" s="175"/>
-      <c r="T83" s="175"/>
-      <c r="U83" s="175"/>
-      <c r="V83" s="176"/>
-      <c r="W83" s="118"/>
-      <c r="X83" s="119"/>
+      <c r="Q83" s="154"/>
+      <c r="R83" s="155"/>
+      <c r="S83" s="155"/>
+      <c r="T83" s="155"/>
+      <c r="U83" s="155"/>
+      <c r="V83" s="156"/>
+      <c r="W83" s="93"/>
+      <c r="X83" s="94"/>
     </row>
     <row r="84" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q84" s="174"/>
-      <c r="R84" s="175"/>
-      <c r="S84" s="175"/>
-      <c r="T84" s="175"/>
-      <c r="U84" s="175"/>
-      <c r="V84" s="176"/>
-      <c r="W84" s="118"/>
-      <c r="X84" s="119"/>
+      <c r="Q84" s="154"/>
+      <c r="R84" s="155"/>
+      <c r="S84" s="155"/>
+      <c r="T84" s="155"/>
+      <c r="U84" s="155"/>
+      <c r="V84" s="156"/>
+      <c r="W84" s="93"/>
+      <c r="X84" s="94"/>
     </row>
     <row r="85" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q85" s="174"/>
-      <c r="R85" s="175"/>
-      <c r="S85" s="175"/>
-      <c r="T85" s="175"/>
-      <c r="U85" s="175"/>
-      <c r="V85" s="176"/>
-      <c r="W85" s="118"/>
-      <c r="X85" s="119"/>
+      <c r="Q85" s="154"/>
+      <c r="R85" s="155"/>
+      <c r="S85" s="155"/>
+      <c r="T85" s="155"/>
+      <c r="U85" s="155"/>
+      <c r="V85" s="156"/>
+      <c r="W85" s="93"/>
+      <c r="X85" s="94"/>
     </row>
     <row r="86" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q86" s="174"/>
-      <c r="R86" s="175"/>
-      <c r="S86" s="175"/>
-      <c r="T86" s="175"/>
-      <c r="U86" s="175"/>
-      <c r="V86" s="176"/>
-      <c r="W86" s="118"/>
-      <c r="X86" s="119"/>
+      <c r="Q86" s="154"/>
+      <c r="R86" s="155"/>
+      <c r="S86" s="155"/>
+      <c r="T86" s="155"/>
+      <c r="U86" s="155"/>
+      <c r="V86" s="156"/>
+      <c r="W86" s="93"/>
+      <c r="X86" s="94"/>
     </row>
     <row r="87" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q87" s="174"/>
-      <c r="R87" s="175"/>
-      <c r="S87" s="175"/>
-      <c r="T87" s="175"/>
-      <c r="U87" s="175"/>
-      <c r="V87" s="176"/>
-      <c r="W87" s="118"/>
-      <c r="X87" s="119"/>
+      <c r="Q87" s="154"/>
+      <c r="R87" s="155"/>
+      <c r="S87" s="155"/>
+      <c r="T87" s="155"/>
+      <c r="U87" s="155"/>
+      <c r="V87" s="156"/>
+      <c r="W87" s="93"/>
+      <c r="X87" s="94"/>
     </row>
     <row r="88" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q88" s="174"/>
-      <c r="R88" s="175"/>
-      <c r="S88" s="175"/>
-      <c r="T88" s="175"/>
-      <c r="U88" s="175"/>
-      <c r="V88" s="176"/>
-      <c r="W88" s="118"/>
-      <c r="X88" s="119"/>
+      <c r="Q88" s="154"/>
+      <c r="R88" s="155"/>
+      <c r="S88" s="155"/>
+      <c r="T88" s="155"/>
+      <c r="U88" s="155"/>
+      <c r="V88" s="156"/>
+      <c r="W88" s="93"/>
+      <c r="X88" s="94"/>
     </row>
     <row r="89" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q89" s="174"/>
-      <c r="R89" s="175"/>
-      <c r="S89" s="175"/>
-      <c r="T89" s="175"/>
-      <c r="U89" s="175"/>
-      <c r="V89" s="176"/>
-      <c r="W89" s="118"/>
-      <c r="X89" s="119"/>
+      <c r="Q89" s="154"/>
+      <c r="R89" s="155"/>
+      <c r="S89" s="155"/>
+      <c r="T89" s="155"/>
+      <c r="U89" s="155"/>
+      <c r="V89" s="156"/>
+      <c r="W89" s="93"/>
+      <c r="X89" s="94"/>
     </row>
     <row r="90" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q90" s="174"/>
-      <c r="R90" s="175"/>
-      <c r="S90" s="175"/>
-      <c r="T90" s="175"/>
-      <c r="U90" s="175"/>
-      <c r="V90" s="176"/>
-      <c r="W90" s="118"/>
-      <c r="X90" s="119"/>
+      <c r="Q90" s="154"/>
+      <c r="R90" s="155"/>
+      <c r="S90" s="155"/>
+      <c r="T90" s="155"/>
+      <c r="U90" s="155"/>
+      <c r="V90" s="156"/>
+      <c r="W90" s="93"/>
+      <c r="X90" s="94"/>
     </row>
     <row r="91" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q91" s="174"/>
-      <c r="R91" s="175"/>
-      <c r="S91" s="175"/>
-      <c r="T91" s="175"/>
-      <c r="U91" s="175"/>
-      <c r="V91" s="176"/>
-      <c r="W91" s="118"/>
-      <c r="X91" s="119"/>
+      <c r="Q91" s="154"/>
+      <c r="R91" s="155"/>
+      <c r="S91" s="155"/>
+      <c r="T91" s="155"/>
+      <c r="U91" s="155"/>
+      <c r="V91" s="156"/>
+      <c r="W91" s="93"/>
+      <c r="X91" s="94"/>
     </row>
     <row r="92" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q92" s="174"/>
-      <c r="R92" s="175"/>
-      <c r="S92" s="175"/>
-      <c r="T92" s="175"/>
-      <c r="U92" s="175"/>
-      <c r="V92" s="176"/>
-      <c r="W92" s="118"/>
-      <c r="X92" s="119"/>
+      <c r="Q92" s="154"/>
+      <c r="R92" s="155"/>
+      <c r="S92" s="155"/>
+      <c r="T92" s="155"/>
+      <c r="U92" s="155"/>
+      <c r="V92" s="156"/>
+      <c r="W92" s="93"/>
+      <c r="X92" s="94"/>
     </row>
     <row r="93" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q93" s="174"/>
-      <c r="R93" s="175"/>
-      <c r="S93" s="175"/>
-      <c r="T93" s="175"/>
-      <c r="U93" s="175"/>
-      <c r="V93" s="176"/>
-      <c r="W93" s="118"/>
-      <c r="X93" s="119"/>
+      <c r="Q93" s="154"/>
+      <c r="R93" s="155"/>
+      <c r="S93" s="155"/>
+      <c r="T93" s="155"/>
+      <c r="U93" s="155"/>
+      <c r="V93" s="156"/>
+      <c r="W93" s="93"/>
+      <c r="X93" s="94"/>
     </row>
     <row r="94" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q94" s="174"/>
-      <c r="R94" s="175"/>
-      <c r="S94" s="175"/>
-      <c r="T94" s="175"/>
-      <c r="U94" s="175"/>
-      <c r="V94" s="176"/>
-      <c r="W94" s="118"/>
-      <c r="X94" s="119"/>
+      <c r="Q94" s="154"/>
+      <c r="R94" s="155"/>
+      <c r="S94" s="155"/>
+      <c r="T94" s="155"/>
+      <c r="U94" s="155"/>
+      <c r="V94" s="156"/>
+      <c r="W94" s="93"/>
+      <c r="X94" s="94"/>
     </row>
     <row r="95" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q95" s="174"/>
-      <c r="R95" s="175"/>
-      <c r="S95" s="175"/>
-      <c r="T95" s="175"/>
-      <c r="U95" s="175"/>
-      <c r="V95" s="176"/>
-      <c r="W95" s="118"/>
-      <c r="X95" s="119"/>
+      <c r="Q95" s="154"/>
+      <c r="R95" s="155"/>
+      <c r="S95" s="155"/>
+      <c r="T95" s="155"/>
+      <c r="U95" s="155"/>
+      <c r="V95" s="156"/>
+      <c r="W95" s="93"/>
+      <c r="X95" s="94"/>
     </row>
     <row r="96" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q96" s="174"/>
-      <c r="R96" s="175"/>
-      <c r="S96" s="175"/>
-      <c r="T96" s="175"/>
-      <c r="U96" s="175"/>
-      <c r="V96" s="176"/>
-      <c r="W96" s="118"/>
-      <c r="X96" s="119"/>
+      <c r="Q96" s="154"/>
+      <c r="R96" s="155"/>
+      <c r="S96" s="155"/>
+      <c r="T96" s="155"/>
+      <c r="U96" s="155"/>
+      <c r="V96" s="156"/>
+      <c r="W96" s="93"/>
+      <c r="X96" s="94"/>
     </row>
     <row r="97" spans="17:26" x14ac:dyDescent="0.3">
-      <c r="Q97" s="174"/>
-      <c r="R97" s="175"/>
-      <c r="S97" s="175"/>
-      <c r="T97" s="175"/>
-      <c r="U97" s="175"/>
-      <c r="V97" s="176"/>
-      <c r="W97" s="118"/>
-      <c r="X97" s="119"/>
+      <c r="Q97" s="154"/>
+      <c r="R97" s="155"/>
+      <c r="S97" s="155"/>
+      <c r="T97" s="155"/>
+      <c r="U97" s="155"/>
+      <c r="V97" s="156"/>
+      <c r="W97" s="93"/>
+      <c r="X97" s="94"/>
     </row>
     <row r="98" spans="17:26" x14ac:dyDescent="0.3">
-      <c r="Q98" s="174"/>
-      <c r="R98" s="175"/>
-      <c r="S98" s="175"/>
-      <c r="T98" s="175"/>
-      <c r="U98" s="175"/>
-      <c r="V98" s="176"/>
-      <c r="W98" s="118"/>
-      <c r="X98" s="119"/>
+      <c r="Q98" s="154"/>
+      <c r="R98" s="155"/>
+      <c r="S98" s="155"/>
+      <c r="T98" s="155"/>
+      <c r="U98" s="155"/>
+      <c r="V98" s="156"/>
+      <c r="W98" s="93"/>
+      <c r="X98" s="94"/>
     </row>
     <row r="99" spans="17:26" x14ac:dyDescent="0.3">
-      <c r="Q99" s="174"/>
-      <c r="R99" s="175"/>
-      <c r="S99" s="175"/>
-      <c r="T99" s="175"/>
-      <c r="U99" s="175"/>
-      <c r="V99" s="176"/>
-      <c r="W99" s="118"/>
-      <c r="X99" s="119"/>
+      <c r="Q99" s="154"/>
+      <c r="R99" s="155"/>
+      <c r="S99" s="155"/>
+      <c r="T99" s="155"/>
+      <c r="U99" s="155"/>
+      <c r="V99" s="156"/>
+      <c r="W99" s="93"/>
+      <c r="X99" s="94"/>
     </row>
     <row r="100" spans="17:26" x14ac:dyDescent="0.3">
-      <c r="Q100" s="174"/>
-      <c r="R100" s="175"/>
-      <c r="S100" s="175"/>
-      <c r="T100" s="175"/>
-      <c r="U100" s="175"/>
-      <c r="V100" s="176"/>
-      <c r="W100" s="118"/>
-      <c r="X100" s="119"/>
+      <c r="Q100" s="154"/>
+      <c r="R100" s="155"/>
+      <c r="S100" s="155"/>
+      <c r="T100" s="155"/>
+      <c r="U100" s="155"/>
+      <c r="V100" s="156"/>
+      <c r="W100" s="93"/>
+      <c r="X100" s="94"/>
     </row>
     <row r="101" spans="17:26" x14ac:dyDescent="0.3">
-      <c r="Q101" s="174"/>
-      <c r="R101" s="175"/>
-      <c r="S101" s="175"/>
-      <c r="T101" s="175"/>
-      <c r="U101" s="175"/>
-      <c r="V101" s="176"/>
-      <c r="W101" s="118"/>
-      <c r="X101" s="119"/>
+      <c r="Q101" s="154"/>
+      <c r="R101" s="155"/>
+      <c r="S101" s="155"/>
+      <c r="T101" s="155"/>
+      <c r="U101" s="155"/>
+      <c r="V101" s="156"/>
+      <c r="W101" s="93"/>
+      <c r="X101" s="94"/>
     </row>
     <row r="102" spans="17:26" x14ac:dyDescent="0.3">
-      <c r="Q102" s="174"/>
-      <c r="R102" s="175"/>
-      <c r="S102" s="175"/>
-      <c r="T102" s="175"/>
-      <c r="U102" s="175"/>
-      <c r="V102" s="176"/>
-      <c r="W102" s="118"/>
-      <c r="X102" s="119"/>
+      <c r="Q102" s="154"/>
+      <c r="R102" s="155"/>
+      <c r="S102" s="155"/>
+      <c r="T102" s="155"/>
+      <c r="U102" s="155"/>
+      <c r="V102" s="156"/>
+      <c r="W102" s="93"/>
+      <c r="X102" s="94"/>
     </row>
     <row r="103" spans="17:26" x14ac:dyDescent="0.3">
-      <c r="Q103" s="174"/>
-      <c r="R103" s="175"/>
-      <c r="S103" s="175"/>
-      <c r="T103" s="175"/>
-      <c r="U103" s="175"/>
-      <c r="V103" s="176"/>
-      <c r="W103" s="118"/>
-      <c r="X103" s="119"/>
+      <c r="Q103" s="154"/>
+      <c r="R103" s="155"/>
+      <c r="S103" s="155"/>
+      <c r="T103" s="155"/>
+      <c r="U103" s="155"/>
+      <c r="V103" s="156"/>
+      <c r="W103" s="93"/>
+      <c r="X103" s="94"/>
     </row>
     <row r="104" spans="17:26" x14ac:dyDescent="0.3">
-      <c r="Q104" s="174"/>
-      <c r="R104" s="175"/>
-      <c r="S104" s="175"/>
-      <c r="T104" s="175"/>
-      <c r="U104" s="175"/>
-      <c r="V104" s="176"/>
-      <c r="W104" s="118"/>
-      <c r="X104" s="119"/>
+      <c r="Q104" s="154"/>
+      <c r="R104" s="155"/>
+      <c r="S104" s="155"/>
+      <c r="T104" s="155"/>
+      <c r="U104" s="155"/>
+      <c r="V104" s="156"/>
+      <c r="W104" s="93"/>
+      <c r="X104" s="94"/>
     </row>
     <row r="105" spans="17:26" x14ac:dyDescent="0.3">
-      <c r="Q105" s="174"/>
-      <c r="R105" s="175"/>
-      <c r="S105" s="175"/>
-      <c r="T105" s="175"/>
-      <c r="U105" s="175"/>
-      <c r="V105" s="176"/>
-      <c r="W105" s="118"/>
-      <c r="X105" s="119"/>
+      <c r="Q105" s="154"/>
+      <c r="R105" s="155"/>
+      <c r="S105" s="155"/>
+      <c r="T105" s="155"/>
+      <c r="U105" s="155"/>
+      <c r="V105" s="156"/>
+      <c r="W105" s="93"/>
+      <c r="X105" s="94"/>
     </row>
     <row r="106" spans="17:26" x14ac:dyDescent="0.3">
-      <c r="Q106" s="174"/>
-      <c r="R106" s="175"/>
-      <c r="S106" s="175"/>
-      <c r="T106" s="175"/>
-      <c r="U106" s="175"/>
-      <c r="V106" s="176"/>
-      <c r="W106" s="118"/>
-      <c r="X106" s="119"/>
+      <c r="Q106" s="154"/>
+      <c r="R106" s="155"/>
+      <c r="S106" s="155"/>
+      <c r="T106" s="155"/>
+      <c r="U106" s="155"/>
+      <c r="V106" s="156"/>
+      <c r="W106" s="93"/>
+      <c r="X106" s="94"/>
     </row>
     <row r="107" spans="17:26" x14ac:dyDescent="0.3">
-      <c r="Q107" s="174"/>
-      <c r="R107" s="175"/>
-      <c r="S107" s="175"/>
-      <c r="T107" s="175"/>
-      <c r="U107" s="175"/>
-      <c r="V107" s="176"/>
-      <c r="W107" s="118"/>
-      <c r="X107" s="119"/>
+      <c r="Q107" s="154"/>
+      <c r="R107" s="155"/>
+      <c r="S107" s="155"/>
+      <c r="T107" s="155"/>
+      <c r="U107" s="155"/>
+      <c r="V107" s="156"/>
+      <c r="W107" s="93"/>
+      <c r="X107" s="94"/>
     </row>
     <row r="108" spans="17:26" x14ac:dyDescent="0.3">
-      <c r="Q108" s="179"/>
-      <c r="R108" s="180"/>
-      <c r="S108" s="180"/>
-      <c r="T108" s="180"/>
-      <c r="U108" s="180"/>
-      <c r="V108" s="181"/>
-      <c r="W108" s="114"/>
-      <c r="X108" s="140"/>
+      <c r="Q108" s="157"/>
+      <c r="R108" s="158"/>
+      <c r="S108" s="158"/>
+      <c r="T108" s="158"/>
+      <c r="U108" s="158"/>
+      <c r="V108" s="159"/>
+      <c r="W108" s="90"/>
+      <c r="X108" s="107"/>
     </row>
     <row r="109" spans="17:26" x14ac:dyDescent="0.3">
-      <c r="Q109" s="174"/>
-      <c r="R109" s="175"/>
-      <c r="S109" s="175"/>
-      <c r="T109" s="175"/>
-      <c r="U109" s="175"/>
-      <c r="V109" s="176"/>
-      <c r="W109" s="118"/>
-      <c r="X109" s="119"/>
+      <c r="Q109" s="154"/>
+      <c r="R109" s="155"/>
+      <c r="S109" s="155"/>
+      <c r="T109" s="155"/>
+      <c r="U109" s="155"/>
+      <c r="V109" s="156"/>
+      <c r="W109" s="93"/>
+      <c r="X109" s="94"/>
       <c r="Z109" s="9" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="110" spans="17:26" x14ac:dyDescent="0.3">
-      <c r="Q110" s="174"/>
-      <c r="R110" s="175"/>
-      <c r="S110" s="175"/>
-      <c r="T110" s="175"/>
-      <c r="U110" s="175"/>
-      <c r="V110" s="176"/>
-      <c r="W110" s="118"/>
-      <c r="X110" s="119"/>
+      <c r="Q110" s="154"/>
+      <c r="R110" s="155"/>
+      <c r="S110" s="155"/>
+      <c r="T110" s="155"/>
+      <c r="U110" s="155"/>
+      <c r="V110" s="156"/>
+      <c r="W110" s="93"/>
+      <c r="X110" s="94"/>
     </row>
     <row r="111" spans="17:26" x14ac:dyDescent="0.3">
-      <c r="Q111" s="174"/>
-      <c r="R111" s="175"/>
-      <c r="S111" s="175"/>
-      <c r="T111" s="175"/>
-      <c r="U111" s="175"/>
-      <c r="V111" s="176"/>
-      <c r="W111" s="118"/>
-      <c r="X111" s="119"/>
+      <c r="Q111" s="154"/>
+      <c r="R111" s="155"/>
+      <c r="S111" s="155"/>
+      <c r="T111" s="155"/>
+      <c r="U111" s="155"/>
+      <c r="V111" s="156"/>
+      <c r="W111" s="93"/>
+      <c r="X111" s="94"/>
     </row>
     <row r="112" spans="17:26" x14ac:dyDescent="0.3">
-      <c r="Q112" s="261"/>
-      <c r="R112" s="262"/>
-      <c r="S112" s="262"/>
-      <c r="T112" s="262"/>
-      <c r="U112" s="262"/>
-      <c r="V112" s="263"/>
-      <c r="W112" s="118"/>
-      <c r="X112" s="119"/>
+      <c r="Q112" s="197"/>
+      <c r="R112" s="198"/>
+      <c r="S112" s="198"/>
+      <c r="T112" s="198"/>
+      <c r="U112" s="198"/>
+      <c r="V112" s="199"/>
+      <c r="W112" s="93"/>
+      <c r="X112" s="94"/>
     </row>
     <row r="113" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q113" s="174"/>
-      <c r="R113" s="175"/>
-      <c r="S113" s="175"/>
-      <c r="T113" s="175"/>
-      <c r="U113" s="175"/>
-      <c r="V113" s="176"/>
-      <c r="W113" s="118"/>
-      <c r="X113" s="119"/>
+      <c r="Q113" s="154"/>
+      <c r="R113" s="155"/>
+      <c r="S113" s="155"/>
+      <c r="T113" s="155"/>
+      <c r="U113" s="155"/>
+      <c r="V113" s="156"/>
+      <c r="W113" s="93"/>
+      <c r="X113" s="94"/>
     </row>
     <row r="114" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q114" s="174"/>
-      <c r="R114" s="175"/>
-      <c r="S114" s="175"/>
-      <c r="T114" s="175"/>
-      <c r="U114" s="175"/>
-      <c r="V114" s="176"/>
-      <c r="W114" s="118"/>
-      <c r="X114" s="119"/>
+      <c r="Q114" s="154"/>
+      <c r="R114" s="155"/>
+      <c r="S114" s="155"/>
+      <c r="T114" s="155"/>
+      <c r="U114" s="155"/>
+      <c r="V114" s="156"/>
+      <c r="W114" s="93"/>
+      <c r="X114" s="94"/>
     </row>
     <row r="115" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q115" s="174"/>
-      <c r="R115" s="175"/>
-      <c r="S115" s="175"/>
-      <c r="T115" s="175"/>
-      <c r="U115" s="175"/>
-      <c r="V115" s="176"/>
-      <c r="W115" s="118"/>
-      <c r="X115" s="119"/>
+      <c r="Q115" s="154"/>
+      <c r="R115" s="155"/>
+      <c r="S115" s="155"/>
+      <c r="T115" s="155"/>
+      <c r="U115" s="155"/>
+      <c r="V115" s="156"/>
+      <c r="W115" s="93"/>
+      <c r="X115" s="94"/>
     </row>
     <row r="116" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q116" s="174"/>
-      <c r="R116" s="175"/>
-      <c r="S116" s="175"/>
-      <c r="T116" s="175"/>
-      <c r="U116" s="175"/>
-      <c r="V116" s="176"/>
-      <c r="W116" s="118"/>
-      <c r="X116" s="119"/>
+      <c r="Q116" s="154"/>
+      <c r="R116" s="155"/>
+      <c r="S116" s="155"/>
+      <c r="T116" s="155"/>
+      <c r="U116" s="155"/>
+      <c r="V116" s="156"/>
+      <c r="W116" s="93"/>
+      <c r="X116" s="94"/>
     </row>
     <row r="117" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q117" s="174"/>
-      <c r="R117" s="175"/>
-      <c r="S117" s="175"/>
-      <c r="T117" s="175"/>
-      <c r="U117" s="175"/>
-      <c r="V117" s="176"/>
-      <c r="W117" s="118"/>
-      <c r="X117" s="119"/>
+      <c r="Q117" s="154"/>
+      <c r="R117" s="155"/>
+      <c r="S117" s="155"/>
+      <c r="T117" s="155"/>
+      <c r="U117" s="155"/>
+      <c r="V117" s="156"/>
+      <c r="W117" s="93"/>
+      <c r="X117" s="94"/>
     </row>
     <row r="118" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q118" s="174"/>
-      <c r="R118" s="175"/>
-      <c r="S118" s="175"/>
-      <c r="T118" s="175"/>
-      <c r="U118" s="175"/>
-      <c r="V118" s="176"/>
-      <c r="W118" s="118"/>
-      <c r="X118" s="119"/>
+      <c r="Q118" s="154"/>
+      <c r="R118" s="155"/>
+      <c r="S118" s="155"/>
+      <c r="T118" s="155"/>
+      <c r="U118" s="155"/>
+      <c r="V118" s="156"/>
+      <c r="W118" s="93"/>
+      <c r="X118" s="94"/>
     </row>
     <row r="119" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q119" s="174"/>
-      <c r="R119" s="175"/>
-      <c r="S119" s="175"/>
-      <c r="T119" s="175"/>
-      <c r="U119" s="175"/>
-      <c r="V119" s="176"/>
-      <c r="W119" s="118"/>
-      <c r="X119" s="119"/>
+      <c r="Q119" s="154"/>
+      <c r="R119" s="155"/>
+      <c r="S119" s="155"/>
+      <c r="T119" s="155"/>
+      <c r="U119" s="155"/>
+      <c r="V119" s="156"/>
+      <c r="W119" s="93"/>
+      <c r="X119" s="94"/>
     </row>
     <row r="120" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q120" s="174"/>
-      <c r="R120" s="175"/>
-      <c r="S120" s="175"/>
-      <c r="T120" s="175"/>
-      <c r="U120" s="175"/>
-      <c r="V120" s="176"/>
-      <c r="W120" s="118"/>
-      <c r="X120" s="119"/>
+      <c r="Q120" s="154"/>
+      <c r="R120" s="155"/>
+      <c r="S120" s="155"/>
+      <c r="T120" s="155"/>
+      <c r="U120" s="155"/>
+      <c r="V120" s="156"/>
+      <c r="W120" s="93"/>
+      <c r="X120" s="94"/>
     </row>
     <row r="121" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q121" s="174"/>
-      <c r="R121" s="175"/>
-      <c r="S121" s="175"/>
-      <c r="T121" s="175"/>
-      <c r="U121" s="175"/>
-      <c r="V121" s="176"/>
-      <c r="W121" s="118"/>
-      <c r="X121" s="119"/>
+      <c r="Q121" s="154"/>
+      <c r="R121" s="155"/>
+      <c r="S121" s="155"/>
+      <c r="T121" s="155"/>
+      <c r="U121" s="155"/>
+      <c r="V121" s="156"/>
+      <c r="W121" s="93"/>
+      <c r="X121" s="94"/>
     </row>
     <row r="122" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q122" s="174"/>
-      <c r="R122" s="175"/>
-      <c r="S122" s="175"/>
-      <c r="T122" s="175"/>
-      <c r="U122" s="175"/>
-      <c r="V122" s="176"/>
-      <c r="W122" s="118"/>
-      <c r="X122" s="119"/>
+      <c r="Q122" s="154"/>
+      <c r="R122" s="155"/>
+      <c r="S122" s="155"/>
+      <c r="T122" s="155"/>
+      <c r="U122" s="155"/>
+      <c r="V122" s="156"/>
+      <c r="W122" s="93"/>
+      <c r="X122" s="94"/>
     </row>
     <row r="123" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q123" s="174"/>
-      <c r="R123" s="175"/>
-      <c r="S123" s="175"/>
-      <c r="T123" s="175"/>
-      <c r="U123" s="175"/>
-      <c r="V123" s="176"/>
-      <c r="W123" s="118"/>
-      <c r="X123" s="119"/>
+      <c r="Q123" s="154"/>
+      <c r="R123" s="155"/>
+      <c r="S123" s="155"/>
+      <c r="T123" s="155"/>
+      <c r="U123" s="155"/>
+      <c r="V123" s="156"/>
+      <c r="W123" s="93"/>
+      <c r="X123" s="94"/>
     </row>
     <row r="124" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q124" s="174"/>
-      <c r="R124" s="175"/>
-      <c r="S124" s="175"/>
-      <c r="T124" s="175"/>
-      <c r="U124" s="175"/>
-      <c r="V124" s="176"/>
-      <c r="W124" s="118"/>
-      <c r="X124" s="119"/>
+      <c r="Q124" s="154"/>
+      <c r="R124" s="155"/>
+      <c r="S124" s="155"/>
+      <c r="T124" s="155"/>
+      <c r="U124" s="155"/>
+      <c r="V124" s="156"/>
+      <c r="W124" s="93"/>
+      <c r="X124" s="94"/>
     </row>
     <row r="125" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q125" s="174"/>
-      <c r="R125" s="175"/>
-      <c r="S125" s="175"/>
-      <c r="T125" s="175"/>
-      <c r="U125" s="175"/>
-      <c r="V125" s="176"/>
-      <c r="W125" s="118"/>
-      <c r="X125" s="119"/>
+      <c r="Q125" s="154"/>
+      <c r="R125" s="155"/>
+      <c r="S125" s="155"/>
+      <c r="T125" s="155"/>
+      <c r="U125" s="155"/>
+      <c r="V125" s="156"/>
+      <c r="W125" s="93"/>
+      <c r="X125" s="94"/>
     </row>
     <row r="126" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q126" s="174"/>
-      <c r="R126" s="175"/>
-      <c r="S126" s="175"/>
-      <c r="T126" s="175"/>
-      <c r="U126" s="175"/>
-      <c r="V126" s="176"/>
-      <c r="W126" s="118"/>
-      <c r="X126" s="119"/>
+      <c r="Q126" s="154"/>
+      <c r="R126" s="155"/>
+      <c r="S126" s="155"/>
+      <c r="T126" s="155"/>
+      <c r="U126" s="155"/>
+      <c r="V126" s="156"/>
+      <c r="W126" s="93"/>
+      <c r="X126" s="94"/>
     </row>
     <row r="127" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q127" s="261"/>
-      <c r="R127" s="262"/>
-      <c r="S127" s="262"/>
-      <c r="T127" s="262"/>
-      <c r="U127" s="262"/>
-      <c r="V127" s="263"/>
-      <c r="W127" s="118"/>
-      <c r="X127" s="119"/>
+      <c r="Q127" s="197"/>
+      <c r="R127" s="198"/>
+      <c r="S127" s="198"/>
+      <c r="T127" s="198"/>
+      <c r="U127" s="198"/>
+      <c r="V127" s="199"/>
+      <c r="W127" s="93"/>
+      <c r="X127" s="94"/>
     </row>
     <row r="128" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q128" s="174"/>
-      <c r="R128" s="175"/>
-      <c r="S128" s="175"/>
-      <c r="T128" s="175"/>
-      <c r="U128" s="175"/>
-      <c r="V128" s="176"/>
-      <c r="W128" s="118"/>
-      <c r="X128" s="119"/>
+      <c r="Q128" s="154"/>
+      <c r="R128" s="155"/>
+      <c r="S128" s="155"/>
+      <c r="T128" s="155"/>
+      <c r="U128" s="155"/>
+      <c r="V128" s="156"/>
+      <c r="W128" s="93"/>
+      <c r="X128" s="94"/>
     </row>
     <row r="129" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q129" s="174"/>
-      <c r="R129" s="175"/>
-      <c r="S129" s="175"/>
-      <c r="T129" s="175"/>
-      <c r="U129" s="175"/>
-      <c r="V129" s="176"/>
-      <c r="W129" s="118"/>
-      <c r="X129" s="119"/>
+      <c r="Q129" s="154"/>
+      <c r="R129" s="155"/>
+      <c r="S129" s="155"/>
+      <c r="T129" s="155"/>
+      <c r="U129" s="155"/>
+      <c r="V129" s="156"/>
+      <c r="W129" s="93"/>
+      <c r="X129" s="94"/>
     </row>
     <row r="130" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q130" s="174"/>
-      <c r="R130" s="175"/>
-      <c r="S130" s="175"/>
-      <c r="T130" s="175"/>
-      <c r="U130" s="175"/>
-      <c r="V130" s="176"/>
-      <c r="W130" s="118"/>
-      <c r="X130" s="119"/>
+      <c r="Q130" s="154"/>
+      <c r="R130" s="155"/>
+      <c r="S130" s="155"/>
+      <c r="T130" s="155"/>
+      <c r="U130" s="155"/>
+      <c r="V130" s="156"/>
+      <c r="W130" s="93"/>
+      <c r="X130" s="94"/>
     </row>
     <row r="131" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q131" s="174"/>
-      <c r="R131" s="175"/>
-      <c r="S131" s="175"/>
-      <c r="T131" s="175"/>
-      <c r="U131" s="175"/>
-      <c r="V131" s="176"/>
-      <c r="W131" s="118"/>
-      <c r="X131" s="119"/>
+      <c r="Q131" s="154"/>
+      <c r="R131" s="155"/>
+      <c r="S131" s="155"/>
+      <c r="T131" s="155"/>
+      <c r="U131" s="155"/>
+      <c r="V131" s="156"/>
+      <c r="W131" s="93"/>
+      <c r="X131" s="94"/>
     </row>
     <row r="132" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q132" s="174"/>
-      <c r="R132" s="175"/>
-      <c r="S132" s="175"/>
-      <c r="T132" s="175"/>
-      <c r="U132" s="175"/>
-      <c r="V132" s="176"/>
-      <c r="W132" s="118"/>
-      <c r="X132" s="119"/>
+      <c r="Q132" s="154"/>
+      <c r="R132" s="155"/>
+      <c r="S132" s="155"/>
+      <c r="T132" s="155"/>
+      <c r="U132" s="155"/>
+      <c r="V132" s="156"/>
+      <c r="W132" s="93"/>
+      <c r="X132" s="94"/>
     </row>
     <row r="133" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q133" s="174"/>
-      <c r="R133" s="175"/>
-      <c r="S133" s="175"/>
-      <c r="T133" s="175"/>
-      <c r="U133" s="175"/>
-      <c r="V133" s="176"/>
-      <c r="W133" s="118"/>
-      <c r="X133" s="119"/>
+      <c r="Q133" s="154"/>
+      <c r="R133" s="155"/>
+      <c r="S133" s="155"/>
+      <c r="T133" s="155"/>
+      <c r="U133" s="155"/>
+      <c r="V133" s="156"/>
+      <c r="W133" s="93"/>
+      <c r="X133" s="94"/>
     </row>
     <row r="134" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q134" s="174"/>
-      <c r="R134" s="175"/>
-      <c r="S134" s="175"/>
-      <c r="T134" s="175"/>
-      <c r="U134" s="175"/>
-      <c r="V134" s="176"/>
-      <c r="W134" s="118"/>
-      <c r="X134" s="119"/>
+      <c r="Q134" s="154"/>
+      <c r="R134" s="155"/>
+      <c r="S134" s="155"/>
+      <c r="T134" s="155"/>
+      <c r="U134" s="155"/>
+      <c r="V134" s="156"/>
+      <c r="W134" s="93"/>
+      <c r="X134" s="94"/>
     </row>
     <row r="135" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q135" s="174"/>
-      <c r="R135" s="175"/>
-      <c r="S135" s="175"/>
-      <c r="T135" s="175"/>
-      <c r="U135" s="175"/>
-      <c r="V135" s="176"/>
-      <c r="W135" s="118"/>
-      <c r="X135" s="119"/>
+      <c r="Q135" s="154"/>
+      <c r="R135" s="155"/>
+      <c r="S135" s="155"/>
+      <c r="T135" s="155"/>
+      <c r="U135" s="155"/>
+      <c r="V135" s="156"/>
+      <c r="W135" s="93"/>
+      <c r="X135" s="94"/>
     </row>
     <row r="136" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q136" s="174"/>
-      <c r="R136" s="175"/>
-      <c r="S136" s="175"/>
-      <c r="T136" s="175"/>
-      <c r="U136" s="175"/>
-      <c r="V136" s="176"/>
-      <c r="W136" s="118"/>
-      <c r="X136" s="119"/>
+      <c r="Q136" s="154"/>
+      <c r="R136" s="155"/>
+      <c r="S136" s="155"/>
+      <c r="T136" s="155"/>
+      <c r="U136" s="155"/>
+      <c r="V136" s="156"/>
+      <c r="W136" s="93"/>
+      <c r="X136" s="94"/>
     </row>
     <row r="137" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q137" s="174"/>
-      <c r="R137" s="175"/>
-      <c r="S137" s="175"/>
-      <c r="T137" s="175"/>
-      <c r="U137" s="175"/>
-      <c r="V137" s="176"/>
-      <c r="W137" s="118"/>
-      <c r="X137" s="119"/>
+      <c r="Q137" s="154"/>
+      <c r="R137" s="155"/>
+      <c r="S137" s="155"/>
+      <c r="T137" s="155"/>
+      <c r="U137" s="155"/>
+      <c r="V137" s="156"/>
+      <c r="W137" s="93"/>
+      <c r="X137" s="94"/>
     </row>
     <row r="138" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q138" s="174"/>
-      <c r="R138" s="175"/>
-      <c r="S138" s="175"/>
-      <c r="T138" s="175"/>
-      <c r="U138" s="175"/>
-      <c r="V138" s="176"/>
-      <c r="W138" s="118"/>
-      <c r="X138" s="119"/>
+      <c r="Q138" s="154"/>
+      <c r="R138" s="155"/>
+      <c r="S138" s="155"/>
+      <c r="T138" s="155"/>
+      <c r="U138" s="155"/>
+      <c r="V138" s="156"/>
+      <c r="W138" s="93"/>
+      <c r="X138" s="94"/>
     </row>
     <row r="139" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q139" s="174"/>
-      <c r="R139" s="175"/>
-      <c r="S139" s="175"/>
-      <c r="T139" s="175"/>
-      <c r="U139" s="175"/>
-      <c r="V139" s="176"/>
-      <c r="W139" s="118"/>
-      <c r="X139" s="119"/>
+      <c r="Q139" s="154"/>
+      <c r="R139" s="155"/>
+      <c r="S139" s="155"/>
+      <c r="T139" s="155"/>
+      <c r="U139" s="155"/>
+      <c r="V139" s="156"/>
+      <c r="W139" s="93"/>
+      <c r="X139" s="94"/>
     </row>
     <row r="140" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q140" s="174"/>
-      <c r="R140" s="175"/>
-      <c r="S140" s="175"/>
-      <c r="T140" s="175"/>
-      <c r="U140" s="175"/>
-      <c r="V140" s="176"/>
-      <c r="W140" s="118"/>
-      <c r="X140" s="119"/>
+      <c r="Q140" s="154"/>
+      <c r="R140" s="155"/>
+      <c r="S140" s="155"/>
+      <c r="T140" s="155"/>
+      <c r="U140" s="155"/>
+      <c r="V140" s="156"/>
+      <c r="W140" s="93"/>
+      <c r="X140" s="94"/>
     </row>
     <row r="141" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q141" s="174"/>
-      <c r="R141" s="175"/>
-      <c r="S141" s="175"/>
-      <c r="T141" s="175"/>
-      <c r="U141" s="175"/>
-      <c r="V141" s="176"/>
-      <c r="W141" s="118"/>
-      <c r="X141" s="119"/>
+      <c r="Q141" s="154"/>
+      <c r="R141" s="155"/>
+      <c r="S141" s="155"/>
+      <c r="T141" s="155"/>
+      <c r="U141" s="155"/>
+      <c r="V141" s="156"/>
+      <c r="W141" s="93"/>
+      <c r="X141" s="94"/>
     </row>
     <row r="142" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q142" s="174"/>
-      <c r="R142" s="175"/>
-      <c r="S142" s="175"/>
-      <c r="T142" s="175"/>
-      <c r="U142" s="175"/>
-      <c r="V142" s="176"/>
-      <c r="W142" s="118"/>
-      <c r="X142" s="119"/>
+      <c r="Q142" s="154"/>
+      <c r="R142" s="155"/>
+      <c r="S142" s="155"/>
+      <c r="T142" s="155"/>
+      <c r="U142" s="155"/>
+      <c r="V142" s="156"/>
+      <c r="W142" s="93"/>
+      <c r="X142" s="94"/>
     </row>
     <row r="143" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q143" s="174"/>
-      <c r="R143" s="175"/>
-      <c r="S143" s="175"/>
-      <c r="T143" s="175"/>
-      <c r="U143" s="175"/>
-      <c r="V143" s="176"/>
-      <c r="W143" s="118"/>
-      <c r="X143" s="119"/>
+      <c r="Q143" s="154"/>
+      <c r="R143" s="155"/>
+      <c r="S143" s="155"/>
+      <c r="T143" s="155"/>
+      <c r="U143" s="155"/>
+      <c r="V143" s="156"/>
+      <c r="W143" s="93"/>
+      <c r="X143" s="94"/>
     </row>
     <row r="144" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q144" s="174"/>
-      <c r="R144" s="175"/>
-      <c r="S144" s="175"/>
-      <c r="T144" s="175"/>
-      <c r="U144" s="175"/>
-      <c r="V144" s="176"/>
-      <c r="W144" s="118"/>
-      <c r="X144" s="119"/>
+      <c r="Q144" s="154"/>
+      <c r="R144" s="155"/>
+      <c r="S144" s="155"/>
+      <c r="T144" s="155"/>
+      <c r="U144" s="155"/>
+      <c r="V144" s="156"/>
+      <c r="W144" s="93"/>
+      <c r="X144" s="94"/>
     </row>
     <row r="145" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q145" s="174"/>
-      <c r="R145" s="175"/>
-      <c r="S145" s="175"/>
-      <c r="T145" s="175"/>
-      <c r="U145" s="175"/>
-      <c r="V145" s="176"/>
-      <c r="W145" s="118"/>
-      <c r="X145" s="119"/>
+      <c r="Q145" s="154"/>
+      <c r="R145" s="155"/>
+      <c r="S145" s="155"/>
+      <c r="T145" s="155"/>
+      <c r="U145" s="155"/>
+      <c r="V145" s="156"/>
+      <c r="W145" s="93"/>
+      <c r="X145" s="94"/>
     </row>
     <row r="146" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q146" s="174"/>
-      <c r="R146" s="175"/>
-      <c r="S146" s="175"/>
-      <c r="T146" s="175"/>
-      <c r="U146" s="175"/>
-      <c r="V146" s="176"/>
-      <c r="W146" s="118"/>
-      <c r="X146" s="119"/>
+      <c r="Q146" s="154"/>
+      <c r="R146" s="155"/>
+      <c r="S146" s="155"/>
+      <c r="T146" s="155"/>
+      <c r="U146" s="155"/>
+      <c r="V146" s="156"/>
+      <c r="W146" s="93"/>
+      <c r="X146" s="94"/>
     </row>
     <row r="147" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q147" s="174"/>
-      <c r="R147" s="175"/>
-      <c r="S147" s="175"/>
-      <c r="T147" s="175"/>
-      <c r="U147" s="175"/>
-      <c r="V147" s="176"/>
-      <c r="W147" s="118"/>
-      <c r="X147" s="119"/>
+      <c r="Q147" s="154"/>
+      <c r="R147" s="155"/>
+      <c r="S147" s="155"/>
+      <c r="T147" s="155"/>
+      <c r="U147" s="155"/>
+      <c r="V147" s="156"/>
+      <c r="W147" s="93"/>
+      <c r="X147" s="94"/>
     </row>
     <row r="148" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q148" s="174"/>
-      <c r="R148" s="175"/>
-      <c r="S148" s="175"/>
-      <c r="T148" s="175"/>
-      <c r="U148" s="175"/>
-      <c r="V148" s="176"/>
-      <c r="W148" s="118"/>
-      <c r="X148" s="119"/>
+      <c r="Q148" s="154"/>
+      <c r="R148" s="155"/>
+      <c r="S148" s="155"/>
+      <c r="T148" s="155"/>
+      <c r="U148" s="155"/>
+      <c r="V148" s="156"/>
+      <c r="W148" s="93"/>
+      <c r="X148" s="94"/>
     </row>
     <row r="149" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q149" s="174"/>
-      <c r="R149" s="175"/>
-      <c r="S149" s="175"/>
-      <c r="T149" s="175"/>
-      <c r="U149" s="175"/>
-      <c r="V149" s="176"/>
-      <c r="W149" s="118"/>
-      <c r="X149" s="119"/>
+      <c r="Q149" s="154"/>
+      <c r="R149" s="155"/>
+      <c r="S149" s="155"/>
+      <c r="T149" s="155"/>
+      <c r="U149" s="155"/>
+      <c r="V149" s="156"/>
+      <c r="W149" s="93"/>
+      <c r="X149" s="94"/>
     </row>
     <row r="150" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q150" s="174"/>
-      <c r="R150" s="175"/>
-      <c r="S150" s="175"/>
-      <c r="T150" s="175"/>
-      <c r="U150" s="175"/>
-      <c r="V150" s="176"/>
-      <c r="W150" s="118"/>
-      <c r="X150" s="119"/>
+      <c r="Q150" s="154"/>
+      <c r="R150" s="155"/>
+      <c r="S150" s="155"/>
+      <c r="T150" s="155"/>
+      <c r="U150" s="155"/>
+      <c r="V150" s="156"/>
+      <c r="W150" s="93"/>
+      <c r="X150" s="94"/>
     </row>
     <row r="151" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q151" s="174"/>
-      <c r="R151" s="175"/>
-      <c r="S151" s="175"/>
-      <c r="T151" s="175"/>
-      <c r="U151" s="175"/>
-      <c r="V151" s="176"/>
-      <c r="W151" s="118"/>
-      <c r="X151" s="119"/>
+      <c r="Q151" s="154"/>
+      <c r="R151" s="155"/>
+      <c r="S151" s="155"/>
+      <c r="T151" s="155"/>
+      <c r="U151" s="155"/>
+      <c r="V151" s="156"/>
+      <c r="W151" s="93"/>
+      <c r="X151" s="94"/>
     </row>
     <row r="152" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q152" s="174"/>
-      <c r="R152" s="175"/>
-      <c r="S152" s="175"/>
-      <c r="T152" s="175"/>
-      <c r="U152" s="175"/>
-      <c r="V152" s="176"/>
-      <c r="W152" s="118"/>
-      <c r="X152" s="119"/>
+      <c r="Q152" s="154"/>
+      <c r="R152" s="155"/>
+      <c r="S152" s="155"/>
+      <c r="T152" s="155"/>
+      <c r="U152" s="155"/>
+      <c r="V152" s="156"/>
+      <c r="W152" s="93"/>
+      <c r="X152" s="94"/>
     </row>
     <row r="153" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q153" s="174"/>
-      <c r="R153" s="175"/>
-      <c r="S153" s="175"/>
-      <c r="T153" s="175"/>
-      <c r="U153" s="175"/>
-      <c r="V153" s="176"/>
-      <c r="W153" s="118"/>
-      <c r="X153" s="119"/>
+      <c r="Q153" s="154"/>
+      <c r="R153" s="155"/>
+      <c r="S153" s="155"/>
+      <c r="T153" s="155"/>
+      <c r="U153" s="155"/>
+      <c r="V153" s="156"/>
+      <c r="W153" s="93"/>
+      <c r="X153" s="94"/>
     </row>
     <row r="154" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q154" s="174"/>
-      <c r="R154" s="175"/>
-      <c r="S154" s="175"/>
-      <c r="T154" s="175"/>
-      <c r="U154" s="175"/>
-      <c r="V154" s="176"/>
-      <c r="W154" s="118"/>
-      <c r="X154" s="119"/>
+      <c r="Q154" s="154"/>
+      <c r="R154" s="155"/>
+      <c r="S154" s="155"/>
+      <c r="T154" s="155"/>
+      <c r="U154" s="155"/>
+      <c r="V154" s="156"/>
+      <c r="W154" s="93"/>
+      <c r="X154" s="94"/>
     </row>
     <row r="155" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q155" s="174"/>
-      <c r="R155" s="175"/>
-      <c r="S155" s="175"/>
-      <c r="T155" s="175"/>
-      <c r="U155" s="175"/>
-      <c r="V155" s="176"/>
-      <c r="W155" s="118"/>
-      <c r="X155" s="119"/>
+      <c r="Q155" s="154"/>
+      <c r="R155" s="155"/>
+      <c r="S155" s="155"/>
+      <c r="T155" s="155"/>
+      <c r="U155" s="155"/>
+      <c r="V155" s="156"/>
+      <c r="W155" s="93"/>
+      <c r="X155" s="94"/>
     </row>
     <row r="156" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q156" s="174"/>
-      <c r="R156" s="175"/>
-      <c r="S156" s="175"/>
-      <c r="T156" s="175"/>
-      <c r="U156" s="175"/>
-      <c r="V156" s="176"/>
-      <c r="W156" s="118"/>
-      <c r="X156" s="119"/>
+      <c r="Q156" s="154"/>
+      <c r="R156" s="155"/>
+      <c r="S156" s="155"/>
+      <c r="T156" s="155"/>
+      <c r="U156" s="155"/>
+      <c r="V156" s="156"/>
+      <c r="W156" s="93"/>
+      <c r="X156" s="94"/>
     </row>
     <row r="157" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q157" s="174"/>
-      <c r="R157" s="175"/>
-      <c r="S157" s="175"/>
-      <c r="T157" s="175"/>
-      <c r="U157" s="175"/>
-      <c r="V157" s="176"/>
-      <c r="W157" s="118"/>
-      <c r="X157" s="119"/>
+      <c r="Q157" s="154"/>
+      <c r="R157" s="155"/>
+      <c r="S157" s="155"/>
+      <c r="T157" s="155"/>
+      <c r="U157" s="155"/>
+      <c r="V157" s="156"/>
+      <c r="W157" s="93"/>
+      <c r="X157" s="94"/>
     </row>
     <row r="158" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q158" s="174"/>
-      <c r="R158" s="175"/>
-      <c r="S158" s="175"/>
-      <c r="T158" s="175"/>
-      <c r="U158" s="175"/>
-      <c r="V158" s="176"/>
-      <c r="W158" s="118"/>
-      <c r="X158" s="119"/>
+      <c r="Q158" s="154"/>
+      <c r="R158" s="155"/>
+      <c r="S158" s="155"/>
+      <c r="T158" s="155"/>
+      <c r="U158" s="155"/>
+      <c r="V158" s="156"/>
+      <c r="W158" s="93"/>
+      <c r="X158" s="94"/>
     </row>
     <row r="159" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q159" s="179"/>
-      <c r="R159" s="180"/>
-      <c r="S159" s="180"/>
-      <c r="T159" s="180"/>
-      <c r="U159" s="180"/>
-      <c r="V159" s="181"/>
-      <c r="W159" s="114"/>
-      <c r="X159" s="140"/>
+      <c r="Q159" s="157"/>
+      <c r="R159" s="158"/>
+      <c r="S159" s="158"/>
+      <c r="T159" s="158"/>
+      <c r="U159" s="158"/>
+      <c r="V159" s="159"/>
+      <c r="W159" s="90"/>
+      <c r="X159" s="107"/>
     </row>
     <row r="160" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q160" s="174"/>
-      <c r="R160" s="175"/>
-      <c r="S160" s="175"/>
-      <c r="T160" s="175"/>
-      <c r="U160" s="175"/>
-      <c r="V160" s="176"/>
-      <c r="W160" s="118"/>
-      <c r="X160" s="119"/>
+      <c r="Q160" s="154"/>
+      <c r="R160" s="155"/>
+      <c r="S160" s="155"/>
+      <c r="T160" s="155"/>
+      <c r="U160" s="155"/>
+      <c r="V160" s="156"/>
+      <c r="W160" s="93"/>
+      <c r="X160" s="94"/>
     </row>
     <row r="161" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q161" s="174"/>
-      <c r="R161" s="175"/>
-      <c r="S161" s="175"/>
-      <c r="T161" s="175"/>
-      <c r="U161" s="175"/>
-      <c r="V161" s="176"/>
-      <c r="W161" s="118"/>
-      <c r="X161" s="119"/>
+      <c r="Q161" s="154"/>
+      <c r="R161" s="155"/>
+      <c r="S161" s="155"/>
+      <c r="T161" s="155"/>
+      <c r="U161" s="155"/>
+      <c r="V161" s="156"/>
+      <c r="W161" s="93"/>
+      <c r="X161" s="94"/>
     </row>
     <row r="162" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q162" s="174"/>
-      <c r="R162" s="175"/>
-      <c r="S162" s="175"/>
-      <c r="T162" s="175"/>
-      <c r="U162" s="175"/>
-      <c r="V162" s="176"/>
-      <c r="W162" s="118"/>
-      <c r="X162" s="119"/>
+      <c r="Q162" s="154"/>
+      <c r="R162" s="155"/>
+      <c r="S162" s="155"/>
+      <c r="T162" s="155"/>
+      <c r="U162" s="155"/>
+      <c r="V162" s="156"/>
+      <c r="W162" s="93"/>
+      <c r="X162" s="94"/>
     </row>
     <row r="163" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q163" s="174"/>
-      <c r="R163" s="175"/>
-      <c r="S163" s="175"/>
-      <c r="T163" s="175"/>
-      <c r="U163" s="175"/>
-      <c r="V163" s="176"/>
-      <c r="W163" s="118"/>
-      <c r="X163" s="119"/>
+      <c r="Q163" s="154"/>
+      <c r="R163" s="155"/>
+      <c r="S163" s="155"/>
+      <c r="T163" s="155"/>
+      <c r="U163" s="155"/>
+      <c r="V163" s="156"/>
+      <c r="W163" s="93"/>
+      <c r="X163" s="94"/>
     </row>
     <row r="164" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q164" s="174"/>
-      <c r="R164" s="175"/>
-      <c r="S164" s="175"/>
-      <c r="T164" s="175"/>
-      <c r="U164" s="175"/>
-      <c r="V164" s="176"/>
-      <c r="W164" s="118"/>
-      <c r="X164" s="119"/>
+      <c r="Q164" s="154"/>
+      <c r="R164" s="155"/>
+      <c r="S164" s="155"/>
+      <c r="T164" s="155"/>
+      <c r="U164" s="155"/>
+      <c r="V164" s="156"/>
+      <c r="W164" s="93"/>
+      <c r="X164" s="94"/>
     </row>
     <row r="165" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q165" s="174"/>
-      <c r="R165" s="175"/>
-      <c r="S165" s="175"/>
-      <c r="T165" s="175"/>
-      <c r="U165" s="175"/>
-      <c r="V165" s="176"/>
-      <c r="W165" s="118"/>
-      <c r="X165" s="119"/>
+      <c r="Q165" s="154"/>
+      <c r="R165" s="155"/>
+      <c r="S165" s="155"/>
+      <c r="T165" s="155"/>
+      <c r="U165" s="155"/>
+      <c r="V165" s="156"/>
+      <c r="W165" s="93"/>
+      <c r="X165" s="94"/>
     </row>
     <row r="166" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q166" s="174"/>
-      <c r="R166" s="175"/>
-      <c r="S166" s="175"/>
-      <c r="T166" s="175"/>
-      <c r="U166" s="175"/>
-      <c r="V166" s="176"/>
-      <c r="W166" s="118"/>
-      <c r="X166" s="119"/>
+      <c r="Q166" s="154"/>
+      <c r="R166" s="155"/>
+      <c r="S166" s="155"/>
+      <c r="T166" s="155"/>
+      <c r="U166" s="155"/>
+      <c r="V166" s="156"/>
+      <c r="W166" s="93"/>
+      <c r="X166" s="94"/>
     </row>
     <row r="167" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q167" s="174"/>
-      <c r="R167" s="175"/>
-      <c r="S167" s="175"/>
-      <c r="T167" s="175"/>
-      <c r="U167" s="175"/>
-      <c r="V167" s="176"/>
-      <c r="W167" s="118"/>
-      <c r="X167" s="119"/>
+      <c r="Q167" s="154"/>
+      <c r="R167" s="155"/>
+      <c r="S167" s="155"/>
+      <c r="T167" s="155"/>
+      <c r="U167" s="155"/>
+      <c r="V167" s="156"/>
+      <c r="W167" s="93"/>
+      <c r="X167" s="94"/>
     </row>
     <row r="168" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q168" s="174"/>
-      <c r="R168" s="175"/>
-      <c r="S168" s="175"/>
-      <c r="T168" s="175"/>
-      <c r="U168" s="175"/>
-      <c r="V168" s="176"/>
-      <c r="W168" s="118"/>
-      <c r="X168" s="119"/>
+      <c r="Q168" s="154"/>
+      <c r="R168" s="155"/>
+      <c r="S168" s="155"/>
+      <c r="T168" s="155"/>
+      <c r="U168" s="155"/>
+      <c r="V168" s="156"/>
+      <c r="W168" s="93"/>
+      <c r="X168" s="94"/>
     </row>
     <row r="169" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q169" s="174"/>
-      <c r="R169" s="175"/>
-      <c r="S169" s="175"/>
-      <c r="T169" s="175"/>
-      <c r="U169" s="175"/>
-      <c r="V169" s="176"/>
-      <c r="W169" s="118"/>
-      <c r="X169" s="119"/>
+      <c r="Q169" s="154"/>
+      <c r="R169" s="155"/>
+      <c r="S169" s="155"/>
+      <c r="T169" s="155"/>
+      <c r="U169" s="155"/>
+      <c r="V169" s="156"/>
+      <c r="W169" s="93"/>
+      <c r="X169" s="94"/>
     </row>
     <row r="170" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q170" s="174"/>
-      <c r="R170" s="175"/>
-      <c r="S170" s="175"/>
-      <c r="T170" s="175"/>
-      <c r="U170" s="175"/>
-      <c r="V170" s="176"/>
-      <c r="W170" s="118"/>
-      <c r="X170" s="119"/>
+      <c r="Q170" s="154"/>
+      <c r="R170" s="155"/>
+      <c r="S170" s="155"/>
+      <c r="T170" s="155"/>
+      <c r="U170" s="155"/>
+      <c r="V170" s="156"/>
+      <c r="W170" s="93"/>
+      <c r="X170" s="94"/>
     </row>
     <row r="171" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q171" s="174"/>
-      <c r="R171" s="175"/>
-      <c r="S171" s="175"/>
-      <c r="T171" s="175"/>
-      <c r="U171" s="175"/>
-      <c r="V171" s="176"/>
-      <c r="W171" s="118"/>
-      <c r="X171" s="119"/>
+      <c r="Q171" s="154"/>
+      <c r="R171" s="155"/>
+      <c r="S171" s="155"/>
+      <c r="T171" s="155"/>
+      <c r="U171" s="155"/>
+      <c r="V171" s="156"/>
+      <c r="W171" s="93"/>
+      <c r="X171" s="94"/>
     </row>
     <row r="172" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q172" s="174"/>
-      <c r="R172" s="175"/>
-      <c r="S172" s="175"/>
-      <c r="T172" s="175"/>
-      <c r="U172" s="175"/>
-      <c r="V172" s="176"/>
-      <c r="W172" s="118"/>
-      <c r="X172" s="119"/>
+      <c r="Q172" s="154"/>
+      <c r="R172" s="155"/>
+      <c r="S172" s="155"/>
+      <c r="T172" s="155"/>
+      <c r="U172" s="155"/>
+      <c r="V172" s="156"/>
+      <c r="W172" s="93"/>
+      <c r="X172" s="94"/>
     </row>
     <row r="173" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q173" s="174"/>
-      <c r="R173" s="175"/>
-      <c r="S173" s="175"/>
-      <c r="T173" s="175"/>
-      <c r="U173" s="175"/>
-      <c r="V173" s="176"/>
-      <c r="W173" s="118"/>
-      <c r="X173" s="119"/>
+      <c r="Q173" s="154"/>
+      <c r="R173" s="155"/>
+      <c r="S173" s="155"/>
+      <c r="T173" s="155"/>
+      <c r="U173" s="155"/>
+      <c r="V173" s="156"/>
+      <c r="W173" s="93"/>
+      <c r="X173" s="94"/>
     </row>
     <row r="174" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q174" s="174"/>
-      <c r="R174" s="175"/>
-      <c r="S174" s="175"/>
-      <c r="T174" s="175"/>
-      <c r="U174" s="175"/>
-      <c r="V174" s="176"/>
-      <c r="W174" s="118"/>
-      <c r="X174" s="119"/>
+      <c r="Q174" s="154"/>
+      <c r="R174" s="155"/>
+      <c r="S174" s="155"/>
+      <c r="T174" s="155"/>
+      <c r="U174" s="155"/>
+      <c r="V174" s="156"/>
+      <c r="W174" s="93"/>
+      <c r="X174" s="94"/>
     </row>
     <row r="175" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q175" s="174"/>
-      <c r="R175" s="175"/>
-      <c r="S175" s="175"/>
-      <c r="T175" s="175"/>
-      <c r="U175" s="175"/>
-      <c r="V175" s="176"/>
-      <c r="W175" s="118"/>
-      <c r="X175" s="119"/>
+      <c r="Q175" s="154"/>
+      <c r="R175" s="155"/>
+      <c r="S175" s="155"/>
+      <c r="T175" s="155"/>
+      <c r="U175" s="155"/>
+      <c r="V175" s="156"/>
+      <c r="W175" s="93"/>
+      <c r="X175" s="94"/>
     </row>
     <row r="176" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q176" s="174"/>
-      <c r="R176" s="175"/>
-      <c r="S176" s="175"/>
-      <c r="T176" s="175"/>
-      <c r="U176" s="175"/>
-      <c r="V176" s="176"/>
-      <c r="W176" s="118"/>
-      <c r="X176" s="119"/>
+      <c r="Q176" s="154"/>
+      <c r="R176" s="155"/>
+      <c r="S176" s="155"/>
+      <c r="T176" s="155"/>
+      <c r="U176" s="155"/>
+      <c r="V176" s="156"/>
+      <c r="W176" s="93"/>
+      <c r="X176" s="94"/>
     </row>
     <row r="177" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q177" s="174"/>
-      <c r="R177" s="175"/>
-      <c r="S177" s="175"/>
-      <c r="T177" s="175"/>
-      <c r="U177" s="175"/>
-      <c r="V177" s="176"/>
-      <c r="W177" s="118"/>
-      <c r="X177" s="119"/>
+      <c r="Q177" s="154"/>
+      <c r="R177" s="155"/>
+      <c r="S177" s="155"/>
+      <c r="T177" s="155"/>
+      <c r="U177" s="155"/>
+      <c r="V177" s="156"/>
+      <c r="W177" s="93"/>
+      <c r="X177" s="94"/>
     </row>
     <row r="178" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q178" s="174"/>
-      <c r="R178" s="175"/>
-      <c r="S178" s="175"/>
-      <c r="T178" s="175"/>
-      <c r="U178" s="175"/>
-      <c r="V178" s="176"/>
-      <c r="W178" s="118"/>
-      <c r="X178" s="119"/>
+      <c r="Q178" s="154"/>
+      <c r="R178" s="155"/>
+      <c r="S178" s="155"/>
+      <c r="T178" s="155"/>
+      <c r="U178" s="155"/>
+      <c r="V178" s="156"/>
+      <c r="W178" s="93"/>
+      <c r="X178" s="94"/>
     </row>
     <row r="179" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q179" s="174"/>
-      <c r="R179" s="175"/>
-      <c r="S179" s="175"/>
-      <c r="T179" s="175"/>
-      <c r="U179" s="175"/>
-      <c r="V179" s="176"/>
-      <c r="W179" s="118"/>
-      <c r="X179" s="119"/>
+      <c r="Q179" s="154"/>
+      <c r="R179" s="155"/>
+      <c r="S179" s="155"/>
+      <c r="T179" s="155"/>
+      <c r="U179" s="155"/>
+      <c r="V179" s="156"/>
+      <c r="W179" s="93"/>
+      <c r="X179" s="94"/>
     </row>
     <row r="180" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q180" s="174"/>
-      <c r="R180" s="175"/>
-      <c r="S180" s="175"/>
-      <c r="T180" s="175"/>
-      <c r="U180" s="175"/>
-      <c r="V180" s="176"/>
-      <c r="W180" s="118"/>
-      <c r="X180" s="119"/>
+      <c r="Q180" s="154"/>
+      <c r="R180" s="155"/>
+      <c r="S180" s="155"/>
+      <c r="T180" s="155"/>
+      <c r="U180" s="155"/>
+      <c r="V180" s="156"/>
+      <c r="W180" s="93"/>
+      <c r="X180" s="94"/>
     </row>
     <row r="181" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q181" s="174"/>
-      <c r="R181" s="175"/>
-      <c r="S181" s="175"/>
-      <c r="T181" s="175"/>
-      <c r="U181" s="175"/>
-      <c r="V181" s="176"/>
-      <c r="W181" s="118"/>
-      <c r="X181" s="119"/>
+      <c r="Q181" s="154"/>
+      <c r="R181" s="155"/>
+      <c r="S181" s="155"/>
+      <c r="T181" s="155"/>
+      <c r="U181" s="155"/>
+      <c r="V181" s="156"/>
+      <c r="W181" s="93"/>
+      <c r="X181" s="94"/>
     </row>
     <row r="182" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q182" s="174"/>
-      <c r="R182" s="175"/>
-      <c r="S182" s="175"/>
-      <c r="T182" s="175"/>
-      <c r="U182" s="175"/>
-      <c r="V182" s="176"/>
-      <c r="W182" s="118"/>
-      <c r="X182" s="119"/>
+      <c r="Q182" s="154"/>
+      <c r="R182" s="155"/>
+      <c r="S182" s="155"/>
+      <c r="T182" s="155"/>
+      <c r="U182" s="155"/>
+      <c r="V182" s="156"/>
+      <c r="W182" s="93"/>
+      <c r="X182" s="94"/>
     </row>
     <row r="183" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q183" s="174"/>
-      <c r="R183" s="175"/>
-      <c r="S183" s="175"/>
-      <c r="T183" s="175"/>
-      <c r="U183" s="175"/>
-      <c r="V183" s="176"/>
-      <c r="W183" s="118"/>
-      <c r="X183" s="119"/>
+      <c r="Q183" s="154"/>
+      <c r="R183" s="155"/>
+      <c r="S183" s="155"/>
+      <c r="T183" s="155"/>
+      <c r="U183" s="155"/>
+      <c r="V183" s="156"/>
+      <c r="W183" s="93"/>
+      <c r="X183" s="94"/>
     </row>
     <row r="184" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q184" s="174"/>
-      <c r="R184" s="175"/>
-      <c r="S184" s="175"/>
-      <c r="T184" s="175"/>
-      <c r="U184" s="175"/>
-      <c r="V184" s="176"/>
-      <c r="W184" s="118"/>
-      <c r="X184" s="119"/>
+      <c r="Q184" s="154"/>
+      <c r="R184" s="155"/>
+      <c r="S184" s="155"/>
+      <c r="T184" s="155"/>
+      <c r="U184" s="155"/>
+      <c r="V184" s="156"/>
+      <c r="W184" s="93"/>
+      <c r="X184" s="94"/>
     </row>
     <row r="185" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q185" s="174"/>
-      <c r="R185" s="175"/>
-      <c r="S185" s="175"/>
-      <c r="T185" s="175"/>
-      <c r="U185" s="175"/>
-      <c r="V185" s="176"/>
-      <c r="W185" s="118"/>
-      <c r="X185" s="119"/>
+      <c r="Q185" s="154"/>
+      <c r="R185" s="155"/>
+      <c r="S185" s="155"/>
+      <c r="T185" s="155"/>
+      <c r="U185" s="155"/>
+      <c r="V185" s="156"/>
+      <c r="W185" s="93"/>
+      <c r="X185" s="94"/>
     </row>
     <row r="186" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q186" s="174"/>
-      <c r="R186" s="175"/>
-      <c r="S186" s="175"/>
-      <c r="T186" s="175"/>
-      <c r="U186" s="175"/>
-      <c r="V186" s="176"/>
-      <c r="W186" s="118"/>
-      <c r="X186" s="119"/>
+      <c r="Q186" s="154"/>
+      <c r="R186" s="155"/>
+      <c r="S186" s="155"/>
+      <c r="T186" s="155"/>
+      <c r="U186" s="155"/>
+      <c r="V186" s="156"/>
+      <c r="W186" s="93"/>
+      <c r="X186" s="94"/>
     </row>
     <row r="187" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q187" s="174"/>
-      <c r="R187" s="175"/>
-      <c r="S187" s="175"/>
-      <c r="T187" s="175"/>
-      <c r="U187" s="175"/>
-      <c r="V187" s="176"/>
-      <c r="W187" s="118"/>
-      <c r="X187" s="119"/>
+      <c r="Q187" s="154"/>
+      <c r="R187" s="155"/>
+      <c r="S187" s="155"/>
+      <c r="T187" s="155"/>
+      <c r="U187" s="155"/>
+      <c r="V187" s="156"/>
+      <c r="W187" s="93"/>
+      <c r="X187" s="94"/>
     </row>
     <row r="188" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q188" s="174"/>
-      <c r="R188" s="175"/>
-      <c r="S188" s="175"/>
-      <c r="T188" s="175"/>
-      <c r="U188" s="175"/>
-      <c r="V188" s="176"/>
-      <c r="W188" s="118"/>
-      <c r="X188" s="119"/>
+      <c r="Q188" s="154"/>
+      <c r="R188" s="155"/>
+      <c r="S188" s="155"/>
+      <c r="T188" s="155"/>
+      <c r="U188" s="155"/>
+      <c r="V188" s="156"/>
+      <c r="W188" s="93"/>
+      <c r="X188" s="94"/>
     </row>
     <row r="189" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q189" s="174"/>
-      <c r="R189" s="175"/>
-      <c r="S189" s="175"/>
-      <c r="T189" s="175"/>
-      <c r="U189" s="175"/>
-      <c r="V189" s="176"/>
-      <c r="W189" s="118"/>
-      <c r="X189" s="119"/>
+      <c r="Q189" s="154"/>
+      <c r="R189" s="155"/>
+      <c r="S189" s="155"/>
+      <c r="T189" s="155"/>
+      <c r="U189" s="155"/>
+      <c r="V189" s="156"/>
+      <c r="W189" s="93"/>
+      <c r="X189" s="94"/>
     </row>
     <row r="190" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q190" s="174"/>
-      <c r="R190" s="175"/>
-      <c r="S190" s="175"/>
-      <c r="T190" s="175"/>
-      <c r="U190" s="175"/>
-      <c r="V190" s="176"/>
-      <c r="W190" s="118"/>
-      <c r="X190" s="119"/>
+      <c r="Q190" s="154"/>
+      <c r="R190" s="155"/>
+      <c r="S190" s="155"/>
+      <c r="T190" s="155"/>
+      <c r="U190" s="155"/>
+      <c r="V190" s="156"/>
+      <c r="W190" s="93"/>
+      <c r="X190" s="94"/>
     </row>
     <row r="191" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q191" s="174"/>
-      <c r="R191" s="175"/>
-      <c r="S191" s="175"/>
-      <c r="T191" s="175"/>
-      <c r="U191" s="175"/>
-      <c r="V191" s="176"/>
-      <c r="W191" s="118"/>
-      <c r="X191" s="119"/>
+      <c r="Q191" s="154"/>
+      <c r="R191" s="155"/>
+      <c r="S191" s="155"/>
+      <c r="T191" s="155"/>
+      <c r="U191" s="155"/>
+      <c r="V191" s="156"/>
+      <c r="W191" s="93"/>
+      <c r="X191" s="94"/>
     </row>
     <row r="192" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q192" s="174"/>
-      <c r="R192" s="175"/>
-      <c r="S192" s="175"/>
-      <c r="T192" s="175"/>
-      <c r="U192" s="175"/>
-      <c r="V192" s="176"/>
-      <c r="W192" s="118"/>
-      <c r="X192" s="119"/>
+      <c r="Q192" s="154"/>
+      <c r="R192" s="155"/>
+      <c r="S192" s="155"/>
+      <c r="T192" s="155"/>
+      <c r="U192" s="155"/>
+      <c r="V192" s="156"/>
+      <c r="W192" s="93"/>
+      <c r="X192" s="94"/>
     </row>
     <row r="193" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q193" s="174"/>
-      <c r="R193" s="175"/>
-      <c r="S193" s="175"/>
-      <c r="T193" s="175"/>
-      <c r="U193" s="175"/>
-      <c r="V193" s="176"/>
-      <c r="W193" s="118"/>
-      <c r="X193" s="119"/>
+      <c r="Q193" s="154"/>
+      <c r="R193" s="155"/>
+      <c r="S193" s="155"/>
+      <c r="T193" s="155"/>
+      <c r="U193" s="155"/>
+      <c r="V193" s="156"/>
+      <c r="W193" s="93"/>
+      <c r="X193" s="94"/>
     </row>
     <row r="194" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q194" s="174"/>
-      <c r="R194" s="175"/>
-      <c r="S194" s="175"/>
-      <c r="T194" s="175"/>
-      <c r="U194" s="175"/>
-      <c r="V194" s="176"/>
-      <c r="W194" s="118"/>
-      <c r="X194" s="119"/>
+      <c r="Q194" s="154"/>
+      <c r="R194" s="155"/>
+      <c r="S194" s="155"/>
+      <c r="T194" s="155"/>
+      <c r="U194" s="155"/>
+      <c r="V194" s="156"/>
+      <c r="W194" s="93"/>
+      <c r="X194" s="94"/>
     </row>
     <row r="195" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q195" s="174"/>
-      <c r="R195" s="175"/>
-      <c r="S195" s="175"/>
-      <c r="T195" s="175"/>
-      <c r="U195" s="175"/>
-      <c r="V195" s="176"/>
-      <c r="W195" s="118"/>
-      <c r="X195" s="119"/>
+      <c r="Q195" s="154"/>
+      <c r="R195" s="155"/>
+      <c r="S195" s="155"/>
+      <c r="T195" s="155"/>
+      <c r="U195" s="155"/>
+      <c r="V195" s="156"/>
+      <c r="W195" s="93"/>
+      <c r="X195" s="94"/>
     </row>
     <row r="196" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q196" s="174"/>
-      <c r="R196" s="175"/>
-      <c r="S196" s="175"/>
-      <c r="T196" s="175"/>
-      <c r="U196" s="175"/>
-      <c r="V196" s="176"/>
-      <c r="W196" s="118"/>
-      <c r="X196" s="119"/>
+      <c r="Q196" s="154"/>
+      <c r="R196" s="155"/>
+      <c r="S196" s="155"/>
+      <c r="T196" s="155"/>
+      <c r="U196" s="155"/>
+      <c r="V196" s="156"/>
+      <c r="W196" s="93"/>
+      <c r="X196" s="94"/>
     </row>
     <row r="197" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q197" s="174"/>
-      <c r="R197" s="175"/>
-      <c r="S197" s="175"/>
-      <c r="T197" s="175"/>
-      <c r="U197" s="175"/>
-      <c r="V197" s="176"/>
-      <c r="W197" s="118"/>
-      <c r="X197" s="119"/>
+      <c r="Q197" s="154"/>
+      <c r="R197" s="155"/>
+      <c r="S197" s="155"/>
+      <c r="T197" s="155"/>
+      <c r="U197" s="155"/>
+      <c r="V197" s="156"/>
+      <c r="W197" s="93"/>
+      <c r="X197" s="94"/>
     </row>
     <row r="198" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q198" s="174"/>
-      <c r="R198" s="175"/>
-      <c r="S198" s="175"/>
-      <c r="T198" s="175"/>
-      <c r="U198" s="175"/>
-      <c r="V198" s="176"/>
-      <c r="W198" s="118"/>
-      <c r="X198" s="119"/>
+      <c r="Q198" s="154"/>
+      <c r="R198" s="155"/>
+      <c r="S198" s="155"/>
+      <c r="T198" s="155"/>
+      <c r="U198" s="155"/>
+      <c r="V198" s="156"/>
+      <c r="W198" s="93"/>
+      <c r="X198" s="94"/>
     </row>
     <row r="199" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q199" s="174"/>
-      <c r="R199" s="175"/>
-      <c r="S199" s="175"/>
-      <c r="T199" s="175"/>
-      <c r="U199" s="175"/>
-      <c r="V199" s="176"/>
-      <c r="W199" s="118"/>
-      <c r="X199" s="119"/>
+      <c r="Q199" s="154"/>
+      <c r="R199" s="155"/>
+      <c r="S199" s="155"/>
+      <c r="T199" s="155"/>
+      <c r="U199" s="155"/>
+      <c r="V199" s="156"/>
+      <c r="W199" s="93"/>
+      <c r="X199" s="94"/>
     </row>
     <row r="200" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q200" s="174"/>
-      <c r="R200" s="175"/>
-      <c r="S200" s="175"/>
-      <c r="T200" s="175"/>
-      <c r="U200" s="175"/>
-      <c r="V200" s="176"/>
-      <c r="W200" s="118"/>
-      <c r="X200" s="119"/>
+      <c r="Q200" s="154"/>
+      <c r="R200" s="155"/>
+      <c r="S200" s="155"/>
+      <c r="T200" s="155"/>
+      <c r="U200" s="155"/>
+      <c r="V200" s="156"/>
+      <c r="W200" s="93"/>
+      <c r="X200" s="94"/>
     </row>
     <row r="201" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q201" s="174"/>
-      <c r="R201" s="175"/>
-      <c r="S201" s="175"/>
-      <c r="T201" s="175"/>
-      <c r="U201" s="175"/>
-      <c r="V201" s="176"/>
-      <c r="W201" s="118"/>
-      <c r="X201" s="119"/>
+      <c r="Q201" s="154"/>
+      <c r="R201" s="155"/>
+      <c r="S201" s="155"/>
+      <c r="T201" s="155"/>
+      <c r="U201" s="155"/>
+      <c r="V201" s="156"/>
+      <c r="W201" s="93"/>
+      <c r="X201" s="94"/>
     </row>
     <row r="202" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q202" s="174"/>
-      <c r="R202" s="175"/>
-      <c r="S202" s="175"/>
-      <c r="T202" s="175"/>
-      <c r="U202" s="175"/>
-      <c r="V202" s="176"/>
-      <c r="W202" s="118"/>
-      <c r="X202" s="119"/>
+      <c r="Q202" s="154"/>
+      <c r="R202" s="155"/>
+      <c r="S202" s="155"/>
+      <c r="T202" s="155"/>
+      <c r="U202" s="155"/>
+      <c r="V202" s="156"/>
+      <c r="W202" s="93"/>
+      <c r="X202" s="94"/>
     </row>
     <row r="203" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q203" s="174"/>
-      <c r="R203" s="175"/>
-      <c r="S203" s="175"/>
-      <c r="T203" s="175"/>
-      <c r="U203" s="175"/>
-      <c r="V203" s="176"/>
-      <c r="W203" s="118"/>
-      <c r="X203" s="119"/>
+      <c r="Q203" s="154"/>
+      <c r="R203" s="155"/>
+      <c r="S203" s="155"/>
+      <c r="T203" s="155"/>
+      <c r="U203" s="155"/>
+      <c r="V203" s="156"/>
+      <c r="W203" s="93"/>
+      <c r="X203" s="94"/>
     </row>
     <row r="204" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q204" s="174"/>
-      <c r="R204" s="175"/>
-      <c r="S204" s="175"/>
-      <c r="T204" s="175"/>
-      <c r="U204" s="175"/>
-      <c r="V204" s="176"/>
-      <c r="W204" s="118"/>
-      <c r="X204" s="119"/>
+      <c r="Q204" s="154"/>
+      <c r="R204" s="155"/>
+      <c r="S204" s="155"/>
+      <c r="T204" s="155"/>
+      <c r="U204" s="155"/>
+      <c r="V204" s="156"/>
+      <c r="W204" s="93"/>
+      <c r="X204" s="94"/>
     </row>
     <row r="205" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q205" s="174"/>
-      <c r="R205" s="175"/>
-      <c r="S205" s="175"/>
-      <c r="T205" s="175"/>
-      <c r="U205" s="175"/>
-      <c r="V205" s="176"/>
-      <c r="W205" s="118"/>
-      <c r="X205" s="119"/>
+      <c r="Q205" s="154"/>
+      <c r="R205" s="155"/>
+      <c r="S205" s="155"/>
+      <c r="T205" s="155"/>
+      <c r="U205" s="155"/>
+      <c r="V205" s="156"/>
+      <c r="W205" s="93"/>
+      <c r="X205" s="94"/>
     </row>
     <row r="206" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q206" s="174"/>
-      <c r="R206" s="175"/>
-      <c r="S206" s="175"/>
-      <c r="T206" s="175"/>
-      <c r="U206" s="175"/>
-      <c r="V206" s="176"/>
-      <c r="W206" s="118"/>
-      <c r="X206" s="119"/>
+      <c r="Q206" s="154"/>
+      <c r="R206" s="155"/>
+      <c r="S206" s="155"/>
+      <c r="T206" s="155"/>
+      <c r="U206" s="155"/>
+      <c r="V206" s="156"/>
+      <c r="W206" s="93"/>
+      <c r="X206" s="94"/>
     </row>
     <row r="207" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q207" s="174"/>
-      <c r="R207" s="175"/>
-      <c r="S207" s="175"/>
-      <c r="T207" s="175"/>
-      <c r="U207" s="175"/>
-      <c r="V207" s="176"/>
-      <c r="W207" s="118"/>
-      <c r="X207" s="119"/>
+      <c r="Q207" s="154"/>
+      <c r="R207" s="155"/>
+      <c r="S207" s="155"/>
+      <c r="T207" s="155"/>
+      <c r="U207" s="155"/>
+      <c r="V207" s="156"/>
+      <c r="W207" s="93"/>
+      <c r="X207" s="94"/>
     </row>
     <row r="208" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q208" s="174"/>
-      <c r="R208" s="175"/>
-      <c r="S208" s="175"/>
-      <c r="T208" s="175"/>
-      <c r="U208" s="175"/>
-      <c r="V208" s="176"/>
-      <c r="W208" s="118"/>
-      <c r="X208" s="119"/>
+      <c r="Q208" s="154"/>
+      <c r="R208" s="155"/>
+      <c r="S208" s="155"/>
+      <c r="T208" s="155"/>
+      <c r="U208" s="155"/>
+      <c r="V208" s="156"/>
+      <c r="W208" s="93"/>
+      <c r="X208" s="94"/>
     </row>
     <row r="209" spans="17:24" x14ac:dyDescent="0.3">
-      <c r="Q209" s="174"/>
-      <c r="R209" s="175"/>
-      <c r="S209" s="175"/>
-      <c r="T209" s="175"/>
-      <c r="U209" s="175"/>
-      <c r="V209" s="176"/>
-      <c r="W209" s="118"/>
-      <c r="X209" s="119"/>
+      <c r="Q209" s="154"/>
+      <c r="R209" s="155"/>
+      <c r="S209" s="155"/>
+      <c r="T209" s="155"/>
+      <c r="U209" s="155"/>
+      <c r="V209" s="156"/>
+      <c r="W209" s="93"/>
+      <c r="X209" s="94"/>
     </row>
     <row r="210" spans="17:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="Q210" s="268"/>
-      <c r="R210" s="269"/>
-      <c r="S210" s="269"/>
-      <c r="T210" s="269"/>
-      <c r="U210" s="269"/>
-      <c r="V210" s="270"/>
-      <c r="W210" s="141"/>
-      <c r="X210" s="142"/>
+      <c r="Q210" s="228"/>
+      <c r="R210" s="229"/>
+      <c r="S210" s="229"/>
+      <c r="T210" s="229"/>
+      <c r="U210" s="229"/>
+      <c r="V210" s="230"/>
+      <c r="W210" s="108"/>
+      <c r="X210" s="109"/>
     </row>
   </sheetData>
   <sheetProtection password="9CDD" sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
     <protectedRange sqref="Y6 E6:F7 G7 I6:J7" name="Диапазон1_1_2_1"/>
   </protectedRanges>
-  <mergeCells count="273">
-    <mergeCell ref="C40:D41"/>
-    <mergeCell ref="E40:F41"/>
-    <mergeCell ref="N6:N7"/>
+  <mergeCells count="266">
+    <mergeCell ref="O6:O7"/>
     <mergeCell ref="I13:J13"/>
     <mergeCell ref="K13:L13"/>
     <mergeCell ref="Q207:V207"/>
@@ -6950,13 +6565,8 @@
     <mergeCell ref="Q118:V118"/>
     <mergeCell ref="Q119:V119"/>
     <mergeCell ref="Q120:V120"/>
-    <mergeCell ref="Q108:V108"/>
-    <mergeCell ref="Q53:V53"/>
-    <mergeCell ref="Q54:V54"/>
-    <mergeCell ref="Q32:V32"/>
-    <mergeCell ref="Q33:V33"/>
-    <mergeCell ref="Q34:V34"/>
-    <mergeCell ref="Q35:V35"/>
+    <mergeCell ref="Q84:V84"/>
+    <mergeCell ref="Q85:V85"/>
     <mergeCell ref="Q26:V26"/>
     <mergeCell ref="Q27:V27"/>
     <mergeCell ref="Q28:V28"/>
@@ -6974,27 +6584,29 @@
     <mergeCell ref="Q36:V36"/>
     <mergeCell ref="Q37:V37"/>
     <mergeCell ref="Q38:V38"/>
-    <mergeCell ref="Q50:V50"/>
-    <mergeCell ref="Q51:V51"/>
-    <mergeCell ref="Q52:V52"/>
-    <mergeCell ref="Q46:V46"/>
-    <mergeCell ref="Q14:V14"/>
-    <mergeCell ref="Q15:V15"/>
-    <mergeCell ref="Q16:V16"/>
-    <mergeCell ref="Q17:V17"/>
     <mergeCell ref="Q47:V47"/>
     <mergeCell ref="Q48:V48"/>
     <mergeCell ref="Q49:V49"/>
     <mergeCell ref="Q39:V39"/>
     <mergeCell ref="Q40:V40"/>
-    <mergeCell ref="C4:H4"/>
-    <mergeCell ref="C5:H6"/>
-    <mergeCell ref="O6:O7"/>
+    <mergeCell ref="I28:J29"/>
+    <mergeCell ref="K28:L29"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="Q51:V51"/>
+    <mergeCell ref="Q46:V46"/>
+    <mergeCell ref="I31:J32"/>
+    <mergeCell ref="K31:L32"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="G24:G25"/>
     <mergeCell ref="Q109:V109"/>
     <mergeCell ref="Q9:V9"/>
     <mergeCell ref="K10:L10"/>
-    <mergeCell ref="K21:K22"/>
-    <mergeCell ref="L21:L22"/>
     <mergeCell ref="Q8:V8"/>
     <mergeCell ref="Q10:V10"/>
     <mergeCell ref="Q11:V11"/>
@@ -7004,17 +6616,18 @@
     <mergeCell ref="Q12:V12"/>
     <mergeCell ref="Q13:V13"/>
     <mergeCell ref="Q31:V31"/>
-    <mergeCell ref="K17:K18"/>
-    <mergeCell ref="L17:L18"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="L16:L17"/>
     <mergeCell ref="Q25:V25"/>
     <mergeCell ref="Q24:V24"/>
     <mergeCell ref="Q22:V22"/>
     <mergeCell ref="Q23:V23"/>
     <mergeCell ref="Q55:V55"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="Q2:V3"/>
-    <mergeCell ref="Q18:V18"/>
+    <mergeCell ref="Q72:V72"/>
+    <mergeCell ref="Q73:V73"/>
+    <mergeCell ref="Q50:V50"/>
+    <mergeCell ref="Q108:V108"/>
+    <mergeCell ref="Q53:V53"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="K3:L3"/>
     <mergeCell ref="Q21:V21"/>
@@ -7024,37 +6637,21 @@
     <mergeCell ref="Q5:V5"/>
     <mergeCell ref="Q6:V6"/>
     <mergeCell ref="Q7:V7"/>
-    <mergeCell ref="Q72:V72"/>
-    <mergeCell ref="Q73:V73"/>
-    <mergeCell ref="C37:D38"/>
-    <mergeCell ref="E37:F38"/>
+    <mergeCell ref="Q14:V14"/>
+    <mergeCell ref="Q15:V15"/>
+    <mergeCell ref="Q16:V16"/>
+    <mergeCell ref="Q17:V17"/>
     <mergeCell ref="N18:O18"/>
-    <mergeCell ref="N9:N10"/>
     <mergeCell ref="O9:O10"/>
-    <mergeCell ref="C8:E9"/>
     <mergeCell ref="H8:L9"/>
     <mergeCell ref="I10:J10"/>
     <mergeCell ref="K12:L12"/>
     <mergeCell ref="K14:L14"/>
     <mergeCell ref="K15:L15"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="G8:G10"/>
     <mergeCell ref="I11:J11"/>
     <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="Q84:V84"/>
-    <mergeCell ref="Q85:V85"/>
-    <mergeCell ref="Q76:V76"/>
-    <mergeCell ref="Q77:V77"/>
-    <mergeCell ref="Q78:V78"/>
-    <mergeCell ref="Q79:V79"/>
-    <mergeCell ref="Q80:V80"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="C5:H6"/>
     <mergeCell ref="W2:W3"/>
     <mergeCell ref="Q74:V74"/>
     <mergeCell ref="Q75:V75"/>
@@ -7063,6 +6660,14 @@
     <mergeCell ref="Q68:V68"/>
     <mergeCell ref="Q69:V69"/>
     <mergeCell ref="Q70:V70"/>
+    <mergeCell ref="Q2:V3"/>
+    <mergeCell ref="Q18:V18"/>
+    <mergeCell ref="Q54:V54"/>
+    <mergeCell ref="Q32:V32"/>
+    <mergeCell ref="Q33:V33"/>
+    <mergeCell ref="Q34:V34"/>
+    <mergeCell ref="Q35:V35"/>
+    <mergeCell ref="Q52:V52"/>
     <mergeCell ref="Q81:V81"/>
     <mergeCell ref="Q82:V82"/>
     <mergeCell ref="Q65:V65"/>
@@ -7072,6 +6677,11 @@
     <mergeCell ref="Q59:V59"/>
     <mergeCell ref="Q60:V60"/>
     <mergeCell ref="Q71:V71"/>
+    <mergeCell ref="Q76:V76"/>
+    <mergeCell ref="Q77:V77"/>
+    <mergeCell ref="Q78:V78"/>
+    <mergeCell ref="Q79:V79"/>
+    <mergeCell ref="Q80:V80"/>
     <mergeCell ref="X2:X3"/>
     <mergeCell ref="Q106:V106"/>
     <mergeCell ref="Q107:V107"/>
@@ -7096,27 +6706,27 @@
     <mergeCell ref="Q89:V89"/>
     <mergeCell ref="Q90:V90"/>
     <mergeCell ref="Q83:V83"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="K29:K30"/>
-    <mergeCell ref="L29:L30"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="K20:K21"/>
+    <mergeCell ref="L20:L21"/>
     <mergeCell ref="N22:N23"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:G22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="360" r:id="rId1"/>
@@ -7204,7 +6814,7 @@
       <c r="A2" s="12"/>
       <c r="B2" s="12"/>
       <c r="C2" s="3" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>18</v>
@@ -7237,22 +6847,22 @@
         <v>5</v>
       </c>
       <c r="N2" s="53"/>
-      <c r="O2" s="342" t="s">
-        <v>48</v>
-      </c>
-      <c r="P2" s="343"/>
-      <c r="Q2" s="344"/>
-      <c r="R2" s="348" t="s">
+      <c r="O2" s="302" t="s">
+        <v>43</v>
+      </c>
+      <c r="P2" s="303"/>
+      <c r="Q2" s="304"/>
+      <c r="R2" s="308" t="s">
         <v>17</v>
       </c>
-      <c r="S2" s="334" t="s">
+      <c r="S2" s="294" t="s">
         <v>16</v>
       </c>
       <c r="T2" s="53"/>
       <c r="U2" s="53"/>
       <c r="V2" s="53"/>
-      <c r="W2" s="327"/>
-      <c r="X2" s="327"/>
+      <c r="W2" s="287"/>
+      <c r="X2" s="287"/>
       <c r="Y2" s="9"/>
       <c r="Z2" s="9"/>
       <c r="AA2" s="9"/>
@@ -7287,31 +6897,31 @@
     <row r="3" spans="1:55" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
-      <c r="C3" s="351">
+      <c r="C3" s="311">
         <f>НалБанки!C3</f>
         <v>0</v>
       </c>
-      <c r="D3" s="337">
+      <c r="D3" s="297">
         <f>НалБанки!D3</f>
         <v>0</v>
       </c>
-      <c r="E3" s="337">
+      <c r="E3" s="297">
         <f>НалБанки!E3</f>
         <v>0</v>
       </c>
-      <c r="F3" s="337">
+      <c r="F3" s="297">
         <f>НалБанки!F3</f>
         <v>0</v>
       </c>
-      <c r="G3" s="337">
+      <c r="G3" s="297">
         <f>НалБанки!G3</f>
         <v>0</v>
       </c>
-      <c r="H3" s="337">
+      <c r="H3" s="297">
         <f>НалБанки!H3</f>
         <v>0</v>
       </c>
-      <c r="I3" s="339">
+      <c r="I3" s="299">
         <f>НалБанки!I3</f>
         <v>40</v>
       </c>
@@ -7323,25 +6933,25 @@
         <f>ROUNDUP(((SUM(D3:F4,H3:I4)+(SUM(G3:G4)*0.75))*L3+((SUM(D3:F4,I3)+SUM(G3:G4)*0.75)*20%+(SUM(D3:F4,H3:I4)+SUM(G3:G4)*0.75)))*M3,0)</f>
         <v>167</v>
       </c>
-      <c r="L3" s="328">
+      <c r="L3" s="288">
         <f>8/92*1.2</f>
         <v>0.10434782608695652</v>
       </c>
-      <c r="M3" s="330">
+      <c r="M3" s="290">
         <f>НалБанки!J3</f>
         <v>3.2</v>
       </c>
       <c r="N3" s="53"/>
-      <c r="O3" s="345"/>
-      <c r="P3" s="346"/>
-      <c r="Q3" s="347"/>
-      <c r="R3" s="349"/>
-      <c r="S3" s="335"/>
+      <c r="O3" s="305"/>
+      <c r="P3" s="306"/>
+      <c r="Q3" s="307"/>
+      <c r="R3" s="309"/>
+      <c r="S3" s="295"/>
       <c r="T3" s="53"/>
       <c r="U3" s="53"/>
       <c r="V3" s="53"/>
-      <c r="W3" s="327"/>
-      <c r="X3" s="327"/>
+      <c r="W3" s="287"/>
+      <c r="X3" s="287"/>
       <c r="Y3" s="9"/>
       <c r="Z3" s="9"/>
       <c r="AA3" s="9"/>
@@ -7376,13 +6986,13 @@
     <row r="4" spans="1:55" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="12"/>
       <c r="B4" s="12"/>
-      <c r="C4" s="352"/>
-      <c r="D4" s="353"/>
-      <c r="E4" s="353"/>
-      <c r="F4" s="353"/>
-      <c r="G4" s="353"/>
-      <c r="H4" s="338"/>
-      <c r="I4" s="340"/>
+      <c r="C4" s="312"/>
+      <c r="D4" s="313"/>
+      <c r="E4" s="313"/>
+      <c r="F4" s="313"/>
+      <c r="G4" s="313"/>
+      <c r="H4" s="298"/>
+      <c r="I4" s="300"/>
       <c r="J4" s="50">
         <f>J3-(J3-H3*M3)/6</f>
         <v>139.16666666666666</v>
@@ -7391,8 +7001,8 @@
         <f>K3-(K3-H3*M3)/6</f>
         <v>139.16666666666666</v>
       </c>
-      <c r="L4" s="329"/>
-      <c r="M4" s="331"/>
+      <c r="L4" s="289"/>
+      <c r="M4" s="291"/>
       <c r="N4" s="53"/>
       <c r="O4" s="15" t="s">
         <v>7</v>
@@ -7403,8 +7013,8 @@
       <c r="Q4" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="R4" s="350"/>
-      <c r="S4" s="336"/>
+      <c r="R4" s="310"/>
+      <c r="S4" s="296"/>
       <c r="T4" s="53"/>
       <c r="U4" s="53"/>
       <c r="V4" s="62" t="s">
@@ -7446,15 +7056,15 @@
     <row r="5" spans="1:55" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="12"/>
       <c r="B5" s="12"/>
-      <c r="C5" s="354">
+      <c r="C5" s="314">
         <f ca="1">TODAY()</f>
-        <v>45490</v>
-      </c>
-      <c r="D5" s="355"/>
-      <c r="E5" s="355"/>
-      <c r="F5" s="355"/>
-      <c r="G5" s="355"/>
-      <c r="H5" s="355"/>
+        <v>45761</v>
+      </c>
+      <c r="D5" s="315"/>
+      <c r="E5" s="315"/>
+      <c r="F5" s="315"/>
+      <c r="G5" s="315"/>
+      <c r="H5" s="315"/>
       <c r="I5" s="27"/>
       <c r="J5" s="27"/>
       <c r="K5" s="27"/>
@@ -7521,10 +7131,10 @@
     <row r="6" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="12"/>
       <c r="B6" s="12"/>
-      <c r="C6" s="341"/>
-      <c r="D6" s="341"/>
-      <c r="E6" s="341"/>
-      <c r="F6" s="341"/>
+      <c r="C6" s="301"/>
+      <c r="D6" s="301"/>
+      <c r="E6" s="301"/>
+      <c r="F6" s="301"/>
       <c r="G6" s="9"/>
       <c r="H6" s="29"/>
       <c r="I6" s="10"/>
@@ -7665,17 +7275,17 @@
     <row r="8" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="12"/>
       <c r="B8" s="12"/>
-      <c r="C8" s="299" t="s">
+      <c r="C8" s="259" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="300"/>
-      <c r="E8" s="301"/>
+      <c r="D8" s="260"/>
+      <c r="E8" s="261"/>
       <c r="F8" s="34"/>
-      <c r="G8" s="305" t="s">
+      <c r="G8" s="265" t="s">
         <v>26</v>
       </c>
-      <c r="H8" s="306"/>
-      <c r="I8" s="307"/>
+      <c r="H8" s="266"/>
+      <c r="I8" s="267"/>
       <c r="J8" s="54"/>
       <c r="K8" s="55"/>
       <c r="L8" s="55"/>
@@ -7741,13 +7351,13 @@
     <row r="9" spans="1:55" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="12"/>
       <c r="B9" s="12"/>
-      <c r="C9" s="302"/>
-      <c r="D9" s="303"/>
-      <c r="E9" s="304"/>
+      <c r="C9" s="262"/>
+      <c r="D9" s="263"/>
+      <c r="E9" s="264"/>
       <c r="F9" s="35"/>
-      <c r="G9" s="308"/>
-      <c r="H9" s="309"/>
-      <c r="I9" s="310"/>
+      <c r="G9" s="268"/>
+      <c r="H9" s="269"/>
+      <c r="I9" s="270"/>
       <c r="J9" s="54"/>
       <c r="K9" s="55"/>
       <c r="L9" s="55"/>
@@ -7813,23 +7423,23 @@
     <row r="10" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10" s="12"/>
-      <c r="C10" s="311" t="s">
+      <c r="C10" s="271" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="313" t="s">
+      <c r="D10" s="273" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="315" t="s">
+      <c r="E10" s="275" t="s">
         <v>14</v>
       </c>
       <c r="F10" s="37"/>
-      <c r="G10" s="317" t="s">
+      <c r="G10" s="277" t="s">
         <v>7</v>
       </c>
-      <c r="H10" s="319" t="s">
+      <c r="H10" s="279" t="s">
         <v>15</v>
       </c>
-      <c r="I10" s="321" t="s">
+      <c r="I10" s="281" t="s">
         <v>14</v>
       </c>
       <c r="J10" s="54"/>
@@ -7881,13 +7491,13 @@
     <row r="11" spans="1:55" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="12"/>
       <c r="B11" s="12"/>
-      <c r="C11" s="312"/>
-      <c r="D11" s="314"/>
-      <c r="E11" s="316"/>
+      <c r="C11" s="272"/>
+      <c r="D11" s="274"/>
+      <c r="E11" s="276"/>
       <c r="F11" s="31"/>
-      <c r="G11" s="318"/>
-      <c r="H11" s="320"/>
-      <c r="I11" s="322"/>
+      <c r="G11" s="278"/>
+      <c r="H11" s="280"/>
+      <c r="I11" s="282"/>
       <c r="J11" s="54"/>
       <c r="K11" s="55"/>
       <c r="L11" s="55"/>
@@ -7967,14 +7577,14 @@
       <c r="N12" s="53"/>
       <c r="O12" s="9"/>
       <c r="P12" s="9"/>
-      <c r="R12" s="323" t="s">
+      <c r="R12" s="283" t="s">
         <v>21</v>
       </c>
-      <c r="S12" s="324"/>
-      <c r="T12" s="332" t="s">
+      <c r="S12" s="284"/>
+      <c r="T12" s="292" t="s">
         <v>30</v>
       </c>
-      <c r="U12" s="333"/>
+      <c r="U12" s="293"/>
       <c r="V12" s="53"/>
       <c r="W12" s="9"/>
       <c r="X12" s="9"/>
@@ -8042,8 +7652,8 @@
       <c r="N13" s="53"/>
       <c r="O13" s="9"/>
       <c r="P13" s="9"/>
-      <c r="R13" s="325"/>
-      <c r="S13" s="326"/>
+      <c r="R13" s="285"/>
+      <c r="S13" s="286"/>
       <c r="T13" s="56" t="s">
         <v>21</v>
       </c>
@@ -8115,23 +7725,23 @@
       <c r="L14" s="55"/>
       <c r="M14" s="55"/>
       <c r="N14" s="53"/>
-      <c r="O14" s="287" t="s">
+      <c r="O14" s="247" t="s">
         <v>28</v>
       </c>
-      <c r="P14" s="288"/>
-      <c r="Q14" s="291">
+      <c r="P14" s="248"/>
+      <c r="Q14" s="251">
         <v>0.02</v>
       </c>
-      <c r="R14" s="297">
+      <c r="R14" s="257">
         <f>IF(R12="ЖЕЛ",J4*Q14,K4*Q14)</f>
         <v>2.7833333333333332</v>
       </c>
-      <c r="S14" s="298"/>
-      <c r="T14" s="281">
+      <c r="S14" s="258"/>
+      <c r="T14" s="241">
         <f>J4</f>
         <v>139.16666666666666</v>
       </c>
-      <c r="U14" s="284">
+      <c r="U14" s="244">
         <f>K4</f>
         <v>139.16666666666666</v>
       </c>
@@ -8200,13 +7810,13 @@
       <c r="L15" s="55"/>
       <c r="M15" s="55"/>
       <c r="N15" s="36"/>
-      <c r="O15" s="289"/>
-      <c r="P15" s="290"/>
-      <c r="Q15" s="292"/>
-      <c r="R15" s="295"/>
-      <c r="S15" s="296"/>
-      <c r="T15" s="282"/>
-      <c r="U15" s="285"/>
+      <c r="O15" s="249"/>
+      <c r="P15" s="250"/>
+      <c r="Q15" s="252"/>
+      <c r="R15" s="255"/>
+      <c r="S15" s="256"/>
+      <c r="T15" s="242"/>
+      <c r="U15" s="245"/>
       <c r="V15" s="9"/>
       <c r="W15" s="12"/>
       <c r="X15" s="12"/>
@@ -8272,20 +7882,20 @@
       <c r="L16" s="55"/>
       <c r="M16" s="55"/>
       <c r="N16" s="9"/>
-      <c r="O16" s="287" t="s">
+      <c r="O16" s="247" t="s">
         <v>29</v>
       </c>
-      <c r="P16" s="288"/>
-      <c r="Q16" s="291">
+      <c r="P16" s="248"/>
+      <c r="Q16" s="251">
         <v>0</v>
       </c>
-      <c r="R16" s="293">
+      <c r="R16" s="253">
         <f>IF(R12="ЖЕЛ",J4*Q16,K4*Q16)</f>
         <v>0</v>
       </c>
-      <c r="S16" s="294"/>
-      <c r="T16" s="282"/>
-      <c r="U16" s="285"/>
+      <c r="S16" s="254"/>
+      <c r="T16" s="242"/>
+      <c r="U16" s="245"/>
       <c r="V16" s="9"/>
       <c r="W16" s="12"/>
       <c r="X16" s="12"/>
@@ -8335,13 +7945,13 @@
       <c r="L17" s="43"/>
       <c r="M17" s="9"/>
       <c r="N17" s="9"/>
-      <c r="O17" s="289"/>
-      <c r="P17" s="290"/>
-      <c r="Q17" s="292"/>
-      <c r="R17" s="295"/>
-      <c r="S17" s="296"/>
-      <c r="T17" s="283"/>
-      <c r="U17" s="286"/>
+      <c r="O17" s="249"/>
+      <c r="P17" s="250"/>
+      <c r="Q17" s="252"/>
+      <c r="R17" s="255"/>
+      <c r="S17" s="256"/>
+      <c r="T17" s="243"/>
+      <c r="U17" s="246"/>
       <c r="V17" s="9"/>
       <c r="W17" s="12"/>
       <c r="X17" s="12"/>
